--- a/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
@@ -1,38 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{3ABD91F6-92AE-44A5-86AA-B41BABEA9E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="212">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -259,10 +244,13 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10697743</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t xml:space="preserve">Test failed for 'PolandOne TwentyFiveAprilTwentyOne' Employee:{10697990}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('text=Assign Pay Group for Hire: PolandOne TwentyFiveAprilTwentyOne')[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>765 Retail Team 1 (Hosun Pecypy (10223419))</t>
@@ -274,7 +262,7 @@
     <t>PolandOne</t>
   </si>
   <si>
-    <t>TwentyFiveAprilSeven</t>
+    <t>TwentyFiveAprilTwentyOne</t>
   </si>
   <si>
     <t xml:space="preserve">698 980 460 </t>
@@ -370,7 +358,7 @@
     <t>ID Card</t>
   </si>
   <si>
-    <t>GHE456200</t>
+    <t>GHE456246</t>
   </si>
   <si>
     <t>Male</t>
@@ -412,7 +400,10 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10697754</t>
+    <t xml:space="preserve">Test failed for 'PolandTwo TwentyFiveAprilTwentyOne' Employee:{10697991}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('text=Assign Pay Group for Hire: PolandTwo TwentyFiveAprilTwentyOne')[22m
+</t>
   </si>
   <si>
     <t>765 Store Management (Jizur Buzese (10226524))</t>
@@ -421,7 +412,7 @@
     <t>PolandTwo</t>
   </si>
   <si>
-    <t>Auto 97159595</t>
+    <t>Auto 32782615</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -436,7 +427,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>GHE456201</t>
+    <t>GHE456247</t>
   </si>
   <si>
     <t>Female</t>
@@ -448,19 +439,22 @@
     <t>Test_3</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'PolandThree TwentyFiveAprilTwentyOne' Employee:{10697992}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('text=Assign Pay Group for Hire: PolandThree TwentyFiveAprilTwentyOne')[22m
+</t>
+  </si>
+  <si>
     <t>PolandThree</t>
   </si>
   <si>
-    <t>TwentyFiveAprilSevenA</t>
-  </si>
-  <si>
-    <t>Auto 86945897</t>
+    <t>Auto 35210117</t>
   </si>
   <si>
     <t>Department Manager_NEW</t>
   </si>
   <si>
-    <t>GHE456215</t>
+    <t>GHE456233</t>
   </si>
   <si>
     <t>01/01/2020</t>
@@ -469,13 +463,16 @@
     <t>Test_4</t>
   </si>
   <si>
-    <t>10697757</t>
+    <t xml:space="preserve">Test failed for 'PolandFour TwentyFiveAprilTwentyOne' Employee:{10697993}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('text=Assign Pay Group for Hire: PolandFour TwentyFiveAprilTwentyOne')[22m
+</t>
   </si>
   <si>
     <t>PolandFour</t>
   </si>
   <si>
-    <t>Auto 10047885</t>
+    <t>Auto 65030250</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -490,16 +487,22 @@
     <t>RE023_NEW</t>
   </si>
   <si>
-    <t>GHE456203</t>
+    <t>GHE456234</t>
   </si>
   <si>
     <t>Test_5</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'PolandFive TwentyFiveAprilTwentyOne' Employee:{10697994}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('text=Assign Pay Group for Hire: PolandFive TwentyFiveAprilTwentyOne')[22m
+</t>
+  </si>
+  <si>
     <t>PolandFive</t>
   </si>
   <si>
-    <t>Auto 17526951</t>
+    <t>Auto 70343081</t>
   </si>
   <si>
     <t>Assistant Store Manager_NEW</t>
@@ -508,7 +511,7 @@
     <t>RE035_NEW</t>
   </si>
   <si>
-    <t>GHE456204</t>
+    <t>GHE456235</t>
   </si>
   <si>
     <t>01/01/2021</t>
@@ -517,13 +520,10 @@
     <t>Test_6</t>
   </si>
   <si>
-    <t>10697759</t>
-  </si>
-  <si>
     <t>PolandSix</t>
   </si>
   <si>
-    <t>Auto 84868528</t>
+    <t>Auto 35350923</t>
   </si>
   <si>
     <t>In-Store Visual Merchandising Manager_NEW</t>
@@ -535,7 +535,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>GHE456205</t>
+    <t>GHE456236</t>
   </si>
   <si>
     <t>Test_7</t>
@@ -550,13 +550,16 @@
     <t>Team Manager - Retail_NEW</t>
   </si>
   <si>
-    <t>GHE456206</t>
+    <t>GHE456237</t>
   </si>
   <si>
     <t>Test_8</t>
   </si>
   <si>
-    <t>10697745</t>
+    <t xml:space="preserve">Test failed for 'PolandEight TwentyFiveAprilTwentyOne' Employee:{10697998}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('text=Assign Pay Group for Hire: PolandEight TwentyFiveAprilTwentyOne')[22m
+</t>
   </si>
   <si>
     <t>PolandEight</t>
@@ -571,15 +574,12 @@
     <t>250 Human Resources Retail</t>
   </si>
   <si>
-    <t>GHE456207</t>
+    <t>GHE456238</t>
   </si>
   <si>
     <t>Test_9</t>
   </si>
   <si>
-    <t>10697746</t>
-  </si>
-  <si>
     <t>PolandNine</t>
   </si>
   <si>
@@ -589,15 +589,12 @@
     <t>258 Cash Office</t>
   </si>
   <si>
-    <t>GHE456208</t>
+    <t>GHE456239</t>
   </si>
   <si>
     <t>Test_10</t>
   </si>
   <si>
-    <t>10697747</t>
-  </si>
-  <si>
     <t>PolandTen</t>
   </si>
   <si>
@@ -607,15 +604,12 @@
     <t>Trial</t>
   </si>
   <si>
-    <t>GHE456209</t>
+    <t>GHE456240</t>
   </si>
   <si>
     <t>Test_11</t>
   </si>
   <si>
-    <t>10697748</t>
-  </si>
-  <si>
     <t>PolandEleven</t>
   </si>
   <si>
@@ -628,15 +622,12 @@
     <t>253 Supervisors</t>
   </si>
   <si>
-    <t>GHE456210</t>
+    <t>GHE456241</t>
   </si>
   <si>
     <t>Test_12</t>
   </si>
   <si>
-    <t>10697749</t>
-  </si>
-  <si>
     <t>PolandTwleve</t>
   </si>
   <si>
@@ -649,34 +640,28 @@
     <t>256 Visual Merchandising</t>
   </si>
   <si>
-    <t>GHE456211</t>
+    <t>GHE456242</t>
   </si>
   <si>
     <t>Test_13</t>
   </si>
   <si>
-    <t>10697750</t>
-  </si>
-  <si>
     <t>PolandThirteen</t>
   </si>
   <si>
     <t>RE043_NEW</t>
   </si>
   <si>
-    <t>GHE456212</t>
+    <t>GHE456243</t>
   </si>
   <si>
     <t>Test_14</t>
   </si>
   <si>
-    <t>10697751</t>
-  </si>
-  <si>
     <t>PolandFourteen</t>
   </si>
   <si>
-    <t>GHE456213</t>
+    <t>GHE456244</t>
   </si>
   <si>
     <t>Test_15</t>
@@ -685,151 +670,151 @@
     <t>PolandFifteen</t>
   </si>
   <si>
-    <t>GHE456214</t>
+    <t>GHE456245</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="63"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="10"/>
       <color indexed="12"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="10"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
+      <scheme val="major"/>
       <sz val="10"/>
       <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="63"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color indexed="12"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="63"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
   </fonts>
   <fills count="7">
@@ -864,7 +849,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -878,15 +863,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -897,25 +876,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -1357,9 +1326,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
     <col min="2" max="2" width="11.109375" customWidth="1"/>
@@ -1440,7 +1409,7 @@
     <col min="77" max="77" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="17.4" customHeight="1" spans="1:77" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1673,7 +1642,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>74</v>
       </c>
@@ -1705,8 +1674,8 @@
         <v>83</v>
       </c>
       <c r="K2" s="37">
-        <f t="shared" ref="K2:K16" ca="1" si="0">TODAY()-31</f>
-        <v>45724</v>
+        <f t="shared" ref="K2:K16" si="0">TODAY()-31</f>
+        <v>45738</v>
       </c>
       <c r="L2" s="32" t="s">
         <v>78</v>
@@ -1745,8 +1714,8 @@
         <v>83</v>
       </c>
       <c r="X2" s="40">
-        <f t="shared" ref="X2:X16" ca="1" si="1">K2</f>
-        <v>45724</v>
+        <f t="shared" ref="X2:X16" si="1">K2</f>
+        <v>45738</v>
       </c>
       <c r="Y2" s="36" t="s">
         <v>91</v>
@@ -1806,16 +1775,16 @@
         <v>101</v>
       </c>
       <c r="AR2" s="44">
-        <f t="shared" ref="AR2:AR16" ca="1" si="2">X2</f>
-        <v>45724</v>
+        <f t="shared" ref="AR2:AR16" si="2">X2</f>
+        <v>45738</v>
       </c>
       <c r="AS2" s="44">
-        <f t="shared" ref="AS2:AS16" ca="1" si="3">X2</f>
-        <v>45724</v>
-      </c>
-      <c r="AT2" s="40" t="str">
+        <f t="shared" ref="AS2:AS16" si="3">X2</f>
+        <v>45738</v>
+      </c>
+      <c r="AT2" s="40">
         <f t="shared" ref="AT2:AT16" si="4">AM2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU2" s="36" t="s">
         <v>102</v>
@@ -1851,7 +1820,7 @@
         <v>109</v>
       </c>
       <c r="BF2" s="46">
-        <v>9893790750</v>
+        <v>9893790796</v>
       </c>
       <c r="BG2" s="32" t="s">
         <v>78</v>
@@ -1860,7 +1829,7 @@
         <v>110</v>
       </c>
       <c r="BI2" s="32">
-        <v>47678965420</v>
+        <v>47678965466</v>
       </c>
       <c r="BJ2" s="32" t="s">
         <v>78</v>
@@ -1911,7 +1880,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:77" s="27" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="13.8" customHeight="1" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
         <v>125</v>
       </c>
@@ -1943,8 +1912,8 @@
         <v>83</v>
       </c>
       <c r="K3" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>78</v>
@@ -1983,8 +1952,8 @@
         <v>83</v>
       </c>
       <c r="X3" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y3" s="36" t="s">
         <v>91</v>
@@ -2044,16 +2013,16 @@
         <v>101</v>
       </c>
       <c r="AR3" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS3" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
-      </c>
-      <c r="AT3" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>45738</v>
+      </c>
+      <c r="AT3" s="40">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU3" s="36" t="s">
         <v>132</v>
@@ -2089,7 +2058,7 @@
         <v>109</v>
       </c>
       <c r="BF3" s="46">
-        <v>9893790751</v>
+        <v>9893790797</v>
       </c>
       <c r="BG3" s="32" t="s">
         <v>78</v>
@@ -2098,7 +2067,7 @@
         <v>110</v>
       </c>
       <c r="BI3" s="32">
-        <v>47678965421</v>
+        <v>47678965467</v>
       </c>
       <c r="BJ3" s="32" t="s">
         <v>78</v>
@@ -2149,12 +2118,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:77" s="27" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="13.8" customHeight="1" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="51">
-        <v>10697767</v>
+      <c r="B4" s="51" t="s">
+        <v>138</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>76</v>
@@ -2166,10 +2135,10 @@
         <v>78</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="H4" s="35" t="s">
         <v>81</v>
@@ -2181,8 +2150,8 @@
         <v>83</v>
       </c>
       <c r="K4" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L4" s="32" t="s">
         <v>78</v>
@@ -2221,8 +2190,8 @@
         <v>83</v>
       </c>
       <c r="X4" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y4" s="36" t="s">
         <v>91</v>
@@ -2282,16 +2251,16 @@
         <v>101</v>
       </c>
       <c r="AR4" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS4" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
-      </c>
-      <c r="AT4" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>45738</v>
+      </c>
+      <c r="AT4" s="40">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU4" s="36" t="s">
         <v>132</v>
@@ -2327,7 +2296,7 @@
         <v>109</v>
       </c>
       <c r="BF4" s="46">
-        <v>9893790765</v>
+        <v>9893790783</v>
       </c>
       <c r="BG4" s="32" t="s">
         <v>78</v>
@@ -2336,7 +2305,7 @@
         <v>110</v>
       </c>
       <c r="BI4" s="32">
-        <v>47678965435</v>
+        <v>47678965453</v>
       </c>
       <c r="BJ4" s="32" t="s">
         <v>78</v>
@@ -2387,7 +2356,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:77" s="27" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="14.4" customHeight="1" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="45" t="s">
         <v>144</v>
       </c>
@@ -2419,8 +2388,8 @@
         <v>83</v>
       </c>
       <c r="K5" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L5" s="32" t="s">
         <v>78</v>
@@ -2459,8 +2428,8 @@
         <v>83</v>
       </c>
       <c r="X5" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y5" s="36" t="s">
         <v>91</v>
@@ -2505,8 +2474,8 @@
         <v>97</v>
       </c>
       <c r="AM5" s="43">
-        <f ca="1">TODAY()+365</f>
-        <v>46120</v>
+        <f>TODAY()+365</f>
+        <v>46134</v>
       </c>
       <c r="AN5" s="32">
         <v>110</v>
@@ -2521,12 +2490,12 @@
         <v>101</v>
       </c>
       <c r="AR5" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS5" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
+        <f t="shared" si="3"/>
+        <v>45738</v>
       </c>
       <c r="AT5" s="40" t="s">
         <v>98</v>
@@ -2565,7 +2534,7 @@
         <v>109</v>
       </c>
       <c r="BF5" s="46">
-        <v>9893790753</v>
+        <v>9893790784</v>
       </c>
       <c r="BG5" s="32" t="s">
         <v>78</v>
@@ -2574,7 +2543,7 @@
         <v>110</v>
       </c>
       <c r="BI5" s="32">
-        <v>47678965423</v>
+        <v>47678965454</v>
       </c>
       <c r="BJ5" s="32" t="s">
         <v>78</v>
@@ -2625,12 +2594,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="B6" s="45">
-        <v>10697758</v>
+      <c r="B6" s="45" t="s">
+        <v>154</v>
       </c>
       <c r="C6" s="30" t="s">
         <v>76</v>
@@ -2642,7 +2611,7 @@
         <v>78</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G6" s="34" t="s">
         <v>80</v>
@@ -2657,8 +2626,8 @@
         <v>83</v>
       </c>
       <c r="K6" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L6" s="32" t="s">
         <v>78</v>
@@ -2697,20 +2666,20 @@
         <v>83</v>
       </c>
       <c r="X6" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y6" s="36" t="s">
         <v>91</v>
       </c>
       <c r="Z6" s="36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AA6" s="41" t="s">
         <v>89</v>
       </c>
       <c r="AB6" s="42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AC6" s="41" t="s">
         <v>94</v>
@@ -2737,7 +2706,7 @@
         <v>45293</v>
       </c>
       <c r="AK6" s="41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL6" s="41" t="s">
         <v>97</v>
@@ -2758,16 +2727,16 @@
         <v>101</v>
       </c>
       <c r="AR6" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS6" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
-      </c>
-      <c r="AT6" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>45738</v>
+      </c>
+      <c r="AT6" s="40">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU6" s="36" t="s">
         <v>132</v>
@@ -2803,7 +2772,7 @@
         <v>109</v>
       </c>
       <c r="BF6" s="46">
-        <v>9893790754</v>
+        <v>9893790785</v>
       </c>
       <c r="BG6" s="32" t="s">
         <v>78</v>
@@ -2812,7 +2781,7 @@
         <v>110</v>
       </c>
       <c r="BI6" s="32">
-        <v>47678965424</v>
+        <v>47678965455</v>
       </c>
       <c r="BJ6" s="32" t="s">
         <v>78</v>
@@ -2821,7 +2790,7 @@
         <v>111</v>
       </c>
       <c r="BL6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM6" s="41" t="s">
         <v>113</v>
@@ -2833,7 +2802,7 @@
         <v>114</v>
       </c>
       <c r="BP6" s="47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BQ6" s="48" t="s">
         <v>116</v>
@@ -2863,16 +2832,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="C7" s="30" t="s">
-        <v>76</v>
-      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="31" t="s">
         <v>127</v>
       </c>
@@ -2895,8 +2860,8 @@
         <v>83</v>
       </c>
       <c r="K7" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L7" s="32" t="s">
         <v>78</v>
@@ -2935,8 +2900,8 @@
         <v>83</v>
       </c>
       <c r="X7" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y7" s="36" t="s">
         <v>91</v>
@@ -2996,16 +2961,16 @@
         <v>101</v>
       </c>
       <c r="AR7" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS7" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
-      </c>
-      <c r="AT7" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>45738</v>
+      </c>
+      <c r="AT7" s="40">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU7" s="36" t="s">
         <v>132</v>
@@ -3041,7 +3006,7 @@
         <v>109</v>
       </c>
       <c r="BF7" s="46">
-        <v>9893790755</v>
+        <v>9893790786</v>
       </c>
       <c r="BG7" s="32" t="s">
         <v>78</v>
@@ -3050,7 +3015,7 @@
         <v>110</v>
       </c>
       <c r="BI7" s="32">
-        <v>47678965425</v>
+        <v>47678965456</v>
       </c>
       <c r="BJ7" s="32" t="s">
         <v>78</v>
@@ -3101,16 +3066,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="45" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="50">
-        <v>10697760</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>76</v>
-      </c>
+      <c r="B8" s="50"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="31" t="s">
         <v>127</v>
       </c>
@@ -3133,8 +3094,8 @@
         <v>83</v>
       </c>
       <c r="K8" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L8" s="32" t="s">
         <v>78</v>
@@ -3173,8 +3134,8 @@
         <v>83</v>
       </c>
       <c r="X8" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y8" s="36" t="s">
         <v>91</v>
@@ -3219,8 +3180,8 @@
         <v>97</v>
       </c>
       <c r="AM8" s="43">
-        <f ca="1">TODAY()+365</f>
-        <v>46120</v>
+        <f>TODAY()+365</f>
+        <v>46134</v>
       </c>
       <c r="AN8" s="32">
         <v>110</v>
@@ -3235,12 +3196,12 @@
         <v>101</v>
       </c>
       <c r="AR8" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS8" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
+        <f t="shared" si="3"/>
+        <v>45738</v>
       </c>
       <c r="AT8" s="40" t="s">
         <v>98</v>
@@ -3279,7 +3240,7 @@
         <v>109</v>
       </c>
       <c r="BF8" s="46">
-        <v>9893790756</v>
+        <v>9893790787</v>
       </c>
       <c r="BG8" s="32" t="s">
         <v>78</v>
@@ -3288,7 +3249,7 @@
         <v>110</v>
       </c>
       <c r="BI8" s="32">
-        <v>47678965426</v>
+        <v>47678965457</v>
       </c>
       <c r="BJ8" s="32" t="s">
         <v>78</v>
@@ -3309,7 +3270,7 @@
         <v>114</v>
       </c>
       <c r="BP8" s="47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BQ8" s="48" t="s">
         <v>116</v>
@@ -3339,7 +3300,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="45" t="s">
         <v>173</v>
       </c>
@@ -3371,8 +3332,8 @@
         <v>83</v>
       </c>
       <c r="K9" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L9" s="32" t="s">
         <v>78</v>
@@ -3411,8 +3372,8 @@
         <v>83</v>
       </c>
       <c r="X9" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y9" s="36" t="s">
         <v>91</v>
@@ -3472,16 +3433,16 @@
         <v>101</v>
       </c>
       <c r="AR9" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS9" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
-      </c>
-      <c r="AT9" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>45738</v>
+      </c>
+      <c r="AT9" s="40">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU9" s="36" t="s">
         <v>102</v>
@@ -3517,7 +3478,7 @@
         <v>109</v>
       </c>
       <c r="BF9" s="46">
-        <v>9893790757</v>
+        <v>9893790788</v>
       </c>
       <c r="BG9" s="32" t="s">
         <v>78</v>
@@ -3526,7 +3487,7 @@
         <v>110</v>
       </c>
       <c r="BI9" s="32">
-        <v>47678965427</v>
+        <v>47678965458</v>
       </c>
       <c r="BJ9" s="32" t="s">
         <v>78</v>
@@ -3577,16 +3538,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>76</v>
-      </c>
+      <c r="B10" s="45"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="31" t="s">
         <v>77</v>
       </c>
@@ -3594,7 +3551,7 @@
         <v>78</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G10" s="34" t="s">
         <v>80</v>
@@ -3609,8 +3566,8 @@
         <v>83</v>
       </c>
       <c r="K10" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L10" s="32" t="s">
         <v>78</v>
@@ -3649,8 +3606,8 @@
         <v>83</v>
       </c>
       <c r="X10" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y10" s="36" t="s">
         <v>91</v>
@@ -3662,7 +3619,7 @@
         <v>89</v>
       </c>
       <c r="AB10" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AC10" s="41" t="s">
         <v>150</v>
@@ -3710,22 +3667,22 @@
         <v>101</v>
       </c>
       <c r="AR10" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS10" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
-      </c>
-      <c r="AT10" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>45738</v>
+      </c>
+      <c r="AT10" s="40">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU10" s="36" t="s">
         <v>102</v>
       </c>
       <c r="AV10" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AW10" s="32" t="s">
         <v>104</v>
@@ -3755,7 +3712,7 @@
         <v>109</v>
       </c>
       <c r="BF10" s="46">
-        <v>9893790758</v>
+        <v>9893790789</v>
       </c>
       <c r="BG10" s="32" t="s">
         <v>78</v>
@@ -3764,7 +3721,7 @@
         <v>110</v>
       </c>
       <c r="BI10" s="32">
-        <v>47678965428</v>
+        <v>47678965459</v>
       </c>
       <c r="BJ10" s="32" t="s">
         <v>78</v>
@@ -3773,7 +3730,7 @@
         <v>111</v>
       </c>
       <c r="BL10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BM10" s="41" t="s">
         <v>113</v>
@@ -3785,7 +3742,7 @@
         <v>114</v>
       </c>
       <c r="BP10" s="47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BQ10" s="48" t="s">
         <v>116</v>
@@ -3815,16 +3772,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>187</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>76</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="B11" s="45"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="31" t="s">
         <v>77</v>
       </c>
@@ -3832,7 +3785,7 @@
         <v>78</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>80</v>
@@ -3847,8 +3800,8 @@
         <v>83</v>
       </c>
       <c r="K11" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L11" s="32" t="s">
         <v>78</v>
@@ -3887,8 +3840,8 @@
         <v>83</v>
       </c>
       <c r="X11" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y11" s="36" t="s">
         <v>91</v>
@@ -3900,7 +3853,7 @@
         <v>148</v>
       </c>
       <c r="AB11" s="42" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AC11" s="41" t="s">
         <v>94</v>
@@ -3933,8 +3886,8 @@
         <v>97</v>
       </c>
       <c r="AM11" s="43">
-        <f ca="1">TODAY()+365</f>
-        <v>46120</v>
+        <f>TODAY()+365</f>
+        <v>46134</v>
       </c>
       <c r="AN11" s="32">
         <v>110</v>
@@ -3943,22 +3896,22 @@
         <v>99</v>
       </c>
       <c r="AP11" s="36" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AQ11" s="36" t="s">
         <v>101</v>
       </c>
       <c r="AR11" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS11" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
+        <f t="shared" si="3"/>
+        <v>45738</v>
       </c>
       <c r="AT11" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>46120</v>
+        <f t="shared" si="4"/>
+        <v>46134</v>
       </c>
       <c r="AU11" s="36" t="s">
         <v>102</v>
@@ -3994,7 +3947,7 @@
         <v>109</v>
       </c>
       <c r="BF11" s="46">
-        <v>9893790759</v>
+        <v>9893790790</v>
       </c>
       <c r="BG11" s="32" t="s">
         <v>78</v>
@@ -4003,7 +3956,7 @@
         <v>110</v>
       </c>
       <c r="BI11" s="32">
-        <v>47678965429</v>
+        <v>47678965460</v>
       </c>
       <c r="BJ11" s="32" t="s">
         <v>78</v>
@@ -4012,7 +3965,7 @@
         <v>111</v>
       </c>
       <c r="BL11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="BM11" s="41" t="s">
         <v>135</v>
@@ -4054,16 +4007,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>76</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="31" t="s">
         <v>77</v>
       </c>
@@ -4071,7 +4020,7 @@
         <v>78</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G12" s="34" t="s">
         <v>80</v>
@@ -4086,8 +4035,8 @@
         <v>83</v>
       </c>
       <c r="K12" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L12" s="32" t="s">
         <v>78</v>
@@ -4126,8 +4075,8 @@
         <v>83</v>
       </c>
       <c r="X12" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y12" s="36" t="s">
         <v>91</v>
@@ -4139,7 +4088,7 @@
         <v>89</v>
       </c>
       <c r="AB12" s="42" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AC12" s="41" t="s">
         <v>150</v>
@@ -4166,7 +4115,7 @@
         <v>45293</v>
       </c>
       <c r="AK12" s="41" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AL12" s="41" t="s">
         <v>97</v>
@@ -4187,22 +4136,22 @@
         <v>101</v>
       </c>
       <c r="AR12" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS12" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
-      </c>
-      <c r="AT12" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>45738</v>
+      </c>
+      <c r="AT12" s="40">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU12" s="36" t="s">
         <v>102</v>
       </c>
       <c r="AV12" s="45" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AW12" s="32" t="s">
         <v>104</v>
@@ -4232,7 +4181,7 @@
         <v>109</v>
       </c>
       <c r="BF12" s="46">
-        <v>9893790760</v>
+        <v>9893790791</v>
       </c>
       <c r="BG12" s="32" t="s">
         <v>78</v>
@@ -4241,7 +4190,7 @@
         <v>110</v>
       </c>
       <c r="BI12" s="32">
-        <v>47678965430</v>
+        <v>47678965461</v>
       </c>
       <c r="BJ12" s="32" t="s">
         <v>78</v>
@@ -4250,7 +4199,7 @@
         <v>111</v>
       </c>
       <c r="BL12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="BM12" s="41" t="s">
         <v>113</v>
@@ -4262,7 +4211,7 @@
         <v>114</v>
       </c>
       <c r="BP12" s="47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BQ12" s="48" t="s">
         <v>116</v>
@@ -4292,16 +4241,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="B13" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>76</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="B13" s="45"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="31" t="s">
         <v>77</v>
       </c>
@@ -4309,7 +4254,7 @@
         <v>78</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G13" s="34" t="s">
         <v>80</v>
@@ -4324,8 +4269,8 @@
         <v>83</v>
       </c>
       <c r="K13" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L13" s="32" t="s">
         <v>78</v>
@@ -4364,8 +4309,8 @@
         <v>83</v>
       </c>
       <c r="X13" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y13" s="36" t="s">
         <v>91</v>
@@ -4377,7 +4322,7 @@
         <v>89</v>
       </c>
       <c r="AB13" s="42" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AC13" s="41" t="s">
         <v>94</v>
@@ -4404,7 +4349,7 @@
         <v>45293</v>
       </c>
       <c r="AK13" s="41" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AL13" s="41" t="s">
         <v>97</v>
@@ -4425,22 +4370,22 @@
         <v>101</v>
       </c>
       <c r="AR13" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS13" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
-      </c>
-      <c r="AT13" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>45738</v>
+      </c>
+      <c r="AT13" s="40">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU13" s="36" t="s">
         <v>102</v>
       </c>
       <c r="AV13" s="45" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="AW13" s="32" t="s">
         <v>104</v>
@@ -4470,7 +4415,7 @@
         <v>109</v>
       </c>
       <c r="BF13" s="46">
-        <v>9893790761</v>
+        <v>9893790792</v>
       </c>
       <c r="BG13" s="32" t="s">
         <v>78</v>
@@ -4479,7 +4424,7 @@
         <v>110</v>
       </c>
       <c r="BI13" s="32">
-        <v>47678965431</v>
+        <v>47678965462</v>
       </c>
       <c r="BJ13" s="32" t="s">
         <v>78</v>
@@ -4488,7 +4433,7 @@
         <v>111</v>
       </c>
       <c r="BL13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="BM13" s="41" t="s">
         <v>135</v>
@@ -4530,16 +4475,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>76</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="B14" s="45"/>
+      <c r="C14" s="30"/>
       <c r="D14" s="31" t="s">
         <v>77</v>
       </c>
@@ -4547,7 +4488,7 @@
         <v>78</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G14" s="34" t="s">
         <v>80</v>
@@ -4562,8 +4503,8 @@
         <v>83</v>
       </c>
       <c r="K14" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L14" s="32" t="s">
         <v>78</v>
@@ -4602,8 +4543,8 @@
         <v>83</v>
       </c>
       <c r="X14" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y14" s="36" t="s">
         <v>91</v>
@@ -4615,7 +4556,7 @@
         <v>148</v>
       </c>
       <c r="AB14" s="42" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AC14" s="41" t="s">
         <v>150</v>
@@ -4642,14 +4583,14 @@
         <v>45293</v>
       </c>
       <c r="AK14" s="41" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AL14" s="41" t="s">
         <v>97</v>
       </c>
       <c r="AM14" s="43">
-        <f ca="1">TODAY()+365</f>
-        <v>46120</v>
+        <f>TODAY()+365</f>
+        <v>46134</v>
       </c>
       <c r="AN14" s="32">
         <v>110</v>
@@ -4664,12 +4605,12 @@
         <v>101</v>
       </c>
       <c r="AR14" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS14" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
+        <f t="shared" si="3"/>
+        <v>45738</v>
       </c>
       <c r="AT14" s="40" t="s">
         <v>98</v>
@@ -4708,7 +4649,7 @@
         <v>109</v>
       </c>
       <c r="BF14" s="46">
-        <v>9893790762</v>
+        <v>9893790793</v>
       </c>
       <c r="BG14" s="32" t="s">
         <v>78</v>
@@ -4717,7 +4658,7 @@
         <v>110</v>
       </c>
       <c r="BI14" s="32">
-        <v>47678965432</v>
+        <v>47678965463</v>
       </c>
       <c r="BJ14" s="32" t="s">
         <v>78</v>
@@ -4726,7 +4667,7 @@
         <v>111</v>
       </c>
       <c r="BL14" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="BM14" s="41" t="s">
         <v>113</v>
@@ -4738,7 +4679,7 @@
         <v>114</v>
       </c>
       <c r="BP14" s="47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BQ14" s="48" t="s">
         <v>116</v>
@@ -4768,16 +4709,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>76</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="31" t="s">
         <v>77</v>
       </c>
@@ -4785,7 +4722,7 @@
         <v>78</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G15" s="34" t="s">
         <v>80</v>
@@ -4800,8 +4737,8 @@
         <v>83</v>
       </c>
       <c r="K15" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L15" s="32" t="s">
         <v>78</v>
@@ -4840,8 +4777,8 @@
         <v>83</v>
       </c>
       <c r="X15" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y15" s="36" t="s">
         <v>91</v>
@@ -4886,8 +4823,8 @@
         <v>97</v>
       </c>
       <c r="AM15" s="43">
-        <f ca="1">TODAY()+365</f>
-        <v>46120</v>
+        <f>TODAY()+365</f>
+        <v>46134</v>
       </c>
       <c r="AN15" s="32">
         <v>110</v>
@@ -4896,22 +4833,22 @@
         <v>99</v>
       </c>
       <c r="AP15" s="41" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AQ15" s="36" t="s">
         <v>101</v>
       </c>
       <c r="AR15" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS15" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
+        <f t="shared" si="3"/>
+        <v>45738</v>
       </c>
       <c r="AT15" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>46120</v>
+        <f t="shared" si="4"/>
+        <v>46134</v>
       </c>
       <c r="AU15" s="36" t="s">
         <v>102</v>
@@ -4947,7 +4884,7 @@
         <v>109</v>
       </c>
       <c r="BF15" s="46">
-        <v>9893790763</v>
+        <v>9893790794</v>
       </c>
       <c r="BG15" s="32" t="s">
         <v>78</v>
@@ -4956,7 +4893,7 @@
         <v>110</v>
       </c>
       <c r="BI15" s="32">
-        <v>47678965433</v>
+        <v>47678965464</v>
       </c>
       <c r="BJ15" s="32" t="s">
         <v>78</v>
@@ -4965,7 +4902,7 @@
         <v>111</v>
       </c>
       <c r="BL15" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="BM15" s="41" t="s">
         <v>135</v>
@@ -5007,16 +4944,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:77" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="B16" s="45">
-        <v>10697752</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>76</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="B16" s="45"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="31" t="s">
         <v>77</v>
       </c>
@@ -5024,7 +4957,7 @@
         <v>78</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G16" s="34" t="s">
         <v>80</v>
@@ -5039,8 +4972,8 @@
         <v>83</v>
       </c>
       <c r="K16" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>45724</v>
+        <f t="shared" si="0"/>
+        <v>45738</v>
       </c>
       <c r="L16" s="32" t="s">
         <v>78</v>
@@ -5079,8 +5012,8 @@
         <v>83</v>
       </c>
       <c r="X16" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>45724</v>
+        <f t="shared" si="1"/>
+        <v>45738</v>
       </c>
       <c r="Y16" s="36" t="s">
         <v>91</v>
@@ -5140,16 +5073,16 @@
         <v>101</v>
       </c>
       <c r="AR16" s="44">
-        <f t="shared" ca="1" si="2"/>
-        <v>45724</v>
+        <f t="shared" si="2"/>
+        <v>45738</v>
       </c>
       <c r="AS16" s="44">
-        <f t="shared" ca="1" si="3"/>
-        <v>45724</v>
-      </c>
-      <c r="AT16" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>45738</v>
+      </c>
+      <c r="AT16" s="40">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU16" s="36" t="s">
         <v>102</v>
@@ -5185,7 +5118,7 @@
         <v>109</v>
       </c>
       <c r="BF16" s="46">
-        <v>9893790764</v>
+        <v>9893790795</v>
       </c>
       <c r="BG16" s="32" t="s">
         <v>78</v>
@@ -5194,7 +5127,7 @@
         <v>110</v>
       </c>
       <c r="BI16" s="32">
-        <v>47678965434</v>
+        <v>47678965465</v>
       </c>
       <c r="BJ16" s="32" t="s">
         <v>78</v>
@@ -5203,7 +5136,7 @@
         <v>111</v>
       </c>
       <c r="BL16" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="BM16" s="41" t="s">
         <v>113</v>
@@ -5215,7 +5148,7 @@
         <v>114</v>
       </c>
       <c r="BP16" s="47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BQ16" s="48" t="s">
         <v>116</v>
@@ -6445,7 +6378,7 @@
       <c r="BY31" s="52"/>
       <c r="BZ31" s="52"/>
     </row>
-    <row r="32" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="52"/>
       <c r="B32" s="52"/>
       <c r="C32" s="52"/>
@@ -6525,7 +6458,7 @@
       <c r="BY32" s="52"/>
       <c r="BZ32" s="52"/>
     </row>
-    <row r="33" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="52"/>
       <c r="B33" s="52"/>
       <c r="C33" s="52"/>
@@ -6605,7 +6538,7 @@
       <c r="BY33" s="52"/>
       <c r="BZ33" s="52"/>
     </row>
-    <row r="34" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="52"/>
       <c r="B34" s="52"/>
       <c r="C34" s="52"/>
@@ -6685,7 +6618,7 @@
       <c r="BY34" s="52"/>
       <c r="BZ34" s="52"/>
     </row>
-    <row r="35" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="52"/>
       <c r="B35" s="52"/>
       <c r="C35" s="52"/>
@@ -6765,7 +6698,7 @@
       <c r="BY35" s="52"/>
       <c r="BZ35" s="52"/>
     </row>
-    <row r="36" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="52"/>
       <c r="B36" s="52"/>
       <c r="C36" s="52"/>
@@ -6845,7 +6778,7 @@
       <c r="BY36" s="52"/>
       <c r="BZ36" s="52"/>
     </row>
-    <row r="37" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="52"/>
       <c r="B37" s="52"/>
       <c r="C37" s="52"/>
@@ -6925,7 +6858,7 @@
       <c r="BY37" s="52"/>
       <c r="BZ37" s="52"/>
     </row>
-    <row r="38" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="52"/>
       <c r="B38" s="52"/>
       <c r="C38" s="52"/>
@@ -7005,7 +6938,7 @@
       <c r="BY38" s="52"/>
       <c r="BZ38" s="52"/>
     </row>
-    <row r="39" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="52"/>
       <c r="B39" s="52"/>
       <c r="C39" s="52"/>
@@ -7085,7 +7018,7 @@
       <c r="BY39" s="52"/>
       <c r="BZ39" s="52"/>
     </row>
-    <row r="40" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="52"/>
       <c r="B40" s="52"/>
       <c r="C40" s="52"/>
@@ -7165,7 +7098,7 @@
       <c r="BY40" s="52"/>
       <c r="BZ40" s="52"/>
     </row>
-    <row r="41" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="52"/>
       <c r="B41" s="52"/>
       <c r="C41" s="52"/>
@@ -7245,7 +7178,7 @@
       <c r="BY41" s="52"/>
       <c r="BZ41" s="52"/>
     </row>
-    <row r="42" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="52"/>
       <c r="B42" s="52"/>
       <c r="C42" s="52"/>
@@ -7325,7 +7258,7 @@
       <c r="BY42" s="52"/>
       <c r="BZ42" s="52"/>
     </row>
-    <row r="43" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="52"/>
       <c r="B43" s="52"/>
       <c r="C43" s="52"/>
@@ -7405,7 +7338,7 @@
       <c r="BY43" s="52"/>
       <c r="BZ43" s="52"/>
     </row>
-    <row r="44" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="52"/>
       <c r="B44" s="52"/>
       <c r="C44" s="52"/>
@@ -7485,7 +7418,7 @@
       <c r="BY44" s="52"/>
       <c r="BZ44" s="52"/>
     </row>
-    <row r="45" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="52"/>
       <c r="B45" s="52"/>
       <c r="C45" s="52"/>
@@ -7565,7 +7498,7 @@
       <c r="BY45" s="52"/>
       <c r="BZ45" s="52"/>
     </row>
-    <row r="46" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="52"/>
       <c r="B46" s="52"/>
       <c r="C46" s="52"/>
@@ -7645,7 +7578,7 @@
       <c r="BY46" s="52"/>
       <c r="BZ46" s="52"/>
     </row>
-    <row r="47" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="52"/>
       <c r="B47" s="52"/>
       <c r="C47" s="52"/>
@@ -7725,7 +7658,7 @@
       <c r="BY47" s="52"/>
       <c r="BZ47" s="52"/>
     </row>
-    <row r="48" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="52"/>
       <c r="B48" s="52"/>
       <c r="C48" s="52"/>
@@ -7805,7 +7738,7 @@
       <c r="BY48" s="52"/>
       <c r="BZ48" s="52"/>
     </row>
-    <row r="49" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="52"/>
       <c r="B49" s="52"/>
       <c r="C49" s="52"/>
@@ -7885,7 +7818,7 @@
       <c r="BY49" s="52"/>
       <c r="BZ49" s="52"/>
     </row>
-    <row r="50" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="52"/>
       <c r="B50" s="52"/>
       <c r="C50" s="52"/>
@@ -7965,7 +7898,7 @@
       <c r="BY50" s="52"/>
       <c r="BZ50" s="52"/>
     </row>
-    <row r="51" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="52"/>
       <c r="B51" s="52"/>
       <c r="C51" s="52"/>
@@ -8045,7 +7978,7 @@
       <c r="BY51" s="52"/>
       <c r="BZ51" s="52"/>
     </row>
-    <row r="52" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="52"/>
       <c r="B52" s="52"/>
       <c r="C52" s="52"/>
@@ -8125,7 +8058,7 @@
       <c r="BY52" s="52"/>
       <c r="BZ52" s="52"/>
     </row>
-    <row r="53" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:78" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="52"/>
       <c r="B53" s="52"/>
       <c r="C53" s="52"/>
@@ -8205,7 +8138,7 @@
       <c r="BY53" s="52"/>
       <c r="BZ53" s="52"/>
     </row>
-    <row r="54" spans="1:78" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A54" s="52"/>
       <c r="B54" s="52"/>
       <c r="C54" s="52"/>
@@ -8287,6 +8220,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
@@ -1,38 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{A83A2770-AB94-4A0E-BC19-E25864C4974A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="237">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -262,10 +247,13 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10698150</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t xml:space="preserve">Test failed for 'Erna Smitham' Employee:{undefined}TimeoutError: page.goto: Timeout 30000ms exceeded.
+Call log:
+  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark14/login.htmld", waiting until "load"[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>765 Retail Team 1 (Jizur Buzese (10226524) (Inherited))</t>
@@ -274,10 +262,10 @@
     <t>Poland</t>
   </si>
   <si>
-    <t>PolandOne</t>
-  </si>
-  <si>
-    <t>TwentyFiveMaySeven</t>
+    <t>Erna</t>
+  </si>
+  <si>
+    <t>Smitham</t>
   </si>
   <si>
     <t xml:space="preserve">698 980 460 </t>
@@ -418,401 +406,22 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'PolandTwo TwentyFiveMaySeven' Employee:{10698151}TimeoutError: locator.click: Timeout 30000ms exceeded.
+    <t xml:space="preserve">Test failed for 'Howell Goodwin' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
 Call log:
-  [2m- waiting for locator('button:has-text("Approve")')[22m
-[2m  -   locator resolved to &lt;button type="button" title="Approve" class="WHVM WBCO W…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
+  [2m- waiting for locator('//button/div[@data-automation-id="titleText" and contains (text(),"Poland- National Health Fund Code: Howell Goodwin")]')[22m
 </t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>765 Store Management (Jizur Buzese (10226524))</t>
   </si>
   <si>
-    <t>PolandTwo</t>
-  </si>
-  <si>
-    <t>Auto 30061231</t>
+    <t>Howell</t>
+  </si>
+  <si>
+    <t>Goodwin</t>
+  </si>
+  <si>
+    <t>Auto 68221345</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -839,385 +448,16 @@
     <t>Test_3</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'PolandThree TwentyFiveMaySeven' Employee:{10698152}TimeoutError: locator.click: Timeout 30000ms exceeded.
+    <t xml:space="preserve">Test failed for 'Max Christiansen' Employee:{}TimeoutError: page.goto: Timeout 30000ms exceeded.
 Call log:
-  [2m- waiting for locator('button:has-text("Approve")')[22m
-[2m  -   locator resolved to &lt;button type="button" title="Approve" class="WHVM WBCO W…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
+  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark14/login.htmld", waiting until "load"[22m
 </t>
   </si>
   <si>
-    <t>PolandThree</t>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Christiansen</t>
   </si>
   <si>
     <t>Auto 46032284</t>
@@ -1235,10 +475,16 @@
     <t>Test_4</t>
   </si>
   <si>
-    <t>Test failed for 'PolandFour TwentyFiveMaySeven' Employee:{}TypeError: Cannot read properties of undefined (reading 'toString')</t>
-  </si>
-  <si>
-    <t>PolandFour</t>
+    <t xml:space="preserve">Test failed for 'Bridgette Durgan' Employee:{}TimeoutError: page.goto: Timeout 30000ms exceeded.
+Call log:
+  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark14/login.htmld", waiting until "load"[22m
+</t>
+  </si>
+  <si>
+    <t>Bridgette</t>
+  </si>
+  <si>
+    <t>Durgan</t>
   </si>
   <si>
     <t>Auto 36118310</t>
@@ -1262,15 +508,16 @@
     <t>Test_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'PolandFive TwentyFiveMaySeven' Employee:{10698153}Error: locator.focus: Error: strict mode violation: getByLabel('Country', { exact: true }) resolved to 2 elements:
-    1) &lt;input value="" dir="ltr" tabindex="0" autocomplete="of…/&gt; aka getByRole('row', { name: 'Remove Row Country National ID Type Paboc Wevyge Related Actions Paboc Wevyge' }).getByLabel('Country')
-    2) &lt;input value="" dir="ltr" tabindex="0" autocomplete="of…/&gt; aka getByRole('row', { name: 'Remove Row Country National ID Type 47678965520 07/05/2025 Paboc Wevyge Related' }).getByLabel('Country', { exact: true })
+    <t xml:space="preserve">Test failed for 'Adeline Lockman' Employee:{}TimeoutError: page.goto: Timeout 30000ms exceeded.
 Call log:
-  [2m- waiting for getByLabel('Country', { exact: true })[22m
+  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark14/login.htmld", waiting until "load"[22m
 </t>
   </si>
   <si>
-    <t>PolandFive</t>
+    <t>Adeline</t>
+  </si>
+  <si>
+    <t>Lockman</t>
   </si>
   <si>
     <t>Auto 40540521</t>
@@ -1291,388 +538,19 @@
     <t>Test_6</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'PolandSix TwentyFiveMaySeven' Employee:{10698154}TimeoutError: locator.click: Timeout 30000ms exceeded.
+    <t xml:space="preserve">Test failed for 'Alana Rohan' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
 Call log:
-  [2m- waiting for locator('button:has-text("Approve")')[22m
-[2m  -   locator resolved to &lt;button type="button" title="Approve" class="WHVM WBCO W…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
+  [2m- waiting for locator('//button/div[@data-automation-id="titleText" and contains (text(),"Poland- National Health Fund Code: Alana Rohan")]')[22m
 </t>
   </si>
   <si>
-    <t>PolandSix</t>
-  </si>
-  <si>
-    <t>Auto 39776938</t>
+    <t>Alana</t>
+  </si>
+  <si>
+    <t>Rohan</t>
+  </si>
+  <si>
+    <t>Auto 22206655</t>
   </si>
   <si>
     <t>In-Store Visual Merchandising Manager_NEW</t>
@@ -1690,389 +568,19 @@
     <t>Test_7</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'PolandSeven TwentyFiveMaySeven' Employee:{10698156}TimeoutError: locator.click: Timeout 30000ms exceeded.
+    <t xml:space="preserve">Test failed for 'Althea Littel' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
 Call log:
-  [2m- waiting for locator('button:has-text("Approve")')[22m
-[2m  -   locator resolved to &lt;button type="button" title="Approve" class="WHVM WBCO W…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
+  [2m- waiting for getByLabel('Urząd Skarbowy')[22m
 </t>
   </si>
   <si>
-    <t>PolandSeven</t>
-  </si>
-  <si>
-    <t>Auto 10948314</t>
+    <t>Althea</t>
+  </si>
+  <si>
+    <t>Littel</t>
+  </si>
+  <si>
+    <t>Auto 72832074</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -2084,10 +592,16 @@
     <t>Test_8</t>
   </si>
   <si>
-    <t>10698157</t>
-  </si>
-  <si>
-    <t>PolandEight</t>
+    <t xml:space="preserve">Test failed for 'Harley Heidenreich-Tremblay' Employee:{}TimeoutError: page.goto: Timeout 30000ms exceeded.
+Call log:
+  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark14/login.htmld", waiting until "load"[22m
+</t>
+  </si>
+  <si>
+    <t>Harley</t>
+  </si>
+  <si>
+    <t>Heidenreich-Tremblay</t>
   </si>
   <si>
     <t>In-Store P&amp;C Supervisor_NEW</t>
@@ -2105,10 +619,16 @@
     <t>Test_9</t>
   </si>
   <si>
-    <t>10698158</t>
-  </si>
-  <si>
-    <t>PolandNine</t>
+    <t xml:space="preserve">Test failed for 'Terrill Lebsack' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//button/div[@data-automation-id="titleText" and contains (text(),"Poland- National Health Fund Code: Terrill Lebsack")]')[22m
+</t>
+  </si>
+  <si>
+    <t>Terrill</t>
+  </si>
+  <si>
+    <t>Lebsack</t>
   </si>
   <si>
     <t>Retail Assistant Cash Office_NEW</t>
@@ -2123,10 +643,16 @@
     <t>Test_10</t>
   </si>
   <si>
-    <t>10698159</t>
-  </si>
-  <si>
-    <t>PolandTen</t>
+    <t xml:space="preserve">Test failed for 'Maryse McGlynn' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//button/div[@data-automation-id="titleText" and contains (text(),"Poland- National Health Fund Code: Maryse McGlynn")]')[22m
+</t>
+  </si>
+  <si>
+    <t>Maryse</t>
+  </si>
+  <si>
+    <t>McGlynn</t>
   </si>
   <si>
     <t>In-Store P&amp;C Assistant_NEW</t>
@@ -2141,10 +667,16 @@
     <t>Test_11</t>
   </si>
   <si>
-    <t>10698160</t>
-  </si>
-  <si>
-    <t>PolandEleven</t>
+    <t xml:space="preserve">Test failed for 'Kiana Koss' Employee:{}TimeoutError: page.goto: Timeout 30000ms exceeded.
+Call log:
+  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark14/login.htmld", waiting until "load"[22m
+</t>
+  </si>
+  <si>
+    <t>Kiana</t>
+  </si>
+  <si>
+    <t>Koss</t>
   </si>
   <si>
     <t>Supervisor_NEW</t>
@@ -2162,10 +694,16 @@
     <t>Test_12</t>
   </si>
   <si>
-    <t>10698161</t>
-  </si>
-  <si>
-    <t>PolandTwleve</t>
+    <t xml:space="preserve">Test failed for 'Molly Langosh' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Urząd Skarbowy')[22m
+</t>
+  </si>
+  <si>
+    <t>Molly</t>
+  </si>
+  <si>
+    <t>Langosh</t>
   </si>
   <si>
     <t>In-Store Visual Merchandising Assistant_NEW</t>
@@ -2183,10 +721,16 @@
     <t>Test_13</t>
   </si>
   <si>
-    <t>10698162</t>
-  </si>
-  <si>
-    <t>PolandThirteen</t>
+    <t xml:space="preserve">Test failed for 'Jewel Armstrong' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//button/div[@data-automation-id="titleText" and contains (text(),"Poland- National Health Fund Code: Jewel Armstrong")]')[22m
+</t>
+  </si>
+  <si>
+    <t>Jewel</t>
+  </si>
+  <si>
+    <t>Armstrong</t>
   </si>
   <si>
     <t>RE043_NEW</t>
@@ -2198,10 +742,16 @@
     <t>Test_14</t>
   </si>
   <si>
-    <t>10698163</t>
-  </si>
-  <si>
-    <t>PolandFourteen</t>
+    <t xml:space="preserve">Test failed for 'Marlee Ruecker' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Urząd Skarbowy')[22m
+</t>
+  </si>
+  <si>
+    <t>Marlee</t>
+  </si>
+  <si>
+    <t>Ruecker</t>
   </si>
   <si>
     <t>GHE456309</t>
@@ -2210,10 +760,16 @@
     <t>Test_15</t>
   </si>
   <si>
-    <t>10698164</t>
-  </si>
-  <si>
-    <t>PolandFifteen</t>
+    <t xml:space="preserve">Test failed for 'Jacinthe Rau' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//button/div[@data-automation-id="titleText" and contains (text(),"Poland- National Health Fund Code: Jacinthe Rau")]')[22m
+</t>
+  </si>
+  <si>
+    <t>Jacinthe</t>
+  </si>
+  <si>
+    <t>Rau</t>
   </si>
   <si>
     <t>GHE456310</t>
@@ -2222,148 +778,148 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="63"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="10"/>
       <color indexed="12"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="10"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
+      <scheme val="major"/>
       <sz val="10"/>
       <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color indexed="63"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color indexed="12"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="63"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2395,12 +951,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2414,15 +965,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -2433,25 +978,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -2531,7 +1066,7 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2540,7 +1075,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2878,9 +1413,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
     <col min="2" max="2" width="11.109375" customWidth="1"/>
@@ -2962,7 +1497,7 @@
     <col min="78" max="78" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="14.4" customHeight="1" spans="1:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3198,7 +1733,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>75</v>
       </c>
@@ -3230,7 +1765,7 @@
         <v>84</v>
       </c>
       <c r="K2" s="35">
-        <f t="shared" ref="K2:K16" ca="1" si="0">TODAY()-31</f>
+        <f t="shared" ref="K2:K16" si="0">TODAY()-31</f>
         <v>45753</v>
       </c>
       <c r="L2" s="30" t="s">
@@ -3270,7 +1805,7 @@
         <v>84</v>
       </c>
       <c r="X2" s="38">
-        <f t="shared" ref="X2:X16" ca="1" si="1">K2</f>
+        <f t="shared" ref="X2:X16" si="1">K2</f>
         <v>45753</v>
       </c>
       <c r="Y2" s="34" t="s">
@@ -3331,16 +1866,16 @@
         <v>102</v>
       </c>
       <c r="AR2" s="42">
-        <f t="shared" ref="AR2:AR16" ca="1" si="2">X2</f>
+        <f t="shared" ref="AR2:AR16" si="2">X2</f>
         <v>45753</v>
       </c>
       <c r="AS2" s="42">
-        <f t="shared" ref="AS2:AS16" ca="1" si="3">X2</f>
+        <f t="shared" ref="AS2:AS16" si="3">X2</f>
         <v>45753</v>
       </c>
-      <c r="AT2" s="38" t="str">
+      <c r="AT2" s="38">
         <f t="shared" ref="AT2:AT16" si="4">AM2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU2" s="34" t="s">
         <v>103</v>
@@ -3439,7 +1974,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>127</v>
       </c>
@@ -3447,19 +1982,19 @@
         <v>128</v>
       </c>
       <c r="C3" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E3" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F3" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="32" t="s">
         <v>131</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>81</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>82</v>
@@ -3471,7 +2006,7 @@
         <v>84</v>
       </c>
       <c r="K3" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L3" s="30" t="s">
@@ -3511,7 +2046,7 @@
         <v>84</v>
       </c>
       <c r="X3" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y3" s="34" t="s">
@@ -3572,16 +2107,16 @@
         <v>102</v>
       </c>
       <c r="AR3" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS3" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
-      <c r="AT3" s="38" t="str">
+      <c r="AT3" s="38">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU3" s="34" t="s">
         <v>135</v>
@@ -3680,7 +2215,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
         <v>140</v>
       </c>
@@ -3688,10 +2223,10 @@
         <v>141</v>
       </c>
       <c r="C4" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>79</v>
@@ -3700,7 +2235,7 @@
         <v>142</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>82</v>
@@ -3712,7 +2247,7 @@
         <v>84</v>
       </c>
       <c r="K4" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L4" s="30" t="s">
@@ -3752,20 +2287,20 @@
         <v>84</v>
       </c>
       <c r="X4" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y4" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z4" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AA4" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB4" s="40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AC4" s="39" t="s">
         <v>95</v>
@@ -3813,16 +2348,16 @@
         <v>102</v>
       </c>
       <c r="AR4" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS4" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
-      <c r="AT4" s="38" t="str">
+      <c r="AT4" s="38">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU4" s="34" t="s">
         <v>135</v>
@@ -3876,7 +2411,7 @@
         <v>112</v>
       </c>
       <c r="BL4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BM4" s="39" t="s">
         <v>114</v>
@@ -3888,7 +2423,7 @@
         <v>115</v>
       </c>
       <c r="BP4" s="45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BQ4" s="46" t="s">
         <v>117</v>
@@ -3921,27 +2456,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C5" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>82</v>
@@ -3953,7 +2488,7 @@
         <v>84</v>
       </c>
       <c r="K5" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L5" s="30" t="s">
@@ -3993,23 +2528,23 @@
         <v>84</v>
       </c>
       <c r="X5" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y5" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z5" s="34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AA5" s="30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AB5" s="40" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AC5" s="39" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AD5" s="30">
         <v>765</v>
@@ -4033,13 +2568,13 @@
         <v>45293</v>
       </c>
       <c r="AK5" s="39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL5" s="39" t="s">
         <v>98</v>
       </c>
       <c r="AM5" s="41">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46149</v>
       </c>
       <c r="AN5" s="30">
@@ -4055,11 +2590,11 @@
         <v>102</v>
       </c>
       <c r="AR5" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS5" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
       <c r="AT5" s="38" t="s">
@@ -4117,7 +2652,7 @@
         <v>112</v>
       </c>
       <c r="BL5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BM5" s="39" t="s">
         <v>138</v>
@@ -4162,27 +2697,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C6" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>82</v>
@@ -4194,7 +2729,7 @@
         <v>84</v>
       </c>
       <c r="K6" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L6" s="30" t="s">
@@ -4234,20 +2769,20 @@
         <v>84</v>
       </c>
       <c r="X6" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y6" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z6" s="34" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AA6" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB6" s="40" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AC6" s="39" t="s">
         <v>95</v>
@@ -4274,7 +2809,7 @@
         <v>45293</v>
       </c>
       <c r="AK6" s="39" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AL6" s="39" t="s">
         <v>98</v>
@@ -4295,16 +2830,16 @@
         <v>102</v>
       </c>
       <c r="AR6" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS6" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
-      <c r="AT6" s="38" t="str">
+      <c r="AT6" s="38">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU6" s="34" t="s">
         <v>135</v>
@@ -4358,7 +2893,7 @@
         <v>112</v>
       </c>
       <c r="BL6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BM6" s="39" t="s">
         <v>114</v>
@@ -4370,7 +2905,7 @@
         <v>115</v>
       </c>
       <c r="BP6" s="45" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="BQ6" s="46" t="s">
         <v>117</v>
@@ -4403,27 +2938,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="43" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C7" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E7" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>82</v>
@@ -4435,7 +2970,7 @@
         <v>84</v>
       </c>
       <c r="K7" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L7" s="30" t="s">
@@ -4475,23 +3010,23 @@
         <v>84</v>
       </c>
       <c r="X7" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y7" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z7" s="34" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AA7" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB7" s="40" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="AC7" s="39" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AD7" s="30">
         <v>765</v>
@@ -4515,7 +3050,7 @@
         <v>45293</v>
       </c>
       <c r="AK7" s="39" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AL7" s="39" t="s">
         <v>98</v>
@@ -4536,16 +3071,16 @@
         <v>102</v>
       </c>
       <c r="AR7" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS7" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
-      <c r="AT7" s="38" t="str">
+      <c r="AT7" s="38">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU7" s="34" t="s">
         <v>135</v>
@@ -4569,7 +3104,7 @@
         <v>109</v>
       </c>
       <c r="BB7" s="30" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="BC7" s="35">
         <v>46022</v>
@@ -4599,7 +3134,7 @@
         <v>112</v>
       </c>
       <c r="BL7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="BM7" s="39" t="s">
         <v>138</v>
@@ -4644,27 +3179,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="43" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C8" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>82</v>
@@ -4676,7 +3211,7 @@
         <v>84</v>
       </c>
       <c r="K8" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L8" s="30" t="s">
@@ -4716,20 +3251,20 @@
         <v>84</v>
       </c>
       <c r="X8" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y8" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z8" s="34" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AB8" s="40" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AC8" s="39" t="s">
         <v>95</v>
@@ -4762,7 +3297,7 @@
         <v>98</v>
       </c>
       <c r="AM8" s="41">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46149</v>
       </c>
       <c r="AN8" s="30">
@@ -4778,11 +3313,11 @@
         <v>102</v>
       </c>
       <c r="AR8" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS8" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
       <c r="AT8" s="38" t="s">
@@ -4840,7 +3375,7 @@
         <v>112</v>
       </c>
       <c r="BL8" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="BM8" s="39" t="s">
         <v>114</v>
@@ -4852,7 +3387,7 @@
         <v>115</v>
       </c>
       <c r="BP8" s="45" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="BQ8" s="46" t="s">
         <v>117</v>
@@ -4885,12 +3420,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="43" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>77</v>
@@ -4902,10 +3437,10 @@
         <v>79</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>82</v>
@@ -4917,7 +3452,7 @@
         <v>84</v>
       </c>
       <c r="K9" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L9" s="30" t="s">
@@ -4957,7 +3492,7 @@
         <v>84</v>
       </c>
       <c r="X9" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y9" s="34" t="s">
@@ -4970,7 +3505,7 @@
         <v>90</v>
       </c>
       <c r="AB9" s="40" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="AC9" s="39" t="s">
         <v>95</v>
@@ -4997,7 +3532,7 @@
         <v>45293</v>
       </c>
       <c r="AK9" s="39" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="AL9" s="39" t="s">
         <v>98</v>
@@ -5018,22 +3553,22 @@
         <v>102</v>
       </c>
       <c r="AR9" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS9" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
-      <c r="AT9" s="38" t="str">
+      <c r="AT9" s="38">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU9" s="34" t="s">
         <v>103</v>
       </c>
       <c r="AV9" s="43" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AW9" s="30" t="s">
         <v>105</v>
@@ -5081,7 +3616,7 @@
         <v>112</v>
       </c>
       <c r="BL9" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="BM9" s="39" t="s">
         <v>138</v>
@@ -5126,12 +3661,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>77</v>
@@ -5143,10 +3678,10 @@
         <v>79</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>82</v>
@@ -5158,7 +3693,7 @@
         <v>84</v>
       </c>
       <c r="K10" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L10" s="30" t="s">
@@ -5198,7 +3733,7 @@
         <v>84</v>
       </c>
       <c r="X10" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y10" s="34" t="s">
@@ -5211,10 +3746,10 @@
         <v>90</v>
       </c>
       <c r="AB10" s="40" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="AC10" s="39" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AD10" s="30">
         <v>765</v>
@@ -5259,22 +3794,22 @@
         <v>102</v>
       </c>
       <c r="AR10" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS10" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
-      <c r="AT10" s="38" t="str">
+      <c r="AT10" s="38">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU10" s="34" t="s">
         <v>103</v>
       </c>
       <c r="AV10" s="43" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="AW10" s="30" t="s">
         <v>105</v>
@@ -5322,7 +3857,7 @@
         <v>112</v>
       </c>
       <c r="BL10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="BM10" s="39" t="s">
         <v>114</v>
@@ -5334,7 +3869,7 @@
         <v>115</v>
       </c>
       <c r="BP10" s="45" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="BQ10" s="46" t="s">
         <v>117</v>
@@ -5367,12 +3902,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="43" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>77</v>
@@ -5384,10 +3919,10 @@
         <v>79</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>82</v>
@@ -5399,7 +3934,7 @@
         <v>84</v>
       </c>
       <c r="K11" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L11" s="30" t="s">
@@ -5439,7 +3974,7 @@
         <v>84</v>
       </c>
       <c r="X11" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y11" s="34" t="s">
@@ -5449,10 +3984,10 @@
         <v>93</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AB11" s="40" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AC11" s="39" t="s">
         <v>95</v>
@@ -5485,7 +4020,7 @@
         <v>98</v>
       </c>
       <c r="AM11" s="41">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46149</v>
       </c>
       <c r="AN11" s="30">
@@ -5495,28 +4030,28 @@
         <v>100</v>
       </c>
       <c r="AP11" s="34" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AQ11" s="34" t="s">
         <v>102</v>
       </c>
       <c r="AR11" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS11" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
       <c r="AT11" s="38">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>46149</v>
       </c>
       <c r="AU11" s="34" t="s">
         <v>103</v>
       </c>
       <c r="AV11" s="43" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AW11" s="30" t="s">
         <v>105</v>
@@ -5564,7 +4099,7 @@
         <v>112</v>
       </c>
       <c r="BL11" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="BM11" s="39" t="s">
         <v>138</v>
@@ -5609,12 +4144,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="43" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>77</v>
@@ -5626,10 +4161,10 @@
         <v>79</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="H12" s="33" t="s">
         <v>82</v>
@@ -5641,7 +4176,7 @@
         <v>84</v>
       </c>
       <c r="K12" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L12" s="30" t="s">
@@ -5681,7 +4216,7 @@
         <v>84</v>
       </c>
       <c r="X12" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y12" s="34" t="s">
@@ -5694,10 +4229,10 @@
         <v>90</v>
       </c>
       <c r="AB12" s="40" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AC12" s="39" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AD12" s="30">
         <v>765</v>
@@ -5721,7 +4256,7 @@
         <v>45293</v>
       </c>
       <c r="AK12" s="39" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="AL12" s="39" t="s">
         <v>98</v>
@@ -5742,22 +4277,22 @@
         <v>102</v>
       </c>
       <c r="AR12" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS12" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
-      <c r="AT12" s="38" t="str">
+      <c r="AT12" s="38">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU12" s="34" t="s">
         <v>103</v>
       </c>
       <c r="AV12" s="43" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AW12" s="30" t="s">
         <v>105</v>
@@ -5805,7 +4340,7 @@
         <v>112</v>
       </c>
       <c r="BL12" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="BM12" s="39" t="s">
         <v>114</v>
@@ -5817,7 +4352,7 @@
         <v>115</v>
       </c>
       <c r="BP12" s="45" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="BQ12" s="46" t="s">
         <v>117</v>
@@ -5850,12 +4385,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="43" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>77</v>
@@ -5867,10 +4402,10 @@
         <v>79</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G13" s="32" t="s">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>82</v>
@@ -5882,7 +4417,7 @@
         <v>84</v>
       </c>
       <c r="K13" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L13" s="30" t="s">
@@ -5922,7 +4457,7 @@
         <v>84</v>
       </c>
       <c r="X13" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y13" s="34" t="s">
@@ -5935,7 +4470,7 @@
         <v>90</v>
       </c>
       <c r="AB13" s="40" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="AC13" s="39" t="s">
         <v>95</v>
@@ -5962,7 +4497,7 @@
         <v>45293</v>
       </c>
       <c r="AK13" s="39" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="AL13" s="39" t="s">
         <v>98</v>
@@ -5983,22 +4518,22 @@
         <v>102</v>
       </c>
       <c r="AR13" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS13" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
-      <c r="AT13" s="38" t="str">
+      <c r="AT13" s="38">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU13" s="34" t="s">
         <v>103</v>
       </c>
       <c r="AV13" s="43" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="AW13" s="30" t="s">
         <v>105</v>
@@ -6046,7 +4581,7 @@
         <v>112</v>
       </c>
       <c r="BL13" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="BM13" s="39" t="s">
         <v>138</v>
@@ -6091,12 +4626,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="43" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>77</v>
@@ -6108,10 +4643,10 @@
         <v>79</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G14" s="32" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="H14" s="33" t="s">
         <v>82</v>
@@ -6123,7 +4658,7 @@
         <v>84</v>
       </c>
       <c r="K14" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L14" s="30" t="s">
@@ -6163,7 +4698,7 @@
         <v>84</v>
       </c>
       <c r="X14" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y14" s="34" t="s">
@@ -6173,13 +4708,13 @@
         <v>93</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AB14" s="40" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AC14" s="39" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AD14" s="30">
         <v>765</v>
@@ -6203,13 +4738,13 @@
         <v>45293</v>
       </c>
       <c r="AK14" s="39" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="AL14" s="39" t="s">
         <v>98</v>
       </c>
       <c r="AM14" s="41">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46149</v>
       </c>
       <c r="AN14" s="30">
@@ -6225,11 +4760,11 @@
         <v>102</v>
       </c>
       <c r="AR14" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS14" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
       <c r="AT14" s="38" t="s">
@@ -6239,7 +4774,7 @@
         <v>103</v>
       </c>
       <c r="AV14" s="43" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AW14" s="30" t="s">
         <v>105</v>
@@ -6257,7 +4792,7 @@
         <v>109</v>
       </c>
       <c r="BB14" s="30" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="BC14" s="35">
         <v>46022</v>
@@ -6287,7 +4822,7 @@
         <v>112</v>
       </c>
       <c r="BL14" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="BM14" s="39" t="s">
         <v>114</v>
@@ -6299,7 +4834,7 @@
         <v>115</v>
       </c>
       <c r="BP14" s="45" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="BQ14" s="46" t="s">
         <v>117</v>
@@ -6332,12 +4867,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="43" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C15" s="28" t="s">
         <v>77</v>
@@ -6349,10 +4884,10 @@
         <v>79</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="H15" s="33" t="s">
         <v>82</v>
@@ -6364,7 +4899,7 @@
         <v>84</v>
       </c>
       <c r="K15" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L15" s="30" t="s">
@@ -6404,7 +4939,7 @@
         <v>84</v>
       </c>
       <c r="X15" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y15" s="34" t="s">
@@ -6414,13 +4949,13 @@
         <v>93</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AB15" s="40" t="s">
         <v>94</v>
       </c>
       <c r="AC15" s="39" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AD15" s="30">
         <v>765</v>
@@ -6450,7 +4985,7 @@
         <v>98</v>
       </c>
       <c r="AM15" s="41">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46149</v>
       </c>
       <c r="AN15" s="30">
@@ -6460,21 +4995,21 @@
         <v>100</v>
       </c>
       <c r="AP15" s="39" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AQ15" s="34" t="s">
         <v>102</v>
       </c>
       <c r="AR15" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS15" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
       <c r="AT15" s="38">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>46149</v>
       </c>
       <c r="AU15" s="34" t="s">
@@ -6529,7 +5064,7 @@
         <v>112</v>
       </c>
       <c r="BL15" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="BM15" s="39" t="s">
         <v>138</v>
@@ -6574,12 +5109,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="43" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>77</v>
@@ -6591,10 +5126,10 @@
         <v>79</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="H16" s="33" t="s">
         <v>82</v>
@@ -6606,7 +5141,7 @@
         <v>84</v>
       </c>
       <c r="K16" s="35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45753</v>
       </c>
       <c r="L16" s="30" t="s">
@@ -6646,7 +5181,7 @@
         <v>84</v>
       </c>
       <c r="X16" s="38">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45753</v>
       </c>
       <c r="Y16" s="34" t="s">
@@ -6707,16 +5242,16 @@
         <v>102</v>
       </c>
       <c r="AR16" s="42">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45753</v>
       </c>
       <c r="AS16" s="42">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45753</v>
       </c>
-      <c r="AT16" s="38" t="str">
+      <c r="AT16" s="38">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU16" s="34" t="s">
         <v>103</v>
@@ -6740,7 +5275,7 @@
         <v>109</v>
       </c>
       <c r="BB16" s="30" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="BC16" s="35">
         <v>46022</v>
@@ -6770,7 +5305,7 @@
         <v>112</v>
       </c>
       <c r="BL16" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="BM16" s="39" t="s">
         <v>114</v>
@@ -6782,7 +5317,7 @@
         <v>115</v>
       </c>
       <c r="BP16" s="45" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="BQ16" s="46" t="s">
         <v>117</v>
@@ -8015,7 +6550,7 @@
       <c r="BY31" s="48"/>
       <c r="BZ31" s="48"/>
     </row>
-    <row r="32" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="48"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
@@ -8095,7 +6630,7 @@
       <c r="BY32" s="48"/>
       <c r="BZ32" s="48"/>
     </row>
-    <row r="33" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="48"/>
       <c r="B33" s="48"/>
       <c r="C33" s="48"/>
@@ -8175,7 +6710,7 @@
       <c r="BY33" s="48"/>
       <c r="BZ33" s="48"/>
     </row>
-    <row r="34" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="48"/>
       <c r="B34" s="48"/>
       <c r="C34" s="48"/>
@@ -8255,7 +6790,7 @@
       <c r="BY34" s="48"/>
       <c r="BZ34" s="48"/>
     </row>
-    <row r="35" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="48"/>
       <c r="B35" s="48"/>
       <c r="C35" s="48"/>
@@ -8335,7 +6870,7 @@
       <c r="BY35" s="48"/>
       <c r="BZ35" s="48"/>
     </row>
-    <row r="36" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="48"/>
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
@@ -8415,7 +6950,7 @@
       <c r="BY36" s="48"/>
       <c r="BZ36" s="48"/>
     </row>
-    <row r="37" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="48"/>
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
@@ -8495,7 +7030,7 @@
       <c r="BY37" s="48"/>
       <c r="BZ37" s="48"/>
     </row>
-    <row r="38" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="48"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
@@ -8575,7 +7110,7 @@
       <c r="BY38" s="48"/>
       <c r="BZ38" s="48"/>
     </row>
-    <row r="39" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="48"/>
       <c r="B39" s="48"/>
       <c r="C39" s="48"/>
@@ -8655,7 +7190,7 @@
       <c r="BY39" s="48"/>
       <c r="BZ39" s="48"/>
     </row>
-    <row r="40" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="48"/>
       <c r="B40" s="48"/>
       <c r="C40" s="48"/>
@@ -8735,7 +7270,7 @@
       <c r="BY40" s="48"/>
       <c r="BZ40" s="48"/>
     </row>
-    <row r="41" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="48"/>
       <c r="B41" s="48"/>
       <c r="C41" s="48"/>
@@ -8815,7 +7350,7 @@
       <c r="BY41" s="48"/>
       <c r="BZ41" s="48"/>
     </row>
-    <row r="42" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="48"/>
       <c r="B42" s="48"/>
       <c r="C42" s="48"/>
@@ -8895,7 +7430,7 @@
       <c r="BY42" s="48"/>
       <c r="BZ42" s="48"/>
     </row>
-    <row r="43" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="48"/>
       <c r="B43" s="48"/>
       <c r="C43" s="48"/>
@@ -8975,7 +7510,7 @@
       <c r="BY43" s="48"/>
       <c r="BZ43" s="48"/>
     </row>
-    <row r="44" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="48"/>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
@@ -9055,7 +7590,7 @@
       <c r="BY44" s="48"/>
       <c r="BZ44" s="48"/>
     </row>
-    <row r="45" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="48"/>
       <c r="B45" s="48"/>
       <c r="C45" s="48"/>
@@ -9135,7 +7670,7 @@
       <c r="BY45" s="48"/>
       <c r="BZ45" s="48"/>
     </row>
-    <row r="46" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="48"/>
       <c r="B46" s="48"/>
       <c r="C46" s="48"/>
@@ -9215,7 +7750,7 @@
       <c r="BY46" s="48"/>
       <c r="BZ46" s="48"/>
     </row>
-    <row r="47" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="48"/>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
@@ -9295,7 +7830,7 @@
       <c r="BY47" s="48"/>
       <c r="BZ47" s="48"/>
     </row>
-    <row r="48" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="48"/>
       <c r="B48" s="48"/>
       <c r="C48" s="48"/>
@@ -9375,7 +7910,7 @@
       <c r="BY48" s="48"/>
       <c r="BZ48" s="48"/>
     </row>
-    <row r="49" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="48"/>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
@@ -9455,7 +7990,7 @@
       <c r="BY49" s="48"/>
       <c r="BZ49" s="48"/>
     </row>
-    <row r="50" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="48"/>
       <c r="B50" s="48"/>
       <c r="C50" s="48"/>
@@ -9535,7 +8070,7 @@
       <c r="BY50" s="48"/>
       <c r="BZ50" s="48"/>
     </row>
-    <row r="51" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="48"/>
       <c r="B51" s="48"/>
       <c r="C51" s="48"/>
@@ -9615,7 +8150,7 @@
       <c r="BY51" s="48"/>
       <c r="BZ51" s="48"/>
     </row>
-    <row r="52" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="48"/>
       <c r="B52" s="48"/>
       <c r="C52" s="48"/>
@@ -9695,7 +8230,7 @@
       <c r="BY52" s="48"/>
       <c r="BZ52" s="48"/>
     </row>
-    <row r="53" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="48"/>
       <c r="B53" s="48"/>
       <c r="C53" s="48"/>
@@ -9775,7 +8310,7 @@
       <c r="BY53" s="48"/>
       <c r="BZ53" s="48"/>
     </row>
-    <row r="54" spans="1:78" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A54" s="48"/>
       <c r="B54" s="48"/>
       <c r="C54" s="48"/>
@@ -9857,6 +8392,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{A83A2770-AB94-4A0E-BC19-E25864C4974A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22CC513-C650-49B9-AFD1-866317F01AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,6 @@
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="223">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -801,9 +800,6 @@
 [2m  - retrying click action, attempt #54[22m
 [2m  -   waiting 500ms[22m
 </t>
-  </si>
-  <si>
-    <t>Failed</t>
   </si>
   <si>
     <t>765 Store Management (Jizur Buzese (10226524))</t>
@@ -2880,89 +2876,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" customWidth="1"/>
-    <col min="4" max="4" width="41.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" customWidth="1"/>
+    <col min="4" max="4" width="41.453125" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="5.6328125" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" customWidth="1"/>
-    <col min="18" max="18" width="11.88671875" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="20.6328125" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" customWidth="1"/>
+    <col min="15" max="15" width="10.81640625" customWidth="1"/>
+    <col min="16" max="16" width="8.08984375" customWidth="1"/>
+    <col min="17" max="17" width="13.1796875" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" customWidth="1"/>
+    <col min="19" max="19" width="8.08984375" customWidth="1"/>
+    <col min="20" max="20" width="5.6328125" customWidth="1"/>
+    <col min="21" max="21" width="12.36328125" customWidth="1"/>
     <col min="22" max="22" width="17" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" customWidth="1"/>
-    <col min="24" max="24" width="10.5546875" customWidth="1"/>
-    <col min="25" max="25" width="8.109375" customWidth="1"/>
-    <col min="26" max="26" width="23.109375" customWidth="1"/>
-    <col min="27" max="27" width="19.6640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6328125" customWidth="1"/>
+    <col min="24" max="24" width="10.54296875" customWidth="1"/>
+    <col min="25" max="25" width="8.08984375" customWidth="1"/>
+    <col min="26" max="26" width="23.08984375" customWidth="1"/>
+    <col min="27" max="27" width="19.6328125" style="1" customWidth="1"/>
     <col min="28" max="28" width="37" customWidth="1"/>
-    <col min="29" max="29" width="9.21875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="8.44140625" customWidth="1"/>
-    <col min="31" max="31" width="12.109375" customWidth="1"/>
-    <col min="32" max="32" width="21.77734375" customWidth="1"/>
-    <col min="33" max="33" width="11.6640625" customWidth="1"/>
-    <col min="34" max="34" width="22.88671875" customWidth="1"/>
-    <col min="35" max="35" width="15.21875" customWidth="1"/>
-    <col min="36" max="36" width="14.109375" customWidth="1"/>
+    <col min="29" max="29" width="9.1796875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="8.453125" customWidth="1"/>
+    <col min="31" max="31" width="12.08984375" customWidth="1"/>
+    <col min="32" max="32" width="21.81640625" customWidth="1"/>
+    <col min="33" max="33" width="11.6328125" customWidth="1"/>
+    <col min="34" max="34" width="22.90625" customWidth="1"/>
+    <col min="35" max="35" width="15.1796875" customWidth="1"/>
+    <col min="36" max="36" width="14.08984375" customWidth="1"/>
     <col min="37" max="37" width="26" customWidth="1"/>
-    <col min="38" max="38" width="13.109375" style="1" customWidth="1"/>
-    <col min="39" max="39" width="19.21875" customWidth="1"/>
-    <col min="40" max="40" width="16.88671875" customWidth="1"/>
-    <col min="41" max="41" width="25.21875" customWidth="1"/>
-    <col min="42" max="42" width="12.6640625" customWidth="1"/>
-    <col min="43" max="43" width="6.5546875" customWidth="1"/>
-    <col min="44" max="44" width="19.33203125" customWidth="1"/>
-    <col min="45" max="45" width="19.109375" customWidth="1"/>
-    <col min="46" max="46" width="15.88671875" customWidth="1"/>
-    <col min="47" max="47" width="19.21875" customWidth="1"/>
-    <col min="48" max="48" width="23.44140625" customWidth="1"/>
-    <col min="49" max="49" width="14.6640625" customWidth="1"/>
-    <col min="50" max="50" width="23.109375" customWidth="1"/>
-    <col min="51" max="51" width="28.6640625" customWidth="1"/>
-    <col min="52" max="52" width="17.77734375" customWidth="1"/>
-    <col min="53" max="53" width="22.44140625" customWidth="1"/>
-    <col min="54" max="54" width="17.77734375" customWidth="1"/>
+    <col min="38" max="38" width="13.08984375" style="1" customWidth="1"/>
+    <col min="39" max="39" width="19.1796875" customWidth="1"/>
+    <col min="40" max="40" width="16.90625" customWidth="1"/>
+    <col min="41" max="41" width="25.1796875" customWidth="1"/>
+    <col min="42" max="42" width="12.6328125" customWidth="1"/>
+    <col min="43" max="43" width="6.54296875" customWidth="1"/>
+    <col min="44" max="44" width="19.36328125" customWidth="1"/>
+    <col min="45" max="45" width="19.08984375" customWidth="1"/>
+    <col min="46" max="46" width="15.90625" customWidth="1"/>
+    <col min="47" max="47" width="19.1796875" customWidth="1"/>
+    <col min="48" max="48" width="23.453125" customWidth="1"/>
+    <col min="49" max="49" width="14.6328125" customWidth="1"/>
+    <col min="50" max="50" width="23.08984375" customWidth="1"/>
+    <col min="51" max="51" width="28.6328125" customWidth="1"/>
+    <col min="52" max="52" width="17.81640625" customWidth="1"/>
+    <col min="53" max="53" width="22.453125" customWidth="1"/>
+    <col min="54" max="54" width="17.81640625" customWidth="1"/>
     <col min="55" max="55" width="18" customWidth="1"/>
-    <col min="56" max="56" width="9.109375" customWidth="1"/>
-    <col min="57" max="57" width="15.5546875" customWidth="1"/>
+    <col min="56" max="56" width="9.08984375" customWidth="1"/>
+    <col min="57" max="57" width="15.54296875" customWidth="1"/>
     <col min="58" max="58" width="12" customWidth="1"/>
-    <col min="59" max="59" width="9.109375" customWidth="1"/>
-    <col min="60" max="60" width="27.33203125" customWidth="1"/>
+    <col min="59" max="59" width="9.08984375" customWidth="1"/>
+    <col min="60" max="60" width="27.36328125" customWidth="1"/>
     <col min="61" max="61" width="12" customWidth="1"/>
-    <col min="62" max="62" width="9.109375" customWidth="1"/>
-    <col min="63" max="63" width="15.5546875" customWidth="1"/>
-    <col min="64" max="64" width="10.77734375" customWidth="1"/>
-    <col min="65" max="65" width="7.33203125" customWidth="1"/>
-    <col min="66" max="66" width="11.33203125" customWidth="1"/>
-    <col min="67" max="67" width="14.21875" customWidth="1"/>
+    <col min="62" max="62" width="9.08984375" customWidth="1"/>
+    <col min="63" max="63" width="15.54296875" customWidth="1"/>
+    <col min="64" max="64" width="10.81640625" customWidth="1"/>
+    <col min="65" max="65" width="7.36328125" customWidth="1"/>
+    <col min="66" max="66" width="11.36328125" customWidth="1"/>
+    <col min="67" max="67" width="14.1796875" customWidth="1"/>
     <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="16.33203125" customWidth="1"/>
-    <col min="70" max="70" width="12.5546875" customWidth="1"/>
-    <col min="71" max="71" width="21.6640625" customWidth="1"/>
-    <col min="72" max="72" width="12.21875" customWidth="1"/>
-    <col min="73" max="73" width="27.44140625" customWidth="1"/>
-    <col min="74" max="74" width="29.21875" customWidth="1"/>
-    <col min="75" max="75" width="8.44140625" customWidth="1"/>
-    <col min="76" max="76" width="26.88671875" customWidth="1"/>
-    <col min="77" max="77" width="22.33203125" customWidth="1"/>
-    <col min="78" max="78" width="23.21875" customWidth="1"/>
+    <col min="69" max="69" width="16.36328125" customWidth="1"/>
+    <col min="70" max="70" width="12.54296875" customWidth="1"/>
+    <col min="71" max="71" width="21.6328125" customWidth="1"/>
+    <col min="72" max="72" width="12.1796875" customWidth="1"/>
+    <col min="73" max="73" width="27.453125" customWidth="1"/>
+    <col min="74" max="74" width="29.1796875" customWidth="1"/>
+    <col min="75" max="75" width="8.453125" customWidth="1"/>
+    <col min="76" max="76" width="26.90625" customWidth="1"/>
+    <col min="77" max="77" width="22.36328125" customWidth="1"/>
+    <col min="78" max="78" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:78" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3198,7 +3194,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>75</v>
       </c>
@@ -3231,7 +3227,7 @@
       </c>
       <c r="K2" s="35">
         <f t="shared" ref="K2:K16" ca="1" si="0">TODAY()-31</f>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L2" s="30" t="s">
         <v>79</v>
@@ -3271,7 +3267,7 @@
       </c>
       <c r="X2" s="38">
         <f t="shared" ref="X2:X16" ca="1" si="1">K2</f>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y2" s="34" t="s">
         <v>92</v>
@@ -3332,11 +3328,11 @@
       </c>
       <c r="AR2" s="42">
         <f t="shared" ref="AR2:AR16" ca="1" si="2">X2</f>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS2" s="42">
         <f t="shared" ref="AS2:AS16" ca="1" si="3">X2</f>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT2" s="38" t="str">
         <f t="shared" ref="AT2:AT16" si="4">AM2</f>
@@ -3439,7 +3435,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="43" t="s">
         <v>127</v>
       </c>
@@ -3447,16 +3443,16 @@
         <v>128</v>
       </c>
       <c r="C3" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E3" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>81</v>
@@ -3472,7 +3468,7 @@
       </c>
       <c r="K3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L3" s="30" t="s">
         <v>79</v>
@@ -3512,19 +3508,19 @@
       </c>
       <c r="X3" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y3" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z3" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AA3" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB3" s="40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC3" s="39" t="s">
         <v>95</v>
@@ -3551,7 +3547,7 @@
         <v>45293</v>
       </c>
       <c r="AK3" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AL3" s="39" t="s">
         <v>98</v>
@@ -3573,21 +3569,21 @@
       </c>
       <c r="AR3" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS3" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT3" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU3" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV3" s="43" t="s">
         <v>135</v>
-      </c>
-      <c r="AV3" s="43" t="s">
-        <v>136</v>
       </c>
       <c r="AW3" s="30" t="s">
         <v>105</v>
@@ -3635,16 +3631,16 @@
         <v>112</v>
       </c>
       <c r="BL3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BM3" s="39" t="s">
         <v>137</v>
-      </c>
-      <c r="BM3" s="39" t="s">
-        <v>138</v>
       </c>
       <c r="BN3" s="45">
         <v>35591</v>
       </c>
       <c r="BO3" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP3" s="45" t="s">
         <v>99</v>
@@ -3680,24 +3676,24 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="43" t="s">
-        <v>141</v>
-      </c>
       <c r="C4" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G4" s="32" t="s">
         <v>81</v>
@@ -3713,7 +3709,7 @@
       </c>
       <c r="K4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L4" s="30" t="s">
         <v>79</v>
@@ -3753,19 +3749,19 @@
       </c>
       <c r="X4" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y4" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z4" s="34" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AA4" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB4" s="40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AC4" s="39" t="s">
         <v>95</v>
@@ -3814,21 +3810,21 @@
       </c>
       <c r="AR4" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS4" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT4" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU4" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV4" s="43" t="s">
         <v>135</v>
-      </c>
-      <c r="AV4" s="43" t="s">
-        <v>136</v>
       </c>
       <c r="AW4" s="30" t="s">
         <v>105</v>
@@ -3876,7 +3872,7 @@
         <v>112</v>
       </c>
       <c r="BL4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BM4" s="39" t="s">
         <v>114</v>
@@ -3888,7 +3884,7 @@
         <v>115</v>
       </c>
       <c r="BP4" s="45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BQ4" s="46" t="s">
         <v>117</v>
@@ -3921,24 +3917,24 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="43" t="s">
-        <v>148</v>
-      </c>
       <c r="C5" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G5" s="32" t="s">
         <v>81</v>
@@ -3954,7 +3950,7 @@
       </c>
       <c r="K5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L5" s="30" t="s">
         <v>79</v>
@@ -3994,22 +3990,22 @@
       </c>
       <c r="X5" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y5" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z5" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA5" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="AA5" s="30" t="s">
+      <c r="AB5" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="AB5" s="40" t="s">
+      <c r="AC5" s="39" t="s">
         <v>152</v>
-      </c>
-      <c r="AC5" s="39" t="s">
-        <v>153</v>
       </c>
       <c r="AD5" s="30">
         <v>765</v>
@@ -4033,14 +4029,14 @@
         <v>45293</v>
       </c>
       <c r="AK5" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AL5" s="39" t="s">
         <v>98</v>
       </c>
       <c r="AM5" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46149</v>
+        <v>46169</v>
       </c>
       <c r="AN5" s="30">
         <v>110</v>
@@ -4056,20 +4052,20 @@
       </c>
       <c r="AR5" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS5" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT5" s="38" t="s">
         <v>99</v>
       </c>
       <c r="AU5" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV5" s="43" t="s">
         <v>135</v>
-      </c>
-      <c r="AV5" s="43" t="s">
-        <v>136</v>
       </c>
       <c r="AW5" s="30" t="s">
         <v>105</v>
@@ -4117,16 +4113,16 @@
         <v>112</v>
       </c>
       <c r="BL5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BM5" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN5" s="45">
         <v>35591</v>
       </c>
       <c r="BO5" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP5" s="45" t="s">
         <v>99</v>
@@ -4162,24 +4158,24 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="B6" s="43" t="s">
-        <v>157</v>
-      </c>
       <c r="C6" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G6" s="32" t="s">
         <v>81</v>
@@ -4195,7 +4191,7 @@
       </c>
       <c r="K6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L6" s="30" t="s">
         <v>79</v>
@@ -4235,19 +4231,19 @@
       </c>
       <c r="X6" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y6" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z6" s="34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA6" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB6" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AC6" s="39" t="s">
         <v>95</v>
@@ -4274,7 +4270,7 @@
         <v>45293</v>
       </c>
       <c r="AK6" s="39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AL6" s="39" t="s">
         <v>98</v>
@@ -4296,21 +4292,21 @@
       </c>
       <c r="AR6" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS6" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT6" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU6" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV6" s="43" t="s">
         <v>135</v>
-      </c>
-      <c r="AV6" s="43" t="s">
-        <v>136</v>
       </c>
       <c r="AW6" s="30" t="s">
         <v>105</v>
@@ -4358,7 +4354,7 @@
         <v>112</v>
       </c>
       <c r="BL6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BM6" s="39" t="s">
         <v>114</v>
@@ -4370,7 +4366,7 @@
         <v>115</v>
       </c>
       <c r="BP6" s="45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BQ6" s="46" t="s">
         <v>117</v>
@@ -4403,24 +4399,24 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="43" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="43" t="s">
-        <v>165</v>
-      </c>
       <c r="C7" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E7" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G7" s="32" t="s">
         <v>81</v>
@@ -4436,7 +4432,7 @@
       </c>
       <c r="K7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L7" s="30" t="s">
         <v>79</v>
@@ -4476,22 +4472,22 @@
       </c>
       <c r="X7" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y7" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z7" s="34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA7" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB7" s="40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC7" s="39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AD7" s="30">
         <v>765</v>
@@ -4515,7 +4511,7 @@
         <v>45293</v>
       </c>
       <c r="AK7" s="39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AL7" s="39" t="s">
         <v>98</v>
@@ -4537,21 +4533,21 @@
       </c>
       <c r="AR7" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS7" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT7" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU7" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV7" s="43" t="s">
         <v>135</v>
-      </c>
-      <c r="AV7" s="43" t="s">
-        <v>136</v>
       </c>
       <c r="AW7" s="30" t="s">
         <v>105</v>
@@ -4569,7 +4565,7 @@
         <v>109</v>
       </c>
       <c r="BB7" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BC7" s="35">
         <v>46022</v>
@@ -4599,16 +4595,16 @@
         <v>112</v>
       </c>
       <c r="BL7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BM7" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN7" s="45">
         <v>35591</v>
       </c>
       <c r="BO7" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP7" s="45" t="s">
         <v>99</v>
@@ -4644,24 +4640,24 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="43" t="s">
-        <v>173</v>
-      </c>
       <c r="C8" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="29" t="s">
         <v>129</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>130</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G8" s="32" t="s">
         <v>81</v>
@@ -4677,7 +4673,7 @@
       </c>
       <c r="K8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L8" s="30" t="s">
         <v>79</v>
@@ -4717,19 +4713,19 @@
       </c>
       <c r="X8" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y8" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z8" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA8" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="AB8" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="AA8" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="AB8" s="40" t="s">
-        <v>176</v>
       </c>
       <c r="AC8" s="39" t="s">
         <v>95</v>
@@ -4763,7 +4759,7 @@
       </c>
       <c r="AM8" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46149</v>
+        <v>46169</v>
       </c>
       <c r="AN8" s="30">
         <v>110</v>
@@ -4779,20 +4775,20 @@
       </c>
       <c r="AR8" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS8" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT8" s="38" t="s">
         <v>99</v>
       </c>
       <c r="AU8" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV8" s="43" t="s">
         <v>135</v>
-      </c>
-      <c r="AV8" s="43" t="s">
-        <v>136</v>
       </c>
       <c r="AW8" s="30" t="s">
         <v>105</v>
@@ -4840,7 +4836,7 @@
         <v>112</v>
       </c>
       <c r="BL8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BM8" s="39" t="s">
         <v>114</v>
@@ -4852,7 +4848,7 @@
         <v>115</v>
       </c>
       <c r="BP8" s="45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BQ8" s="46" t="s">
         <v>117</v>
@@ -4885,12 +4881,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="43" t="s">
         <v>178</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>179</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>77</v>
@@ -4902,7 +4898,7 @@
         <v>79</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="32" t="s">
         <v>81</v>
@@ -4918,7 +4914,7 @@
       </c>
       <c r="K9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>79</v>
@@ -4958,7 +4954,7 @@
       </c>
       <c r="X9" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y9" s="34" t="s">
         <v>92</v>
@@ -4970,7 +4966,7 @@
         <v>90</v>
       </c>
       <c r="AB9" s="40" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC9" s="39" t="s">
         <v>95</v>
@@ -4997,7 +4993,7 @@
         <v>45293</v>
       </c>
       <c r="AK9" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL9" s="39" t="s">
         <v>98</v>
@@ -5019,11 +5015,11 @@
       </c>
       <c r="AR9" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS9" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT9" s="38" t="str">
         <f t="shared" si="4"/>
@@ -5033,7 +5029,7 @@
         <v>103</v>
       </c>
       <c r="AV9" s="43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AW9" s="30" t="s">
         <v>105</v>
@@ -5081,16 +5077,16 @@
         <v>112</v>
       </c>
       <c r="BL9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BM9" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN9" s="45">
         <v>35591</v>
       </c>
       <c r="BO9" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP9" s="45" t="s">
         <v>99</v>
@@ -5126,12 +5122,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="43" t="s">
         <v>185</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>186</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>77</v>
@@ -5143,7 +5139,7 @@
         <v>79</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>81</v>
@@ -5159,7 +5155,7 @@
       </c>
       <c r="K10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L10" s="30" t="s">
         <v>79</v>
@@ -5199,7 +5195,7 @@
       </c>
       <c r="X10" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y10" s="34" t="s">
         <v>92</v>
@@ -5211,10 +5207,10 @@
         <v>90</v>
       </c>
       <c r="AB10" s="40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AC10" s="39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AD10" s="30">
         <v>765</v>
@@ -5260,11 +5256,11 @@
       </c>
       <c r="AR10" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS10" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT10" s="38" t="str">
         <f t="shared" si="4"/>
@@ -5274,7 +5270,7 @@
         <v>103</v>
       </c>
       <c r="AV10" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AW10" s="30" t="s">
         <v>105</v>
@@ -5322,7 +5318,7 @@
         <v>112</v>
       </c>
       <c r="BL10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BM10" s="39" t="s">
         <v>114</v>
@@ -5334,7 +5330,7 @@
         <v>115</v>
       </c>
       <c r="BP10" s="45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BQ10" s="46" t="s">
         <v>117</v>
@@ -5367,12 +5363,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="43" t="s">
         <v>191</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>192</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>77</v>
@@ -5384,7 +5380,7 @@
         <v>79</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G11" s="32" t="s">
         <v>81</v>
@@ -5400,7 +5396,7 @@
       </c>
       <c r="K11" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L11" s="30" t="s">
         <v>79</v>
@@ -5440,7 +5436,7 @@
       </c>
       <c r="X11" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y11" s="34" t="s">
         <v>92</v>
@@ -5449,10 +5445,10 @@
         <v>93</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB11" s="40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AC11" s="39" t="s">
         <v>95</v>
@@ -5486,7 +5482,7 @@
       </c>
       <c r="AM11" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46149</v>
+        <v>46169</v>
       </c>
       <c r="AN11" s="30">
         <v>110</v>
@@ -5495,28 +5491,28 @@
         <v>100</v>
       </c>
       <c r="AP11" s="34" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AQ11" s="34" t="s">
         <v>102</v>
       </c>
       <c r="AR11" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS11" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT11" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>46149</v>
+        <v>46169</v>
       </c>
       <c r="AU11" s="34" t="s">
         <v>103</v>
       </c>
       <c r="AV11" s="43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AW11" s="30" t="s">
         <v>105</v>
@@ -5564,16 +5560,16 @@
         <v>112</v>
       </c>
       <c r="BL11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BM11" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN11" s="45">
         <v>35591</v>
       </c>
       <c r="BO11" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP11" s="45" t="s">
         <v>99</v>
@@ -5609,12 +5605,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="43" t="s">
         <v>197</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>198</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>77</v>
@@ -5626,7 +5622,7 @@
         <v>79</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G12" s="32" t="s">
         <v>81</v>
@@ -5642,7 +5638,7 @@
       </c>
       <c r="K12" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L12" s="30" t="s">
         <v>79</v>
@@ -5682,7 +5678,7 @@
       </c>
       <c r="X12" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y12" s="34" t="s">
         <v>92</v>
@@ -5694,10 +5690,10 @@
         <v>90</v>
       </c>
       <c r="AB12" s="40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AC12" s="39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AD12" s="30">
         <v>765</v>
@@ -5721,7 +5717,7 @@
         <v>45293</v>
       </c>
       <c r="AK12" s="39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AL12" s="39" t="s">
         <v>98</v>
@@ -5743,11 +5739,11 @@
       </c>
       <c r="AR12" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS12" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT12" s="38" t="str">
         <f t="shared" si="4"/>
@@ -5757,7 +5753,7 @@
         <v>103</v>
       </c>
       <c r="AV12" s="43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AW12" s="30" t="s">
         <v>105</v>
@@ -5805,7 +5801,7 @@
         <v>112</v>
       </c>
       <c r="BL12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BM12" s="39" t="s">
         <v>114</v>
@@ -5817,7 +5813,7 @@
         <v>115</v>
       </c>
       <c r="BP12" s="45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BQ12" s="46" t="s">
         <v>117</v>
@@ -5850,12 +5846,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="43" t="s">
         <v>204</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>205</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>77</v>
@@ -5867,7 +5863,7 @@
         <v>79</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G13" s="32" t="s">
         <v>81</v>
@@ -5883,7 +5879,7 @@
       </c>
       <c r="K13" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L13" s="30" t="s">
         <v>79</v>
@@ -5923,7 +5919,7 @@
       </c>
       <c r="X13" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y13" s="34" t="s">
         <v>92</v>
@@ -5935,7 +5931,7 @@
         <v>90</v>
       </c>
       <c r="AB13" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AC13" s="39" t="s">
         <v>95</v>
@@ -5962,7 +5958,7 @@
         <v>45293</v>
       </c>
       <c r="AK13" s="39" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL13" s="39" t="s">
         <v>98</v>
@@ -5984,11 +5980,11 @@
       </c>
       <c r="AR13" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS13" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT13" s="38" t="str">
         <f t="shared" si="4"/>
@@ -5998,7 +5994,7 @@
         <v>103</v>
       </c>
       <c r="AV13" s="43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AW13" s="30" t="s">
         <v>105</v>
@@ -6046,16 +6042,16 @@
         <v>112</v>
       </c>
       <c r="BL13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BM13" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN13" s="45">
         <v>35591</v>
       </c>
       <c r="BO13" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP13" s="45" t="s">
         <v>99</v>
@@ -6091,12 +6087,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="43" t="s">
         <v>211</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>212</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>77</v>
@@ -6108,7 +6104,7 @@
         <v>79</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G14" s="32" t="s">
         <v>81</v>
@@ -6124,7 +6120,7 @@
       </c>
       <c r="K14" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L14" s="30" t="s">
         <v>79</v>
@@ -6164,7 +6160,7 @@
       </c>
       <c r="X14" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y14" s="34" t="s">
         <v>92</v>
@@ -6173,13 +6169,13 @@
         <v>93</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB14" s="40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AC14" s="39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AD14" s="30">
         <v>765</v>
@@ -6203,14 +6199,14 @@
         <v>45293</v>
       </c>
       <c r="AK14" s="39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL14" s="39" t="s">
         <v>98</v>
       </c>
       <c r="AM14" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46149</v>
+        <v>46169</v>
       </c>
       <c r="AN14" s="30">
         <v>110</v>
@@ -6226,11 +6222,11 @@
       </c>
       <c r="AR14" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS14" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT14" s="38" t="s">
         <v>99</v>
@@ -6239,7 +6235,7 @@
         <v>103</v>
       </c>
       <c r="AV14" s="43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AW14" s="30" t="s">
         <v>105</v>
@@ -6257,7 +6253,7 @@
         <v>109</v>
       </c>
       <c r="BB14" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BC14" s="35">
         <v>46022</v>
@@ -6287,7 +6283,7 @@
         <v>112</v>
       </c>
       <c r="BL14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="BM14" s="39" t="s">
         <v>114</v>
@@ -6299,7 +6295,7 @@
         <v>115</v>
       </c>
       <c r="BP14" s="45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BQ14" s="46" t="s">
         <v>117</v>
@@ -6332,12 +6328,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" s="43" t="s">
         <v>216</v>
-      </c>
-      <c r="B15" s="43" t="s">
-        <v>217</v>
       </c>
       <c r="C15" s="28" t="s">
         <v>77</v>
@@ -6349,7 +6345,7 @@
         <v>79</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G15" s="32" t="s">
         <v>81</v>
@@ -6365,7 +6361,7 @@
       </c>
       <c r="K15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L15" s="30" t="s">
         <v>79</v>
@@ -6405,7 +6401,7 @@
       </c>
       <c r="X15" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y15" s="34" t="s">
         <v>92</v>
@@ -6414,13 +6410,13 @@
         <v>93</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB15" s="40" t="s">
         <v>94</v>
       </c>
       <c r="AC15" s="39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AD15" s="30">
         <v>765</v>
@@ -6451,7 +6447,7 @@
       </c>
       <c r="AM15" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46149</v>
+        <v>46169</v>
       </c>
       <c r="AN15" s="30">
         <v>110</v>
@@ -6460,22 +6456,22 @@
         <v>100</v>
       </c>
       <c r="AP15" s="39" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AQ15" s="34" t="s">
         <v>102</v>
       </c>
       <c r="AR15" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS15" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT15" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>46149</v>
+        <v>46169</v>
       </c>
       <c r="AU15" s="34" t="s">
         <v>103</v>
@@ -6529,16 +6525,16 @@
         <v>112</v>
       </c>
       <c r="BL15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BM15" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN15" s="45">
         <v>35591</v>
       </c>
       <c r="BO15" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP15" s="45" t="s">
         <v>99</v>
@@ -6574,12 +6570,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="B16" s="43" t="s">
         <v>220</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>221</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>77</v>
@@ -6591,7 +6587,7 @@
         <v>79</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G16" s="32" t="s">
         <v>81</v>
@@ -6607,7 +6603,7 @@
       </c>
       <c r="K16" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="L16" s="30" t="s">
         <v>79</v>
@@ -6647,7 +6643,7 @@
       </c>
       <c r="X16" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="Y16" s="34" t="s">
         <v>92</v>
@@ -6708,11 +6704,11 @@
       </c>
       <c r="AR16" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AS16" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
+        <v>45773</v>
       </c>
       <c r="AT16" s="38" t="str">
         <f t="shared" si="4"/>
@@ -6740,7 +6736,7 @@
         <v>109</v>
       </c>
       <c r="BB16" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BC16" s="35">
         <v>46022</v>
@@ -6770,7 +6766,7 @@
         <v>112</v>
       </c>
       <c r="BL16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BM16" s="39" t="s">
         <v>114</v>
@@ -6782,7 +6778,7 @@
         <v>115</v>
       </c>
       <c r="BP16" s="45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BQ16" s="46" t="s">
         <v>117</v>
@@ -6815,7 +6811,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
@@ -6895,7 +6891,7 @@
       <c r="BY17" s="48"/>
       <c r="BZ17" s="48"/>
     </row>
-    <row r="18" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="48"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
@@ -6975,7 +6971,7 @@
       <c r="BY18" s="48"/>
       <c r="BZ18" s="48"/>
     </row>
-    <row r="19" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
@@ -7055,7 +7051,7 @@
       <c r="BY19" s="48"/>
       <c r="BZ19" s="48"/>
     </row>
-    <row r="20" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="48"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
@@ -7135,7 +7131,7 @@
       <c r="BY20" s="48"/>
       <c r="BZ20" s="48"/>
     </row>
-    <row r="21" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="48"/>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
@@ -7215,7 +7211,7 @@
       <c r="BY21" s="48"/>
       <c r="BZ21" s="48"/>
     </row>
-    <row r="22" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="48"/>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
@@ -7295,7 +7291,7 @@
       <c r="BY22" s="48"/>
       <c r="BZ22" s="48"/>
     </row>
-    <row r="23" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="48"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
@@ -7375,7 +7371,7 @@
       <c r="BY23" s="48"/>
       <c r="BZ23" s="48"/>
     </row>
-    <row r="24" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="48"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
@@ -7455,7 +7451,7 @@
       <c r="BY24" s="48"/>
       <c r="BZ24" s="48"/>
     </row>
-    <row r="25" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="48"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
@@ -7535,7 +7531,7 @@
       <c r="BY25" s="48"/>
       <c r="BZ25" s="48"/>
     </row>
-    <row r="26" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="48"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -7615,7 +7611,7 @@
       <c r="BY26" s="48"/>
       <c r="BZ26" s="48"/>
     </row>
-    <row r="27" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="48"/>
       <c r="B27" s="48"/>
       <c r="C27" s="48"/>
@@ -7695,7 +7691,7 @@
       <c r="BY27" s="48"/>
       <c r="BZ27" s="48"/>
     </row>
-    <row r="28" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="48"/>
       <c r="B28" s="48"/>
       <c r="C28" s="48"/>
@@ -7775,7 +7771,7 @@
       <c r="BY28" s="48"/>
       <c r="BZ28" s="48"/>
     </row>
-    <row r="29" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="48"/>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
@@ -7855,7 +7851,7 @@
       <c r="BY29" s="48"/>
       <c r="BZ29" s="48"/>
     </row>
-    <row r="30" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="48"/>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
@@ -7935,7 +7931,7 @@
       <c r="BY30" s="48"/>
       <c r="BZ30" s="48"/>
     </row>
-    <row r="31" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="48"/>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
@@ -8015,7 +8011,7 @@
       <c r="BY31" s="48"/>
       <c r="BZ31" s="48"/>
     </row>
-    <row r="32" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="48"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
@@ -8095,7 +8091,7 @@
       <c r="BY32" s="48"/>
       <c r="BZ32" s="48"/>
     </row>
-    <row r="33" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="48"/>
       <c r="B33" s="48"/>
       <c r="C33" s="48"/>
@@ -8175,7 +8171,7 @@
       <c r="BY33" s="48"/>
       <c r="BZ33" s="48"/>
     </row>
-    <row r="34" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="48"/>
       <c r="B34" s="48"/>
       <c r="C34" s="48"/>
@@ -8255,7 +8251,7 @@
       <c r="BY34" s="48"/>
       <c r="BZ34" s="48"/>
     </row>
-    <row r="35" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="48"/>
       <c r="B35" s="48"/>
       <c r="C35" s="48"/>
@@ -8335,7 +8331,7 @@
       <c r="BY35" s="48"/>
       <c r="BZ35" s="48"/>
     </row>
-    <row r="36" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="48"/>
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
@@ -8415,7 +8411,7 @@
       <c r="BY36" s="48"/>
       <c r="BZ36" s="48"/>
     </row>
-    <row r="37" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="48"/>
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
@@ -8495,7 +8491,7 @@
       <c r="BY37" s="48"/>
       <c r="BZ37" s="48"/>
     </row>
-    <row r="38" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="48"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
@@ -8575,7 +8571,7 @@
       <c r="BY38" s="48"/>
       <c r="BZ38" s="48"/>
     </row>
-    <row r="39" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="48"/>
       <c r="B39" s="48"/>
       <c r="C39" s="48"/>
@@ -8655,7 +8651,7 @@
       <c r="BY39" s="48"/>
       <c r="BZ39" s="48"/>
     </row>
-    <row r="40" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="48"/>
       <c r="B40" s="48"/>
       <c r="C40" s="48"/>
@@ -8735,7 +8731,7 @@
       <c r="BY40" s="48"/>
       <c r="BZ40" s="48"/>
     </row>
-    <row r="41" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="48"/>
       <c r="B41" s="48"/>
       <c r="C41" s="48"/>
@@ -8815,7 +8811,7 @@
       <c r="BY41" s="48"/>
       <c r="BZ41" s="48"/>
     </row>
-    <row r="42" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="48"/>
       <c r="B42" s="48"/>
       <c r="C42" s="48"/>
@@ -8895,7 +8891,7 @@
       <c r="BY42" s="48"/>
       <c r="BZ42" s="48"/>
     </row>
-    <row r="43" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="48"/>
       <c r="B43" s="48"/>
       <c r="C43" s="48"/>
@@ -8975,7 +8971,7 @@
       <c r="BY43" s="48"/>
       <c r="BZ43" s="48"/>
     </row>
-    <row r="44" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="48"/>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
@@ -9055,7 +9051,7 @@
       <c r="BY44" s="48"/>
       <c r="BZ44" s="48"/>
     </row>
-    <row r="45" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="48"/>
       <c r="B45" s="48"/>
       <c r="C45" s="48"/>
@@ -9135,7 +9131,7 @@
       <c r="BY45" s="48"/>
       <c r="BZ45" s="48"/>
     </row>
-    <row r="46" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="48"/>
       <c r="B46" s="48"/>
       <c r="C46" s="48"/>
@@ -9215,7 +9211,7 @@
       <c r="BY46" s="48"/>
       <c r="BZ46" s="48"/>
     </row>
-    <row r="47" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="48"/>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
@@ -9295,7 +9291,7 @@
       <c r="BY47" s="48"/>
       <c r="BZ47" s="48"/>
     </row>
-    <row r="48" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="48"/>
       <c r="B48" s="48"/>
       <c r="C48" s="48"/>
@@ -9375,7 +9371,7 @@
       <c r="BY48" s="48"/>
       <c r="BZ48" s="48"/>
     </row>
-    <row r="49" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="48"/>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
@@ -9455,7 +9451,7 @@
       <c r="BY49" s="48"/>
       <c r="BZ49" s="48"/>
     </row>
-    <row r="50" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="48"/>
       <c r="B50" s="48"/>
       <c r="C50" s="48"/>
@@ -9535,7 +9531,7 @@
       <c r="BY50" s="48"/>
       <c r="BZ50" s="48"/>
     </row>
-    <row r="51" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="48"/>
       <c r="B51" s="48"/>
       <c r="C51" s="48"/>
@@ -9615,7 +9611,7 @@
       <c r="BY51" s="48"/>
       <c r="BZ51" s="48"/>
     </row>
-    <row r="52" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="48"/>
       <c r="B52" s="48"/>
       <c r="C52" s="48"/>
@@ -9695,7 +9691,7 @@
       <c r="BY52" s="48"/>
       <c r="BZ52" s="48"/>
     </row>
-    <row r="53" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="48"/>
       <c r="B53" s="48"/>
       <c r="C53" s="48"/>
@@ -9775,7 +9771,7 @@
       <c r="BY53" s="48"/>
       <c r="BZ53" s="48"/>
     </row>
-    <row r="54" spans="1:78" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:78" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="48"/>
       <c r="B54" s="48"/>
       <c r="C54" s="48"/>

--- a/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
@@ -1,18 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{230C2C61-7F88-4DB0-86D9-19B1978EAF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -247,25 +262,22 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Erna Smitham' Employee:{undefined}TimeoutError: page.goto: Timeout 30000ms exceeded.
+    <t xml:space="preserve">Test failed for 'Maurice Bartoletti' Employee:{undefined}TimeoutError: locator.clear: Timeout 30000ms exceeded.
 Call log:
-  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark14/login.htmld", waiting until "load"[22m
+  [2m- waiting for locator('[aria-label="Search Workday "]')[22m
 </t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>765 Retail Team 1 (Jizur Buzese (10226524) (Inherited))</t>
   </si>
   <si>
     <t>Poland</t>
   </si>
   <si>
-    <t>Erna</t>
-  </si>
-  <si>
-    <t>Smitham</t>
+    <t>Maurice</t>
+  </si>
+  <si>
+    <t>Bartoletti</t>
   </si>
   <si>
     <t xml:space="preserve">698 980 460 </t>
@@ -415,10 +427,10 @@
     <t>765 Store Management (Jizur Buzese (10226524))</t>
   </si>
   <si>
-    <t>Howell</t>
-  </si>
-  <si>
-    <t>Goodwin</t>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Ward</t>
   </si>
   <si>
     <t>Auto 68221345</t>
@@ -774,149 +786,152 @@
   <si>
     <t>GHE456310</t>
   </si>
+  <si>
+    <t>Passed</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color indexed="8"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color indexed="63"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
       <u/>
+      <sz val="10"/>
       <color indexed="12"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color indexed="10"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color indexed="63"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color indexed="12"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="63"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color indexed="63"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color indexed="10"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
   </fonts>
   <fills count="7">
@@ -951,7 +966,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -965,9 +980,15 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -978,15 +999,25 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1413,91 +1444,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" customWidth="1"/>
-    <col min="4" max="4" width="41.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" customWidth="1"/>
+    <col min="4" max="4" width="41.453125" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="5.6328125" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" customWidth="1"/>
-    <col min="18" max="18" width="11.88671875" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="20.6328125" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" customWidth="1"/>
+    <col min="15" max="15" width="10.81640625" customWidth="1"/>
+    <col min="16" max="16" width="8.08984375" customWidth="1"/>
+    <col min="17" max="17" width="13.1796875" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" customWidth="1"/>
+    <col min="19" max="19" width="8.08984375" customWidth="1"/>
+    <col min="20" max="20" width="5.6328125" customWidth="1"/>
+    <col min="21" max="21" width="12.36328125" customWidth="1"/>
     <col min="22" max="22" width="17" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" customWidth="1"/>
-    <col min="24" max="24" width="10.5546875" customWidth="1"/>
-    <col min="25" max="25" width="8.109375" customWidth="1"/>
-    <col min="26" max="26" width="23.109375" customWidth="1"/>
-    <col min="27" max="27" width="19.6640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6328125" customWidth="1"/>
+    <col min="24" max="24" width="10.54296875" customWidth="1"/>
+    <col min="25" max="25" width="8.08984375" customWidth="1"/>
+    <col min="26" max="26" width="23.08984375" customWidth="1"/>
+    <col min="27" max="27" width="19.6328125" style="1" customWidth="1"/>
     <col min="28" max="28" width="37" customWidth="1"/>
-    <col min="29" max="29" width="9.21875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="8.44140625" customWidth="1"/>
-    <col min="31" max="31" width="12.109375" customWidth="1"/>
-    <col min="32" max="32" width="21.77734375" customWidth="1"/>
-    <col min="33" max="33" width="11.6640625" customWidth="1"/>
-    <col min="34" max="34" width="22.88671875" customWidth="1"/>
-    <col min="35" max="35" width="15.21875" customWidth="1"/>
-    <col min="36" max="36" width="14.109375" customWidth="1"/>
+    <col min="29" max="29" width="9.1796875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="8.453125" customWidth="1"/>
+    <col min="31" max="31" width="12.08984375" customWidth="1"/>
+    <col min="32" max="32" width="21.81640625" customWidth="1"/>
+    <col min="33" max="33" width="11.6328125" customWidth="1"/>
+    <col min="34" max="34" width="22.90625" customWidth="1"/>
+    <col min="35" max="35" width="15.1796875" customWidth="1"/>
+    <col min="36" max="36" width="14.08984375" customWidth="1"/>
     <col min="37" max="37" width="26" customWidth="1"/>
-    <col min="38" max="38" width="13.109375" style="1" customWidth="1"/>
-    <col min="39" max="39" width="19.21875" customWidth="1"/>
-    <col min="40" max="40" width="16.88671875" customWidth="1"/>
-    <col min="41" max="41" width="25.21875" customWidth="1"/>
-    <col min="42" max="42" width="12.6640625" customWidth="1"/>
-    <col min="43" max="43" width="6.5546875" customWidth="1"/>
-    <col min="44" max="44" width="19.33203125" customWidth="1"/>
-    <col min="45" max="45" width="19.109375" customWidth="1"/>
-    <col min="46" max="46" width="15.88671875" customWidth="1"/>
-    <col min="47" max="47" width="19.21875" customWidth="1"/>
-    <col min="48" max="48" width="23.44140625" customWidth="1"/>
-    <col min="49" max="49" width="14.6640625" customWidth="1"/>
-    <col min="50" max="50" width="23.109375" customWidth="1"/>
-    <col min="51" max="51" width="28.6640625" customWidth="1"/>
-    <col min="52" max="52" width="17.77734375" customWidth="1"/>
-    <col min="53" max="53" width="22.44140625" customWidth="1"/>
-    <col min="54" max="54" width="17.77734375" customWidth="1"/>
+    <col min="38" max="38" width="13.08984375" style="1" customWidth="1"/>
+    <col min="39" max="39" width="19.1796875" customWidth="1"/>
+    <col min="40" max="40" width="16.90625" customWidth="1"/>
+    <col min="41" max="41" width="25.1796875" customWidth="1"/>
+    <col min="42" max="42" width="12.6328125" customWidth="1"/>
+    <col min="43" max="43" width="6.54296875" customWidth="1"/>
+    <col min="44" max="44" width="19.36328125" customWidth="1"/>
+    <col min="45" max="45" width="19.08984375" customWidth="1"/>
+    <col min="46" max="46" width="15.90625" customWidth="1"/>
+    <col min="47" max="47" width="19.1796875" customWidth="1"/>
+    <col min="48" max="48" width="23.453125" customWidth="1"/>
+    <col min="49" max="49" width="14.6328125" customWidth="1"/>
+    <col min="50" max="50" width="23.08984375" customWidth="1"/>
+    <col min="51" max="51" width="28.6328125" customWidth="1"/>
+    <col min="52" max="52" width="17.81640625" customWidth="1"/>
+    <col min="53" max="53" width="22.453125" customWidth="1"/>
+    <col min="54" max="54" width="17.81640625" customWidth="1"/>
     <col min="55" max="55" width="18" customWidth="1"/>
-    <col min="56" max="56" width="9.109375" customWidth="1"/>
-    <col min="57" max="57" width="15.5546875" customWidth="1"/>
+    <col min="56" max="56" width="9.08984375" customWidth="1"/>
+    <col min="57" max="57" width="15.54296875" customWidth="1"/>
     <col min="58" max="58" width="12" customWidth="1"/>
-    <col min="59" max="59" width="9.109375" customWidth="1"/>
-    <col min="60" max="60" width="27.33203125" customWidth="1"/>
+    <col min="59" max="59" width="9.08984375" customWidth="1"/>
+    <col min="60" max="60" width="27.36328125" customWidth="1"/>
     <col min="61" max="61" width="12" customWidth="1"/>
-    <col min="62" max="62" width="9.109375" customWidth="1"/>
-    <col min="63" max="63" width="15.5546875" customWidth="1"/>
-    <col min="64" max="64" width="10.77734375" customWidth="1"/>
-    <col min="65" max="65" width="7.33203125" customWidth="1"/>
-    <col min="66" max="66" width="11.33203125" customWidth="1"/>
-    <col min="67" max="67" width="14.21875" customWidth="1"/>
+    <col min="62" max="62" width="9.08984375" customWidth="1"/>
+    <col min="63" max="63" width="15.54296875" customWidth="1"/>
+    <col min="64" max="64" width="10.81640625" customWidth="1"/>
+    <col min="65" max="65" width="7.36328125" customWidth="1"/>
+    <col min="66" max="66" width="11.36328125" customWidth="1"/>
+    <col min="67" max="67" width="14.1796875" customWidth="1"/>
     <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="16.33203125" customWidth="1"/>
-    <col min="70" max="70" width="12.5546875" customWidth="1"/>
-    <col min="71" max="71" width="21.6640625" customWidth="1"/>
-    <col min="72" max="72" width="12.21875" customWidth="1"/>
-    <col min="73" max="73" width="27.44140625" customWidth="1"/>
-    <col min="74" max="74" width="29.21875" customWidth="1"/>
-    <col min="75" max="75" width="8.44140625" customWidth="1"/>
-    <col min="76" max="76" width="26.88671875" customWidth="1"/>
-    <col min="77" max="77" width="22.33203125" customWidth="1"/>
-    <col min="78" max="78" width="23.21875" customWidth="1"/>
+    <col min="69" max="69" width="16.36328125" customWidth="1"/>
+    <col min="70" max="70" width="12.54296875" customWidth="1"/>
+    <col min="71" max="71" width="21.6328125" customWidth="1"/>
+    <col min="72" max="72" width="12.1796875" customWidth="1"/>
+    <col min="73" max="73" width="27.453125" customWidth="1"/>
+    <col min="74" max="74" width="29.1796875" customWidth="1"/>
+    <col min="75" max="75" width="8.453125" customWidth="1"/>
+    <col min="76" max="76" width="26.90625" customWidth="1"/>
+    <col min="77" max="77" width="22.36328125" customWidth="1"/>
+    <col min="78" max="78" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" customHeight="1" spans="1:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:78" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1733,7 +1764,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>75</v>
       </c>
@@ -1741,87 +1772,87 @@
         <v>76</v>
       </c>
       <c r="C2" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="E2" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="F2" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="G2" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="H2" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="I2" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="J2" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="K2" s="35">
+        <f t="shared" ref="K2:K16" ca="1" si="0">TODAY()-31</f>
+        <v>45779</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="M2" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="35">
-        <f t="shared" ref="K2:K16" si="0">TODAY()-31</f>
-        <v>45753</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M2" s="30" t="s">
+      <c r="N2" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N2" s="34" t="s">
+      <c r="O2" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="P2" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="Q2" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q2" s="34" t="s">
+      <c r="R2" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S2" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U2" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R2" s="34" t="s">
+      <c r="V2" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W2" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X2" s="38">
+        <f t="shared" ref="X2:X16" ca="1" si="1">K2</f>
+        <v>45779</v>
+      </c>
+      <c r="Y2" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z2" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA2" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="S2" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T2" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V2" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W2" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X2" s="38">
-        <f t="shared" ref="X2:X16" si="1">K2</f>
-        <v>45753</v>
-      </c>
-      <c r="Y2" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z2" s="34" t="s">
+      <c r="AB2" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AA2" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB2" s="40" t="s">
+      <c r="AC2" s="39" t="s">
         <v>94</v>
-      </c>
-      <c r="AC2" s="39" t="s">
-        <v>95</v>
       </c>
       <c r="AD2" s="30">
         <v>765</v>
@@ -1833,10 +1864,10 @@
         <v>40</v>
       </c>
       <c r="AG2" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH2" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI2" s="35">
         <v>43831</v>
@@ -1845,224 +1876,224 @@
         <v>45293</v>
       </c>
       <c r="AK2" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL2" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL2" s="39" t="s">
+      <c r="AM2" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM2" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN2" s="30">
         <v>110</v>
       </c>
       <c r="AO2" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP2" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP2" s="34" t="s">
+      <c r="AQ2" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ2" s="34" t="s">
+      <c r="AR2" s="42">
+        <f t="shared" ref="AR2:AR16" ca="1" si="2">X2</f>
+        <v>45779</v>
+      </c>
+      <c r="AS2" s="42">
+        <f t="shared" ref="AS2:AS16" ca="1" si="3">X2</f>
+        <v>45779</v>
+      </c>
+      <c r="AT2" s="38" t="str">
+        <f t="shared" ref="AT2:AT16" si="4">AM2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AU2" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AR2" s="42">
-        <f t="shared" ref="AR2:AR16" si="2">X2</f>
-        <v>45753</v>
-      </c>
-      <c r="AS2" s="42">
-        <f t="shared" ref="AS2:AS16" si="3">X2</f>
-        <v>45753</v>
-      </c>
-      <c r="AT2" s="38">
-        <f t="shared" ref="AT2:AT16" si="4">AM2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AU2" s="34" t="s">
+      <c r="AV2" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="AV2" s="43" t="s">
+      <c r="AW2" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AW2" s="30" t="s">
+      <c r="AX2" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX2" s="30" t="s">
+      <c r="AY2" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY2" s="30" t="s">
+      <c r="AZ2" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ2" s="30" t="s">
+      <c r="BA2" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA2" s="30" t="s">
+      <c r="BB2" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC2" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD2" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE2" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC2" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD2" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE2" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF2" s="44">
         <v>9893790846</v>
       </c>
       <c r="BG2" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH2" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI2" s="30">
         <v>47678965516</v>
       </c>
       <c r="BJ2" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK2" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="BL2" t="s">
         <v>112</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" s="39" t="s">
         <v>113</v>
-      </c>
-      <c r="BM2" s="39" t="s">
-        <v>114</v>
       </c>
       <c r="BN2" s="45">
         <v>35591</v>
       </c>
       <c r="BO2" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP2" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="BP2" s="45" t="s">
+      <c r="BQ2" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="BQ2" s="46" t="s">
+      <c r="BR2" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR2" s="30" t="s">
+      <c r="BS2" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS2" s="47" t="s">
+      <c r="BT2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="30" t="s">
+      <c r="BU2" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU2" s="46" t="s">
+      <c r="BV2" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV2" s="46" t="s">
+      <c r="BW2" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW2" s="30" t="s">
+      <c r="BX2" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX2" s="30" t="s">
+      <c r="BY2" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY2" s="30" t="s">
+      <c r="BZ2" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ2" s="25" t="s">
+    </row>
+    <row r="3" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="43" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="3" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="B3" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="C3" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="29" t="s">
+      <c r="E3" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="31" t="s">
+      <c r="G3" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="H3" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L3" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N3" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q3" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R3" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S3" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T3" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U3" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V3" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W3" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X3" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y3" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z3" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J3" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K3" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L3" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M3" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N3" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O3" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P3" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q3" s="34" t="s">
+      <c r="AA3" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="R3" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S3" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T3" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V3" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W3" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X3" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y3" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z3" s="34" t="s">
+      <c r="AB3" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="AA3" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB3" s="40" t="s">
-        <v>133</v>
-      </c>
       <c r="AC3" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD3" s="30">
         <v>765</v>
@@ -2074,10 +2105,10 @@
         <v>40</v>
       </c>
       <c r="AG3" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH3" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI3" s="35">
         <v>43831</v>
@@ -2086,224 +2117,224 @@
         <v>45293</v>
       </c>
       <c r="AK3" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AL3" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM3" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM3" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN3" s="30">
         <v>110</v>
       </c>
       <c r="AO3" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP3" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP3" s="34" t="s">
+      <c r="AQ3" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ3" s="34" t="s">
-        <v>102</v>
-      </c>
       <c r="AR3" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
       </c>
       <c r="AS3" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT3" s="38">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT3" s="38" t="str">
         <f t="shared" si="4"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AU3" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV3" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="AV3" s="43" t="s">
-        <v>136</v>
-      </c>
       <c r="AW3" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX3" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX3" s="30" t="s">
+      <c r="AY3" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY3" s="30" t="s">
+      <c r="AZ3" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ3" s="30" t="s">
+      <c r="BA3" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA3" s="30" t="s">
+      <c r="BB3" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC3" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD3" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE3" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB3" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC3" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD3" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE3" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF3" s="44">
         <v>9893790847</v>
       </c>
       <c r="BG3" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH3" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI3" s="30">
         <v>47678965517</v>
       </c>
       <c r="BJ3" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK3" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BM3" s="39" t="s">
         <v>137</v>
-      </c>
-      <c r="BM3" s="39" t="s">
-        <v>138</v>
       </c>
       <c r="BN3" s="45">
         <v>35591</v>
       </c>
       <c r="BO3" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="BP3" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="BQ3" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR3" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS3" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT3" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU3" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV3" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW3" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX3" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BY3" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ3" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="BP3" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="BQ3" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR3" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BS3" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT3" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU3" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV3" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW3" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="BY3" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="BZ3" s="25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="B4" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="C4" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="31" t="s">
+      <c r="G4" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="H4" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L4" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N4" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q4" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R4" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S4" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T4" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U4" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V4" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W4" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X4" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y4" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z4" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="H4" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K4" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M4" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N4" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O4" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P4" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q4" s="34" t="s">
+      <c r="AA4" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="R4" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S4" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T4" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U4" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V4" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W4" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X4" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y4" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z4" s="34" t="s">
+      <c r="AB4" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="AA4" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB4" s="40" t="s">
-        <v>145</v>
-      </c>
       <c r="AC4" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD4" s="30">
         <v>765</v>
@@ -2315,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="AG4" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH4" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI4" s="35">
         <v>43831</v>
@@ -2327,224 +2358,224 @@
         <v>45293</v>
       </c>
       <c r="AK4" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL4" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL4" s="39" t="s">
+      <c r="AM4" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM4" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN4" s="30">
         <v>110</v>
       </c>
       <c r="AO4" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP4" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP4" s="34" t="s">
+      <c r="AQ4" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ4" s="34" t="s">
-        <v>102</v>
-      </c>
       <c r="AR4" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
       </c>
       <c r="AS4" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT4" s="38">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT4" s="38" t="str">
         <f t="shared" si="4"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AU4" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV4" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="AV4" s="43" t="s">
-        <v>136</v>
-      </c>
       <c r="AW4" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX4" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AY4" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AZ4" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ4" s="30" t="s">
+      <c r="BA4" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA4" s="30" t="s">
+      <c r="BB4" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC4" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD4" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE4" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB4" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC4" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE4" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF4" s="44">
         <v>9893790848</v>
       </c>
       <c r="BG4" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH4" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI4" s="30">
         <v>47678965518</v>
       </c>
       <c r="BJ4" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK4" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BM4" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN4" s="45">
         <v>35591</v>
       </c>
       <c r="BO4" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP4" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="BQ4" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR4" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS4" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT4" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU4" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV4" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW4" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX4" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BY4" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ4" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="BQ4" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR4" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BS4" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT4" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU4" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV4" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW4" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX4" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="BY4" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="BZ4" s="25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="B5" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="C5" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="31" t="s">
+      <c r="G5" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="H5" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L5" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N5" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O5" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P5" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R5" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S5" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T5" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U5" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V5" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W5" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X5" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y5" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z5" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="H5" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J5" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K5" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L5" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M5" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N5" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O5" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P5" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q5" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="R5" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S5" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T5" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U5" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V5" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W5" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X5" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y5" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z5" s="34" t="s">
+      <c r="AA5" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="AA5" s="30" t="s">
+      <c r="AB5" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="AB5" s="40" t="s">
+      <c r="AC5" s="39" t="s">
         <v>154</v>
-      </c>
-      <c r="AC5" s="39" t="s">
-        <v>155</v>
       </c>
       <c r="AD5" s="30">
         <v>765</v>
@@ -2556,10 +2587,10 @@
         <v>30</v>
       </c>
       <c r="AG5" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH5" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI5" s="35">
         <v>43831</v>
@@ -2568,224 +2599,224 @@
         <v>45293</v>
       </c>
       <c r="AK5" s="39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AL5" s="39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AM5" s="41">
-        <f>TODAY()+365</f>
-        <v>46149</v>
+        <f ca="1">TODAY()+365</f>
+        <v>46175</v>
       </c>
       <c r="AN5" s="30">
         <v>110</v>
       </c>
       <c r="AO5" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP5" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP5" s="34" t="s">
+      <c r="AQ5" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ5" s="34" t="s">
-        <v>102</v>
-      </c>
       <c r="AR5" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
       </c>
       <c r="AS5" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
       </c>
       <c r="AT5" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AU5" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV5" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="AV5" s="43" t="s">
-        <v>136</v>
-      </c>
       <c r="AW5" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX5" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX5" s="30" t="s">
+      <c r="AY5" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY5" s="30" t="s">
+      <c r="AZ5" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ5" s="30" t="s">
+      <c r="BA5" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA5" s="30" t="s">
+      <c r="BB5" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC5" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD5" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE5" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB5" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC5" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD5" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE5" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF5" s="44">
         <v>9893790849</v>
       </c>
       <c r="BG5" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH5" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI5" s="30">
         <v>47678965519</v>
       </c>
       <c r="BJ5" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK5" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BM5" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN5" s="45">
         <v>35591</v>
       </c>
       <c r="BO5" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP5" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ5" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR5" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR5" s="30" t="s">
+      <c r="BS5" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS5" s="47" t="s">
+      <c r="BT5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT5" s="30" t="s">
+      <c r="BU5" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU5" s="46" t="s">
+      <c r="BV5" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV5" s="46" t="s">
+      <c r="BW5" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW5" s="30" t="s">
+      <c r="BX5" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX5" s="30" t="s">
+      <c r="BY5" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY5" s="30" t="s">
+      <c r="BZ5" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ5" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="6" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="C6" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="31" t="s">
+      <c r="G6" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="H6" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q6" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S6" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T6" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U6" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V6" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W6" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X6" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y6" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z6" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L6" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M6" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O6" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P6" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q6" s="34" t="s">
+      <c r="AA6" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="R6" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S6" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T6" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U6" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V6" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W6" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X6" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y6" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z6" s="34" t="s">
+      <c r="AB6" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="AA6" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB6" s="40" t="s">
-        <v>163</v>
-      </c>
       <c r="AC6" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD6" s="30">
         <v>765</v>
@@ -2797,10 +2828,10 @@
         <v>40</v>
       </c>
       <c r="AG6" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH6" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI6" s="35">
         <v>43831</v>
@@ -2809,224 +2840,224 @@
         <v>45293</v>
       </c>
       <c r="AK6" s="39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL6" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM6" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM6" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN6" s="30">
         <v>110</v>
       </c>
       <c r="AO6" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP6" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP6" s="34" t="s">
+      <c r="AQ6" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ6" s="34" t="s">
-        <v>102</v>
-      </c>
       <c r="AR6" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
       </c>
       <c r="AS6" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT6" s="38">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT6" s="38" t="str">
         <f t="shared" si="4"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AU6" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV6" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="AV6" s="43" t="s">
-        <v>136</v>
-      </c>
       <c r="AW6" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX6" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX6" s="30" t="s">
+      <c r="AY6" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY6" s="30" t="s">
+      <c r="AZ6" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ6" s="30" t="s">
+      <c r="BA6" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA6" s="30" t="s">
+      <c r="BB6" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC6" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD6" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE6" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB6" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC6" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD6" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE6" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF6" s="44">
         <v>9893790850</v>
       </c>
       <c r="BG6" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH6" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI6" s="30">
         <v>47678965520</v>
       </c>
       <c r="BJ6" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK6" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BM6" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN6" s="45">
         <v>35591</v>
       </c>
       <c r="BO6" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP6" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="BQ6" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR6" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS6" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT6" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU6" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV6" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW6" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX6" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BY6" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ6" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="BQ6" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR6" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BS6" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT6" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU6" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV6" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW6" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX6" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="BY6" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="BZ6" s="25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+      <c r="B7" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="C7" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="31" t="s">
+      <c r="G7" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="H7" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L7" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O7" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q7" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R7" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S7" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T7" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U7" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V7" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W7" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X7" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y7" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z7" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="H7" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L7" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N7" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O7" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P7" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q7" s="34" t="s">
+      <c r="AA7" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="R7" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S7" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T7" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U7" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V7" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W7" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X7" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y7" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z7" s="34" t="s">
+      <c r="AB7" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="AA7" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB7" s="40" t="s">
-        <v>172</v>
-      </c>
       <c r="AC7" s="39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD7" s="30">
         <v>765</v>
@@ -3038,10 +3069,10 @@
         <v>20</v>
       </c>
       <c r="AG7" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH7" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI7" s="35">
         <v>43831</v>
@@ -3050,224 +3081,224 @@
         <v>45293</v>
       </c>
       <c r="AK7" s="39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AL7" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM7" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM7" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN7" s="30">
         <v>110</v>
       </c>
       <c r="AO7" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP7" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP7" s="34" t="s">
+      <c r="AQ7" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ7" s="34" t="s">
-        <v>102</v>
-      </c>
       <c r="AR7" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
       </c>
       <c r="AS7" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT7" s="38">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT7" s="38" t="str">
         <f t="shared" si="4"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AU7" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV7" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="AV7" s="43" t="s">
-        <v>136</v>
-      </c>
       <c r="AW7" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX7" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX7" s="30" t="s">
+      <c r="AY7" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY7" s="30" t="s">
+      <c r="AZ7" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ7" s="30" t="s">
+      <c r="BA7" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA7" s="30" t="s">
-        <v>109</v>
-      </c>
       <c r="BB7" s="30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BC7" s="35">
         <v>46022</v>
       </c>
       <c r="BD7" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BE7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BF7" s="44">
         <v>9893790851</v>
       </c>
       <c r="BG7" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH7" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI7" s="30">
         <v>47678965521</v>
       </c>
       <c r="BJ7" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK7" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BM7" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN7" s="45">
         <v>35591</v>
       </c>
       <c r="BO7" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP7" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ7" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR7" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR7" s="30" t="s">
+      <c r="BS7" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS7" s="47" t="s">
+      <c r="BT7" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT7" s="30" t="s">
+      <c r="BU7" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU7" s="46" t="s">
+      <c r="BV7" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV7" s="46" t="s">
+      <c r="BW7" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW7" s="30" t="s">
+      <c r="BX7" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX7" s="30" t="s">
+      <c r="BY7" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY7" s="30" t="s">
+      <c r="BZ7" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ7" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="8" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="C8" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="31" t="s">
+      <c r="G8" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="H8" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L8" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O8" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R8" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S8" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T8" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U8" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V8" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W8" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X8" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y8" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z8" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="H8" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L8" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O8" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P8" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q8" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="R8" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S8" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T8" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U8" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V8" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W8" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X8" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y8" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z8" s="34" t="s">
+      <c r="AA8" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB8" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="AA8" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB8" s="40" t="s">
-        <v>181</v>
-      </c>
       <c r="AC8" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD8" s="30">
         <v>765</v>
@@ -3279,10 +3310,10 @@
         <v>40</v>
       </c>
       <c r="AG8" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH8" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI8" s="35">
         <v>43831</v>
@@ -3291,224 +3322,224 @@
         <v>45293</v>
       </c>
       <c r="AK8" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL8" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL8" s="39" t="s">
-        <v>98</v>
-      </c>
       <c r="AM8" s="41">
-        <f>TODAY()+365</f>
-        <v>46149</v>
+        <f ca="1">TODAY()+365</f>
+        <v>46175</v>
       </c>
       <c r="AN8" s="30">
         <v>110</v>
       </c>
       <c r="AO8" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP8" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP8" s="34" t="s">
+      <c r="AQ8" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ8" s="34" t="s">
-        <v>102</v>
-      </c>
       <c r="AR8" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
       </c>
       <c r="AS8" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
       </c>
       <c r="AT8" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AU8" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV8" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="AV8" s="43" t="s">
-        <v>136</v>
-      </c>
       <c r="AW8" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX8" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX8" s="30" t="s">
+      <c r="AY8" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY8" s="30" t="s">
+      <c r="AZ8" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ8" s="30" t="s">
+      <c r="BA8" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA8" s="30" t="s">
+      <c r="BB8" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC8" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD8" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE8" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB8" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC8" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD8" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE8" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF8" s="44">
         <v>9893790852</v>
       </c>
       <c r="BG8" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH8" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI8" s="30">
         <v>47678965522</v>
       </c>
       <c r="BJ8" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK8" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BM8" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN8" s="45">
         <v>35591</v>
       </c>
       <c r="BO8" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP8" s="45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BQ8" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR8" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR8" s="30" t="s">
+      <c r="BS8" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS8" s="47" t="s">
+      <c r="BT8" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT8" s="30" t="s">
+      <c r="BU8" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU8" s="46" t="s">
+      <c r="BV8" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV8" s="46" t="s">
+      <c r="BW8" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW8" s="30" t="s">
+      <c r="BX8" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX8" s="30" t="s">
+      <c r="BY8" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY8" s="30" t="s">
+      <c r="BZ8" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ8" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="9" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="43" t="s">
         <v>183</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="C9" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="29" t="s">
+      <c r="G9" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L9" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="G9" s="32" t="s">
+      <c r="M9" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O9" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R9" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S9" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T9" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U9" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V9" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W9" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X9" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y9" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z9" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA9" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB9" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="H9" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K9" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O9" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P9" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q9" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="R9" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S9" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T9" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U9" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V9" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W9" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X9" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y9" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z9" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA9" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB9" s="40" t="s">
-        <v>187</v>
-      </c>
       <c r="AC9" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD9" s="30">
         <v>765</v>
@@ -3520,10 +3551,10 @@
         <v>40</v>
       </c>
       <c r="AG9" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH9" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI9" s="35">
         <v>43831</v>
@@ -3532,224 +3563,224 @@
         <v>45293</v>
       </c>
       <c r="AK9" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL9" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM9" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM9" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN9" s="30">
         <v>110</v>
       </c>
       <c r="AO9" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP9" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP9" s="34" t="s">
+      <c r="AQ9" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ9" s="34" t="s">
+      <c r="AR9" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
+      </c>
+      <c r="AS9" s="42">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT9" s="38" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="AU9" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AR9" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="AS9" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT9" s="38">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="AU9" s="34" t="s">
-        <v>103</v>
-      </c>
       <c r="AV9" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AW9" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX9" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX9" s="30" t="s">
+      <c r="AY9" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY9" s="30" t="s">
+      <c r="AZ9" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ9" s="30" t="s">
+      <c r="BA9" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA9" s="30" t="s">
+      <c r="BB9" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC9" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD9" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE9" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB9" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC9" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD9" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE9" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF9" s="44">
         <v>9893790853</v>
       </c>
       <c r="BG9" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH9" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI9" s="30">
         <v>47678965523</v>
       </c>
       <c r="BJ9" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK9" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BM9" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN9" s="45">
         <v>35591</v>
       </c>
       <c r="BO9" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP9" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ9" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR9" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR9" s="30" t="s">
+      <c r="BS9" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS9" s="47" t="s">
+      <c r="BT9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT9" s="30" t="s">
+      <c r="BU9" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU9" s="46" t="s">
+      <c r="BV9" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV9" s="46" t="s">
+      <c r="BW9" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW9" s="30" t="s">
+      <c r="BX9" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX9" s="30" t="s">
+      <c r="BY9" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY9" s="30" t="s">
+      <c r="BZ9" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ9" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="10" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="C10" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="29" t="s">
+      <c r="G10" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L10" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="G10" s="32" t="s">
+      <c r="M10" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O10" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R10" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S10" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T10" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U10" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V10" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W10" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X10" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y10" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z10" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA10" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB10" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K10" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L10" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M10" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O10" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P10" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S10" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T10" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U10" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V10" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W10" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X10" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y10" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z10" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA10" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB10" s="40" t="s">
-        <v>195</v>
-      </c>
       <c r="AC10" s="39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD10" s="30">
         <v>765</v>
@@ -3761,10 +3792,10 @@
         <v>10</v>
       </c>
       <c r="AG10" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH10" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI10" s="35">
         <v>43831</v>
@@ -3773,224 +3804,224 @@
         <v>45293</v>
       </c>
       <c r="AK10" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL10" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL10" s="39" t="s">
+      <c r="AM10" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM10" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN10" s="30">
         <v>110</v>
       </c>
       <c r="AO10" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP10" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP10" s="34" t="s">
+      <c r="AQ10" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ10" s="34" t="s">
+      <c r="AR10" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
+      </c>
+      <c r="AS10" s="42">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT10" s="38" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="AU10" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AR10" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="AS10" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT10" s="38">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="AU10" s="34" t="s">
-        <v>103</v>
-      </c>
       <c r="AV10" s="43" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AW10" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX10" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX10" s="30" t="s">
+      <c r="AY10" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY10" s="30" t="s">
+      <c r="AZ10" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ10" s="30" t="s">
+      <c r="BA10" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA10" s="30" t="s">
+      <c r="BB10" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC10" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD10" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE10" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB10" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC10" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD10" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE10" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF10" s="44">
         <v>9893790854</v>
       </c>
       <c r="BG10" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH10" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI10" s="30">
         <v>47678965524</v>
       </c>
       <c r="BJ10" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK10" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BM10" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN10" s="45">
         <v>35591</v>
       </c>
       <c r="BO10" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP10" s="45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BQ10" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR10" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR10" s="30" t="s">
+      <c r="BS10" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS10" s="47" t="s">
+      <c r="BT10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT10" s="30" t="s">
+      <c r="BU10" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU10" s="46" t="s">
+      <c r="BV10" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV10" s="46" t="s">
+      <c r="BW10" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW10" s="30" t="s">
+      <c r="BX10" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX10" s="30" t="s">
+      <c r="BY10" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY10" s="30" t="s">
+      <c r="BZ10" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ10" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="11" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="C11" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C11" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="29" t="s">
+      <c r="G11" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L11" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="G11" s="32" t="s">
+      <c r="M11" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O11" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P11" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q11" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R11" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S11" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T11" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U11" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V11" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W11" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X11" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y11" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z11" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA11" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB11" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="H11" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J11" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L11" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M11" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N11" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O11" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P11" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q11" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="R11" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S11" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T11" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U11" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V11" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W11" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X11" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y11" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z11" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA11" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB11" s="40" t="s">
-        <v>202</v>
-      </c>
       <c r="AC11" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD11" s="30">
         <v>765</v>
@@ -4002,10 +4033,10 @@
         <v>40</v>
       </c>
       <c r="AG11" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH11" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI11" s="35">
         <v>43831</v>
@@ -4014,225 +4045,225 @@
         <v>45293</v>
       </c>
       <c r="AK11" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL11" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL11" s="39" t="s">
-        <v>98</v>
-      </c>
       <c r="AM11" s="41">
-        <f>TODAY()+365</f>
-        <v>46149</v>
+        <f ca="1">TODAY()+365</f>
+        <v>46175</v>
       </c>
       <c r="AN11" s="30">
         <v>110</v>
       </c>
       <c r="AO11" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AP11" s="34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AQ11" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="AR11" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
+      </c>
+      <c r="AS11" s="42">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT11" s="38">
+        <f t="shared" ca="1" si="4"/>
+        <v>46175</v>
+      </c>
+      <c r="AU11" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AR11" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="AS11" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT11" s="38">
-        <f t="shared" si="4"/>
-        <v>46149</v>
-      </c>
-      <c r="AU11" s="34" t="s">
-        <v>103</v>
-      </c>
       <c r="AV11" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AW11" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX11" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX11" s="30" t="s">
+      <c r="AY11" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY11" s="30" t="s">
+      <c r="AZ11" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ11" s="30" t="s">
+      <c r="BA11" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA11" s="30" t="s">
+      <c r="BB11" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC11" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD11" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE11" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB11" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC11" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD11" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE11" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF11" s="44">
         <v>9893790855</v>
       </c>
       <c r="BG11" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH11" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI11" s="30">
         <v>47678965525</v>
       </c>
       <c r="BJ11" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK11" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BM11" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN11" s="45">
         <v>35591</v>
       </c>
       <c r="BO11" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP11" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ11" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR11" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR11" s="30" t="s">
+      <c r="BS11" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS11" s="47" t="s">
+      <c r="BT11" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT11" s="30" t="s">
+      <c r="BU11" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU11" s="46" t="s">
+      <c r="BV11" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV11" s="46" t="s">
+      <c r="BW11" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW11" s="30" t="s">
+      <c r="BX11" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX11" s="30" t="s">
+      <c r="BY11" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY11" s="30" t="s">
+      <c r="BZ11" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ11" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="12" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="C12" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="C12" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="29" t="s">
+      <c r="G12" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L12" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="G12" s="32" t="s">
+      <c r="M12" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O12" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P12" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q12" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R12" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S12" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T12" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U12" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V12" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W12" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X12" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y12" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z12" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA12" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB12" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="H12" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J12" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K12" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L12" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M12" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N12" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O12" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P12" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q12" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="R12" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S12" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T12" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U12" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V12" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W12" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X12" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y12" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z12" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA12" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB12" s="40" t="s">
-        <v>209</v>
-      </c>
       <c r="AC12" s="39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD12" s="30">
         <v>765</v>
@@ -4244,10 +4275,10 @@
         <v>30</v>
       </c>
       <c r="AG12" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH12" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI12" s="35">
         <v>43831</v>
@@ -4256,224 +4287,224 @@
         <v>45293</v>
       </c>
       <c r="AK12" s="39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AL12" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM12" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM12" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN12" s="30">
         <v>110</v>
       </c>
       <c r="AO12" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP12" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP12" s="34" t="s">
+      <c r="AQ12" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ12" s="34" t="s">
+      <c r="AR12" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
+      </c>
+      <c r="AS12" s="42">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT12" s="38" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="AU12" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AR12" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="AS12" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT12" s="38">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="AU12" s="34" t="s">
-        <v>103</v>
-      </c>
       <c r="AV12" s="43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AW12" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX12" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX12" s="30" t="s">
+      <c r="AY12" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY12" s="30" t="s">
+      <c r="AZ12" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ12" s="30" t="s">
+      <c r="BA12" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA12" s="30" t="s">
+      <c r="BB12" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC12" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD12" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE12" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB12" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC12" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD12" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE12" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF12" s="44">
         <v>9893790856</v>
       </c>
       <c r="BG12" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH12" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI12" s="30">
         <v>47678965526</v>
       </c>
       <c r="BJ12" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK12" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BM12" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN12" s="45">
         <v>35591</v>
       </c>
       <c r="BO12" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP12" s="45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BQ12" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR12" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR12" s="30" t="s">
+      <c r="BS12" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS12" s="47" t="s">
+      <c r="BT12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT12" s="30" t="s">
+      <c r="BU12" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU12" s="46" t="s">
+      <c r="BV12" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV12" s="46" t="s">
+      <c r="BW12" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW12" s="30" t="s">
+      <c r="BX12" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX12" s="30" t="s">
+      <c r="BY12" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY12" s="30" t="s">
+      <c r="BZ12" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ12" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="13" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="C13" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="C13" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="29" t="s">
+      <c r="G13" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L13" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="G13" s="32" t="s">
+      <c r="M13" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N13" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O13" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P13" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q13" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R13" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S13" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U13" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="V13" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W13" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X13" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y13" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z13" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA13" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB13" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="H13" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J13" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K13" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L13" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M13" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N13" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O13" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P13" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q13" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="R13" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S13" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T13" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U13" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V13" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W13" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X13" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y13" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z13" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA13" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB13" s="40" t="s">
-        <v>217</v>
-      </c>
       <c r="AC13" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD13" s="30">
         <v>765</v>
@@ -4485,10 +4516,10 @@
         <v>40</v>
       </c>
       <c r="AG13" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH13" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI13" s="35">
         <v>43831</v>
@@ -4497,224 +4528,224 @@
         <v>45293</v>
       </c>
       <c r="AK13" s="39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL13" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM13" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM13" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN13" s="30">
         <v>110</v>
       </c>
       <c r="AO13" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP13" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP13" s="34" t="s">
+      <c r="AQ13" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ13" s="34" t="s">
+      <c r="AR13" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
+      </c>
+      <c r="AS13" s="42">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT13" s="38" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="AU13" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AR13" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="AS13" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT13" s="38">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="AU13" s="34" t="s">
-        <v>103</v>
-      </c>
       <c r="AV13" s="43" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AW13" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX13" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX13" s="30" t="s">
+      <c r="AY13" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY13" s="30" t="s">
+      <c r="AZ13" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ13" s="30" t="s">
+      <c r="BA13" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA13" s="30" t="s">
+      <c r="BB13" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC13" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD13" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE13" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB13" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC13" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD13" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE13" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF13" s="44">
         <v>9893790857</v>
       </c>
       <c r="BG13" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH13" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI13" s="30">
         <v>47678965527</v>
       </c>
       <c r="BJ13" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK13" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="BM13" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN13" s="45">
         <v>35591</v>
       </c>
       <c r="BO13" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP13" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ13" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR13" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR13" s="30" t="s">
+      <c r="BS13" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS13" s="47" t="s">
+      <c r="BT13" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT13" s="30" t="s">
+      <c r="BU13" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU13" s="46" t="s">
+      <c r="BV13" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV13" s="46" t="s">
+      <c r="BW13" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW13" s="30" t="s">
+      <c r="BX13" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX13" s="30" t="s">
+      <c r="BY13" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY13" s="30" t="s">
+      <c r="BZ13" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ13" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="14" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="43" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="C14" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="29" t="s">
+      <c r="G14" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L14" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="H14" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="34" t="s">
+      <c r="M14" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N14" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O14" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P14" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q14" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R14" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S14" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T14" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="J14" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K14" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L14" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M14" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N14" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O14" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P14" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q14" s="34" t="s">
+      <c r="U14" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R14" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S14" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T14" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U14" s="35" t="s">
+      <c r="V14" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V14" s="37" t="s">
+      <c r="W14" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X14" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y14" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="W14" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X14" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y14" s="34" t="s">
+      <c r="Z14" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z14" s="34" t="s">
-        <v>93</v>
-      </c>
       <c r="AA14" s="30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AB14" s="40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AC14" s="39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD14" s="30">
         <v>765</v>
@@ -4726,10 +4757,10 @@
         <v>20</v>
       </c>
       <c r="AG14" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH14" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI14" s="35">
         <v>43831</v>
@@ -4738,224 +4769,224 @@
         <v>45293</v>
       </c>
       <c r="AK14" s="39" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AL14" s="39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AM14" s="41">
-        <f>TODAY()+365</f>
-        <v>46149</v>
+        <f ca="1">TODAY()+365</f>
+        <v>46175</v>
       </c>
       <c r="AN14" s="30">
         <v>110</v>
       </c>
       <c r="AO14" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP14" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP14" s="34" t="s">
+      <c r="AQ14" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ14" s="34" t="s">
+      <c r="AR14" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
+      </c>
+      <c r="AS14" s="42">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT14" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="AU14" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AR14" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="AS14" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT14" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="AU14" s="34" t="s">
-        <v>103</v>
-      </c>
       <c r="AV14" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AW14" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX14" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX14" s="30" t="s">
+      <c r="AY14" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY14" s="30" t="s">
+      <c r="AZ14" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ14" s="30" t="s">
+      <c r="BA14" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA14" s="30" t="s">
-        <v>109</v>
-      </c>
       <c r="BB14" s="30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BC14" s="35">
         <v>46022</v>
       </c>
       <c r="BD14" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BE14" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BF14" s="44">
         <v>9893790858</v>
       </c>
       <c r="BG14" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH14" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI14" s="30">
         <v>47678965528</v>
       </c>
       <c r="BJ14" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK14" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="BM14" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN14" s="45">
         <v>35591</v>
       </c>
       <c r="BO14" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP14" s="45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BQ14" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR14" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR14" s="30" t="s">
+      <c r="BS14" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS14" s="47" t="s">
+      <c r="BT14" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT14" s="30" t="s">
+      <c r="BU14" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU14" s="46" t="s">
+      <c r="BV14" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV14" s="46" t="s">
+      <c r="BW14" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW14" s="30" t="s">
+      <c r="BX14" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX14" s="30" t="s">
+      <c r="BY14" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY14" s="30" t="s">
+      <c r="BZ14" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ14" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="15" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="B15" s="43" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="C15" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="C15" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="29" t="s">
+      <c r="G15" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L15" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="G15" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="H15" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" s="34" t="s">
+      <c r="M15" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N15" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O15" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P15" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q15" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R15" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S15" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T15" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="J15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K15" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L15" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M15" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N15" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O15" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P15" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q15" s="34" t="s">
+      <c r="U15" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R15" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S15" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U15" s="35" t="s">
+      <c r="V15" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V15" s="37" t="s">
+      <c r="W15" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X15" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y15" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="W15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X15" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y15" s="34" t="s">
+      <c r="Z15" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z15" s="34" t="s">
+      <c r="AA15" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB15" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AA15" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB15" s="40" t="s">
-        <v>94</v>
-      </c>
       <c r="AC15" s="39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD15" s="30">
         <v>765</v>
@@ -4967,10 +4998,10 @@
         <v>10</v>
       </c>
       <c r="AG15" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH15" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI15" s="35">
         <v>43831</v>
@@ -4979,225 +5010,225 @@
         <v>45293</v>
       </c>
       <c r="AK15" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL15" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL15" s="39" t="s">
-        <v>98</v>
-      </c>
       <c r="AM15" s="41">
-        <f>TODAY()+365</f>
-        <v>46149</v>
+        <f ca="1">TODAY()+365</f>
+        <v>46175</v>
       </c>
       <c r="AN15" s="30">
         <v>110</v>
       </c>
       <c r="AO15" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AP15" s="39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AQ15" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="AR15" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
+      </c>
+      <c r="AS15" s="42">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT15" s="38">
+        <f t="shared" ca="1" si="4"/>
+        <v>46175</v>
+      </c>
+      <c r="AU15" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AR15" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="AS15" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT15" s="38">
-        <f t="shared" si="4"/>
-        <v>46149</v>
-      </c>
-      <c r="AU15" s="34" t="s">
+      <c r="AV15" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="AV15" s="43" t="s">
+      <c r="AW15" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AW15" s="30" t="s">
+      <c r="AX15" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX15" s="30" t="s">
+      <c r="AY15" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY15" s="30" t="s">
+      <c r="AZ15" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ15" s="30" t="s">
+      <c r="BA15" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA15" s="30" t="s">
+      <c r="BB15" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC15" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD15" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE15" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB15" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC15" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD15" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE15" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF15" s="44">
         <v>9893790859</v>
       </c>
       <c r="BG15" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH15" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI15" s="30">
         <v>47678965529</v>
       </c>
       <c r="BJ15" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK15" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BM15" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN15" s="45">
         <v>35591</v>
       </c>
       <c r="BO15" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP15" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ15" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR15" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR15" s="30" t="s">
+      <c r="BS15" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS15" s="47" t="s">
+      <c r="BT15" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT15" s="30" t="s">
+      <c r="BU15" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU15" s="46" t="s">
+      <c r="BV15" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV15" s="46" t="s">
+      <c r="BW15" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW15" s="30" t="s">
+      <c r="BX15" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX15" s="30" t="s">
+      <c r="BY15" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY15" s="30" t="s">
+      <c r="BZ15" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ15" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="16" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="43" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="C16" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="C16" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="29" t="s">
+      <c r="G16" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45779</v>
+      </c>
+      <c r="L16" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="H16" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I16" s="34" t="s">
+      <c r="M16" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N16" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="O16" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="P16" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q16" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="R16" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S16" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T16" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="J16" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K16" s="35">
-        <f t="shared" si="0"/>
-        <v>45753</v>
-      </c>
-      <c r="L16" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M16" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N16" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="O16" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="P16" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q16" s="34" t="s">
+      <c r="U16" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R16" s="34" t="s">
+      <c r="V16" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="W16" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X16" s="38">
+        <f t="shared" ca="1" si="1"/>
+        <v>45779</v>
+      </c>
+      <c r="Y16" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z16" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA16" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="S16" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T16" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U16" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="V16" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="W16" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="X16" s="38">
-        <f t="shared" si="1"/>
-        <v>45753</v>
-      </c>
-      <c r="Y16" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z16" s="34" t="s">
+      <c r="AB16" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AA16" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB16" s="40" t="s">
+      <c r="AC16" s="39" t="s">
         <v>94</v>
-      </c>
-      <c r="AC16" s="39" t="s">
-        <v>95</v>
       </c>
       <c r="AD16" s="30">
         <v>765</v>
@@ -5209,10 +5240,10 @@
         <v>40</v>
       </c>
       <c r="AG16" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH16" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI16" s="35">
         <v>43831</v>
@@ -5221,136 +5252,136 @@
         <v>45293</v>
       </c>
       <c r="AK16" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL16" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL16" s="39" t="s">
+      <c r="AM16" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM16" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN16" s="30">
         <v>110</v>
       </c>
       <c r="AO16" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP16" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP16" s="34" t="s">
+      <c r="AQ16" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="AQ16" s="34" t="s">
+      <c r="AR16" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>45779</v>
+      </c>
+      <c r="AS16" s="42">
+        <f t="shared" ca="1" si="3"/>
+        <v>45779</v>
+      </c>
+      <c r="AT16" s="38" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="AU16" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AR16" s="42">
-        <f t="shared" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="AS16" s="42">
-        <f t="shared" si="3"/>
-        <v>45753</v>
-      </c>
-      <c r="AT16" s="38">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="AU16" s="34" t="s">
+      <c r="AV16" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="AV16" s="43" t="s">
+      <c r="AW16" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AW16" s="30" t="s">
+      <c r="AX16" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX16" s="30" t="s">
+      <c r="AY16" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY16" s="30" t="s">
+      <c r="AZ16" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ16" s="30" t="s">
+      <c r="BA16" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA16" s="30" t="s">
-        <v>109</v>
-      </c>
       <c r="BB16" s="30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BC16" s="35">
         <v>46022</v>
       </c>
       <c r="BD16" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BE16" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BF16" s="44">
         <v>9893790860</v>
       </c>
       <c r="BG16" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH16" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI16" s="30">
         <v>47678965530</v>
       </c>
       <c r="BJ16" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK16" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BM16" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN16" s="45">
         <v>35591</v>
       </c>
       <c r="BO16" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP16" s="45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BQ16" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR16" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR16" s="30" t="s">
+      <c r="BS16" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS16" s="47" t="s">
+      <c r="BT16" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT16" s="30" t="s">
+      <c r="BU16" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU16" s="46" t="s">
+      <c r="BV16" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV16" s="46" t="s">
+      <c r="BW16" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW16" s="30" t="s">
+      <c r="BX16" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX16" s="30" t="s">
+      <c r="BY16" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY16" s="30" t="s">
+      <c r="BZ16" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ16" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="17" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
@@ -5430,7 +5461,7 @@
       <c r="BY17" s="48"/>
       <c r="BZ17" s="48"/>
     </row>
-    <row r="18" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="48"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
@@ -5510,7 +5541,7 @@
       <c r="BY18" s="48"/>
       <c r="BZ18" s="48"/>
     </row>
-    <row r="19" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
@@ -5590,7 +5621,7 @@
       <c r="BY19" s="48"/>
       <c r="BZ19" s="48"/>
     </row>
-    <row r="20" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="48"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
@@ -5670,7 +5701,7 @@
       <c r="BY20" s="48"/>
       <c r="BZ20" s="48"/>
     </row>
-    <row r="21" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="48"/>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
@@ -5750,7 +5781,7 @@
       <c r="BY21" s="48"/>
       <c r="BZ21" s="48"/>
     </row>
-    <row r="22" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="48"/>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
@@ -5830,7 +5861,7 @@
       <c r="BY22" s="48"/>
       <c r="BZ22" s="48"/>
     </row>
-    <row r="23" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="48"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
@@ -5910,7 +5941,7 @@
       <c r="BY23" s="48"/>
       <c r="BZ23" s="48"/>
     </row>
-    <row r="24" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="48"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
@@ -5990,7 +6021,7 @@
       <c r="BY24" s="48"/>
       <c r="BZ24" s="48"/>
     </row>
-    <row r="25" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="48"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
@@ -6070,7 +6101,7 @@
       <c r="BY25" s="48"/>
       <c r="BZ25" s="48"/>
     </row>
-    <row r="26" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="48"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -6150,7 +6181,7 @@
       <c r="BY26" s="48"/>
       <c r="BZ26" s="48"/>
     </row>
-    <row r="27" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="48"/>
       <c r="B27" s="48"/>
       <c r="C27" s="48"/>
@@ -6230,7 +6261,7 @@
       <c r="BY27" s="48"/>
       <c r="BZ27" s="48"/>
     </row>
-    <row r="28" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="48"/>
       <c r="B28" s="48"/>
       <c r="C28" s="48"/>
@@ -6310,7 +6341,7 @@
       <c r="BY28" s="48"/>
       <c r="BZ28" s="48"/>
     </row>
-    <row r="29" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="48"/>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
@@ -6390,7 +6421,7 @@
       <c r="BY29" s="48"/>
       <c r="BZ29" s="48"/>
     </row>
-    <row r="30" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="48"/>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
@@ -6470,7 +6501,7 @@
       <c r="BY30" s="48"/>
       <c r="BZ30" s="48"/>
     </row>
-    <row r="31" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="48"/>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
@@ -6550,7 +6581,7 @@
       <c r="BY31" s="48"/>
       <c r="BZ31" s="48"/>
     </row>
-    <row r="32" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="48"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
@@ -6630,7 +6661,7 @@
       <c r="BY32" s="48"/>
       <c r="BZ32" s="48"/>
     </row>
-    <row r="33" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="48"/>
       <c r="B33" s="48"/>
       <c r="C33" s="48"/>
@@ -6710,7 +6741,7 @@
       <c r="BY33" s="48"/>
       <c r="BZ33" s="48"/>
     </row>
-    <row r="34" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="48"/>
       <c r="B34" s="48"/>
       <c r="C34" s="48"/>
@@ -6790,7 +6821,7 @@
       <c r="BY34" s="48"/>
       <c r="BZ34" s="48"/>
     </row>
-    <row r="35" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="48"/>
       <c r="B35" s="48"/>
       <c r="C35" s="48"/>
@@ -6870,7 +6901,7 @@
       <c r="BY35" s="48"/>
       <c r="BZ35" s="48"/>
     </row>
-    <row r="36" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="48"/>
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
@@ -6950,7 +6981,7 @@
       <c r="BY36" s="48"/>
       <c r="BZ36" s="48"/>
     </row>
-    <row r="37" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="48"/>
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
@@ -7030,7 +7061,7 @@
       <c r="BY37" s="48"/>
       <c r="BZ37" s="48"/>
     </row>
-    <row r="38" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="48"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
@@ -7110,7 +7141,7 @@
       <c r="BY38" s="48"/>
       <c r="BZ38" s="48"/>
     </row>
-    <row r="39" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="48"/>
       <c r="B39" s="48"/>
       <c r="C39" s="48"/>
@@ -7190,7 +7221,7 @@
       <c r="BY39" s="48"/>
       <c r="BZ39" s="48"/>
     </row>
-    <row r="40" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="48"/>
       <c r="B40" s="48"/>
       <c r="C40" s="48"/>
@@ -7270,7 +7301,7 @@
       <c r="BY40" s="48"/>
       <c r="BZ40" s="48"/>
     </row>
-    <row r="41" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="48"/>
       <c r="B41" s="48"/>
       <c r="C41" s="48"/>
@@ -7350,7 +7381,7 @@
       <c r="BY41" s="48"/>
       <c r="BZ41" s="48"/>
     </row>
-    <row r="42" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="48"/>
       <c r="B42" s="48"/>
       <c r="C42" s="48"/>
@@ -7430,7 +7461,7 @@
       <c r="BY42" s="48"/>
       <c r="BZ42" s="48"/>
     </row>
-    <row r="43" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="48"/>
       <c r="B43" s="48"/>
       <c r="C43" s="48"/>
@@ -7510,7 +7541,7 @@
       <c r="BY43" s="48"/>
       <c r="BZ43" s="48"/>
     </row>
-    <row r="44" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="48"/>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
@@ -7590,7 +7621,7 @@
       <c r="BY44" s="48"/>
       <c r="BZ44" s="48"/>
     </row>
-    <row r="45" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="48"/>
       <c r="B45" s="48"/>
       <c r="C45" s="48"/>
@@ -7670,7 +7701,7 @@
       <c r="BY45" s="48"/>
       <c r="BZ45" s="48"/>
     </row>
-    <row r="46" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="48"/>
       <c r="B46" s="48"/>
       <c r="C46" s="48"/>
@@ -7750,7 +7781,7 @@
       <c r="BY46" s="48"/>
       <c r="BZ46" s="48"/>
     </row>
-    <row r="47" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="48"/>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
@@ -7830,7 +7861,7 @@
       <c r="BY47" s="48"/>
       <c r="BZ47" s="48"/>
     </row>
-    <row r="48" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="48"/>
       <c r="B48" s="48"/>
       <c r="C48" s="48"/>
@@ -7910,7 +7941,7 @@
       <c r="BY48" s="48"/>
       <c r="BZ48" s="48"/>
     </row>
-    <row r="49" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="48"/>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
@@ -7990,7 +8021,7 @@
       <c r="BY49" s="48"/>
       <c r="BZ49" s="48"/>
     </row>
-    <row r="50" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="48"/>
       <c r="B50" s="48"/>
       <c r="C50" s="48"/>
@@ -8070,7 +8101,7 @@
       <c r="BY50" s="48"/>
       <c r="BZ50" s="48"/>
     </row>
-    <row r="51" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="48"/>
       <c r="B51" s="48"/>
       <c r="C51" s="48"/>
@@ -8150,7 +8181,7 @@
       <c r="BY51" s="48"/>
       <c r="BZ51" s="48"/>
     </row>
-    <row r="52" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="48"/>
       <c r="B52" s="48"/>
       <c r="C52" s="48"/>
@@ -8230,7 +8261,7 @@
       <c r="BY52" s="48"/>
       <c r="BZ52" s="48"/>
     </row>
-    <row r="53" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="48"/>
       <c r="B53" s="48"/>
       <c r="C53" s="48"/>
@@ -8310,7 +8341,7 @@
       <c r="BY53" s="48"/>
       <c r="BZ53" s="48"/>
     </row>
-    <row r="54" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:78" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="48"/>
       <c r="B54" s="48"/>
       <c r="C54" s="48"/>
@@ -8392,6 +8423,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{AD340D60-483A-48AA-B6AA-1FB7856AB1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{73A4B905-1302-4225-9A8F-79A6B08D92A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="225">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -262,175 +262,185 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10698396</t>
+    <t xml:space="preserve">Test failed for 'PolandOne TwentyFiveJuneTenF' Employee:{undefined}Error: [31mTimed out 5000ms waiting for [39m[2mexpect([22m[31mlocator[39m[2m).[22mtoBeVisible[2m()[22m
+Locator: locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[1]')
+Expected: visible
+Received: &lt;element(s) not found&gt;
+Call log:
+  [2m- expect.toBeVisible with timeout 5000ms[22m
+[2m  - waiting for locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[1]')[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>765 Retail Team 1 (Jizur Buzese (10226524) (Inherited))</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>PolandOne</t>
+  </si>
+  <si>
+    <t>TwentyFiveJuneTenF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698 980 460 </t>
+  </si>
+  <si>
+    <t>Landline</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Automation Street Name</t>
+  </si>
+  <si>
+    <t>Greater Poland</t>
+  </si>
+  <si>
+    <t>00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warsaw  </t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Test001@gmail.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Retail Assistant_NEW</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>ZasadniczaSzkołaZawodowa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RE029_NEW2 </t>
+  </si>
+  <si>
+    <t>5 Days</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Automation Comments here….</t>
+  </si>
+  <si>
+    <t>Open-ended</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>94 Retail Operative</t>
+  </si>
+  <si>
+    <t>16 Mens Accessories</t>
+  </si>
+  <si>
+    <t>0202</t>
+  </si>
+  <si>
+    <t>Ulga podatkowa obowiązuje</t>
+  </si>
+  <si>
+    <t>1/12 kwoty zmniejszającej podatek</t>
+  </si>
+  <si>
+    <t>Standardowy</t>
+  </si>
+  <si>
+    <t>PESEL</t>
+  </si>
+  <si>
+    <t>Tax ID Number</t>
+  </si>
+  <si>
+    <t>Personal Identity (PESEL) Number</t>
+  </si>
+  <si>
+    <t>ID Card</t>
+  </si>
+  <si>
+    <t>GHE456411</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Married (Poland)</t>
+  </si>
+  <si>
+    <t>01/01/2019</t>
+  </si>
+  <si>
+    <t>Citizen (Poland)</t>
+  </si>
+  <si>
+    <t>Bank of Poland</t>
+  </si>
+  <si>
+    <t>NBPLPLPW</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>11111111111111111111111101</t>
+  </si>
+  <si>
+    <t>PL09109024023899695521479863</t>
+  </si>
+  <si>
+    <t>Defaulted</t>
+  </si>
+  <si>
+    <t>Please select a Poland Pay Group</t>
+  </si>
+  <si>
+    <t>PL Monthly</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Test_2</t>
+  </si>
+  <si>
+    <t>10698476</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>765 Retail Team 1 (Jizur Buzese (10226524) (Inherited))</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>PolandOne</t>
-  </si>
-  <si>
-    <t>TwentyFiveJuneTwoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698 980 460 </t>
-  </si>
-  <si>
-    <t>Landline</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Automation Street Name</t>
-  </si>
-  <si>
-    <t>Greater Poland</t>
-  </si>
-  <si>
-    <t>00001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warsaw  </t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Test001@gmail.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Retail Assistant_NEW</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>ZasadniczaSzkołaZawodowa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RE029_NEW2 </t>
-  </si>
-  <si>
-    <t>5 Days</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Automation Comments here….</t>
-  </si>
-  <si>
-    <t>Open-ended</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>94 Retail Operative</t>
-  </si>
-  <si>
-    <t>16 Mens Accessories</t>
-  </si>
-  <si>
-    <t>0202</t>
-  </si>
-  <si>
-    <t>Ulga podatkowa obowiązuje</t>
-  </si>
-  <si>
-    <t>1/12 kwoty zmniejszającej podatek</t>
-  </si>
-  <si>
-    <t>Standardowy</t>
-  </si>
-  <si>
-    <t>PESEL</t>
-  </si>
-  <si>
-    <t>Tax ID Number</t>
-  </si>
-  <si>
-    <t>Personal Identity (PESEL) Number</t>
-  </si>
-  <si>
-    <t>ID Card</t>
-  </si>
-  <si>
-    <t>GHE456366</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Married (Poland)</t>
-  </si>
-  <si>
-    <t>01/01/2019</t>
-  </si>
-  <si>
-    <t>Citizen (Poland)</t>
-  </si>
-  <si>
-    <t>Bank of Poland</t>
-  </si>
-  <si>
-    <t>NBPLPLPW</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>11111111111111111111111101</t>
-  </si>
-  <si>
-    <t>PL09109024023899695521479863</t>
-  </si>
-  <si>
-    <t>Defaulted</t>
-  </si>
-  <si>
-    <t>Please select a Poland Pay Group</t>
-  </si>
-  <si>
-    <t>PL Monthly</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Test_2</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>765 Store Management (Jizur Buzese (10226524))</t>
   </si>
   <si>
     <t>PolandTwo</t>
   </si>
   <si>
-    <t>TwentyFiveJuneTwo</t>
-  </si>
-  <si>
-    <t>Auto 25777904</t>
+    <t>TwentyFiveJuneTen</t>
+  </si>
+  <si>
+    <t>Auto 66228638</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -445,7 +455,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>GHE456367</t>
+    <t>GHE456412</t>
   </si>
   <si>
     <t>Female</t>
@@ -457,19 +467,22 @@
     <t>Test_3</t>
   </si>
   <si>
-    <t>10698398</t>
+    <t xml:space="preserve">Test failed for 'PolandThree TwentyFiveJuneTen' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//label[contains(.,\'Hire Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
+</t>
   </si>
   <si>
     <t>PolandThree</t>
   </si>
   <si>
-    <t>Auto 71021656</t>
+    <t>Auto 72722622</t>
   </si>
   <si>
     <t>Department Manager_NEW</t>
   </si>
   <si>
-    <t>GHE456368</t>
+    <t>GHE456413</t>
   </si>
   <si>
     <t>01/01/2020</t>
@@ -478,13 +491,13 @@
     <t>Test_4</t>
   </si>
   <si>
-    <t>Test failed for 'PolandFour TwentyFiveJuneTwo' Employee:{}TypeError: Cannot read properties of undefined (reading 'toString')</t>
+    <t>Test failed for 'PolandFour TwentyFiveJuneTen' Employee:{}TypeError: Cannot read properties of undefined (reading 'toString')</t>
   </si>
   <si>
     <t>PolandFour</t>
   </si>
   <si>
-    <t>Auto 46361787</t>
+    <t>Auto 87262994</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -499,19 +512,19 @@
     <t>RE023_NEW</t>
   </si>
   <si>
-    <t>GHE456369</t>
+    <t>GHE456399</t>
   </si>
   <si>
     <t>Test_5</t>
   </si>
   <si>
-    <t>10698399</t>
+    <t>10698477</t>
   </si>
   <si>
     <t>PolandFive</t>
   </si>
   <si>
-    <t>Auto 59695475</t>
+    <t>Auto 17641870</t>
   </si>
   <si>
     <t>Assistant Store Manager_NEW</t>
@@ -520,7 +533,7 @@
     <t>RE035_NEW</t>
   </si>
   <si>
-    <t>GHE456370</t>
+    <t>GHE456400</t>
   </si>
   <si>
     <t>01/01/2021</t>
@@ -529,10 +542,13 @@
     <t>Test_6</t>
   </si>
   <si>
+    <t>10698478</t>
+  </si>
+  <si>
     <t>PolandSix</t>
   </si>
   <si>
-    <t>Auto 32134447</t>
+    <t>Auto 55924303</t>
   </si>
   <si>
     <t>In-Store Visual Merchandising Manager_NEW</t>
@@ -544,28 +560,31 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>GHE456371</t>
+    <t>GHE456401</t>
   </si>
   <si>
     <t>Test_7</t>
   </si>
   <si>
+    <t>10698479</t>
+  </si>
+  <si>
     <t>PolandSeven</t>
   </si>
   <si>
-    <t>Auto 13336789</t>
+    <t>Auto 80547148</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
   </si>
   <si>
-    <t>GHE456372</t>
+    <t>GHE456402</t>
   </si>
   <si>
     <t>Test_8</t>
   </si>
   <si>
-    <t>10698402</t>
+    <t>10698480</t>
   </si>
   <si>
     <t>PolandEight</t>
@@ -580,13 +599,374 @@
     <t>250 Human Resources Retail</t>
   </si>
   <si>
-    <t>GHE456373</t>
+    <t>GHE456403</t>
   </si>
   <si>
     <t>Test_9</t>
   </si>
   <si>
-    <t>10698403</t>
+    <t xml:space="preserve">Test failed for 'PolandNine TwentyFiveJuneTen' Employee:{10698481}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//div[@data-automation-id=\'titleText\'][contains(./text(),\'Add Bank Details\')]')[22m
+[2m  -   locator resolved to &lt;div class="css-t9tuu3" data-automation-id="titleText"&gt;Add Bank Details&lt;/div&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="mh6g0f epf0sd82 css-bcl7hk"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1k479cq" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+</t>
   </si>
   <si>
     <t>PolandNine</t>
@@ -598,13 +978,381 @@
     <t>258 Cash Office</t>
   </si>
   <si>
-    <t>GHE456374</t>
+    <t>GHE456404</t>
   </si>
   <si>
     <t>Test_10</t>
   </si>
   <si>
-    <t>10698404</t>
+    <t xml:space="preserve">Test failed for 'PolandTen TwentyFiveJuneTen' Employee:{10698482}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByRole('button', { name: 'Approve' })[22m
+[2m  -   locator resolved to &lt;button type="button" title="Approve" class="WIWM WEDO W…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class=" css-roynbj"&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+</t>
   </si>
   <si>
     <t>PolandTen</t>
@@ -616,13 +1364,13 @@
     <t>Trial</t>
   </si>
   <si>
-    <t>GHE456375</t>
+    <t>GHE456405</t>
   </si>
   <si>
     <t>Test_11</t>
   </si>
   <si>
-    <t>10698405</t>
+    <t>10698483</t>
   </si>
   <si>
     <t>PolandEleven</t>
@@ -637,13 +1385,13 @@
     <t>253 Supervisors</t>
   </si>
   <si>
-    <t>GHE456376</t>
+    <t>GHE456406</t>
   </si>
   <si>
     <t>Test_12</t>
   </si>
   <si>
-    <t>10698406</t>
+    <t>10698485</t>
   </si>
   <si>
     <t>PolandTwleve</t>
@@ -658,13 +1406,13 @@
     <t>256 Visual Merchandising</t>
   </si>
   <si>
-    <t>GHE456377</t>
+    <t>GHE456407</t>
   </si>
   <si>
     <t>Test_13</t>
   </si>
   <si>
-    <t>10698407</t>
+    <t>10698486</t>
   </si>
   <si>
     <t>PolandThirteen</t>
@@ -673,31 +1421,31 @@
     <t>RE043_NEW</t>
   </si>
   <si>
-    <t>GHE456378</t>
+    <t>GHE456408</t>
   </si>
   <si>
     <t>Test_14</t>
   </si>
   <si>
-    <t>10698408</t>
+    <t>10698487</t>
   </si>
   <si>
     <t>PolandFourteen</t>
   </si>
   <si>
-    <t>GHE456379</t>
+    <t>GHE456409</t>
   </si>
   <si>
     <t>Test_15</t>
   </si>
   <si>
-    <t>10698409</t>
+    <t>10698489</t>
   </si>
   <si>
     <t>PolandFifteen</t>
   </si>
   <si>
-    <t>GHE456380</t>
+    <t>GHE456410</t>
   </si>
 </sst>
 </file>
@@ -1682,7 +2430,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:78" s="25" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>75</v>
       </c>
@@ -1715,7 +2463,7 @@
       </c>
       <c r="K2" s="35">
         <f t="shared" ref="K2:K16" ca="1" si="0">TODAY()-31</f>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L2" s="30" t="s">
         <v>79</v>
@@ -1755,7 +2503,7 @@
       </c>
       <c r="X2" s="38">
         <f t="shared" ref="X2:X16" ca="1" si="1">K2</f>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y2" s="34" t="s">
         <v>92</v>
@@ -1816,11 +2564,11 @@
       </c>
       <c r="AR2" s="42">
         <f t="shared" ref="AR2:AR16" ca="1" si="2">X2</f>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS2" s="42">
         <f t="shared" ref="AS2:AS16" ca="1" si="3">X2</f>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT2" s="38" t="str">
         <f t="shared" ref="AT2:AT16" si="4">AM2</f>
@@ -1860,7 +2608,7 @@
         <v>110</v>
       </c>
       <c r="BF2" s="44">
-        <v>9893790916</v>
+        <v>9893790961</v>
       </c>
       <c r="BG2" s="30" t="s">
         <v>79</v>
@@ -1869,7 +2617,7 @@
         <v>111</v>
       </c>
       <c r="BI2" s="30">
-        <v>47678965586</v>
+        <v>47678965631</v>
       </c>
       <c r="BJ2" s="30" t="s">
         <v>79</v>
@@ -1927,23 +2675,23 @@
       <c r="A3" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="27">
-        <v>10698397</v>
+      <c r="B3" s="27" t="s">
+        <v>128</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>82</v>
@@ -1956,7 +2704,7 @@
       </c>
       <c r="K3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L3" s="30" t="s">
         <v>79</v>
@@ -1996,19 +2744,19 @@
       </c>
       <c r="X3" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y3" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z3" s="34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AA3" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB3" s="40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC3" s="39" t="s">
         <v>95</v>
@@ -2035,7 +2783,7 @@
         <v>45293</v>
       </c>
       <c r="AK3" s="39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AL3" s="39" t="s">
         <v>98</v>
@@ -2057,21 +2805,21 @@
       </c>
       <c r="AR3" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS3" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT3" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU3" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AV3" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AW3" s="30" t="s">
         <v>105</v>
@@ -2101,7 +2849,7 @@
         <v>110</v>
       </c>
       <c r="BF3" s="44">
-        <v>9893790917</v>
+        <v>9893790962</v>
       </c>
       <c r="BG3" s="30" t="s">
         <v>79</v>
@@ -2110,7 +2858,7 @@
         <v>111</v>
       </c>
       <c r="BI3" s="30">
-        <v>47678965587</v>
+        <v>47678965632</v>
       </c>
       <c r="BJ3" s="30" t="s">
         <v>79</v>
@@ -2119,16 +2867,16 @@
         <v>112</v>
       </c>
       <c r="BL3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BM3" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BN3" s="45">
         <v>35591</v>
       </c>
       <c r="BO3" s="45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BP3" s="45" t="s">
         <v>99</v>
@@ -2164,27 +2912,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:78" s="25" customFormat="1" ht="400.2" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" s="28" t="s">
         <v>77</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>82</v>
@@ -2197,7 +2945,7 @@
       </c>
       <c r="K4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L4" s="30" t="s">
         <v>79</v>
@@ -2237,19 +2985,19 @@
       </c>
       <c r="X4" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y4" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z4" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AA4" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB4" s="40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AC4" s="39" t="s">
         <v>95</v>
@@ -2298,21 +3046,21 @@
       </c>
       <c r="AR4" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS4" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT4" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU4" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AV4" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AW4" s="30" t="s">
         <v>105</v>
@@ -2342,7 +3090,7 @@
         <v>110</v>
       </c>
       <c r="BF4" s="44">
-        <v>9893790918</v>
+        <v>9893790963</v>
       </c>
       <c r="BG4" s="30" t="s">
         <v>79</v>
@@ -2351,7 +3099,7 @@
         <v>111</v>
       </c>
       <c r="BI4" s="30">
-        <v>47678965588</v>
+        <v>47678965633</v>
       </c>
       <c r="BJ4" s="30" t="s">
         <v>79</v>
@@ -2360,7 +3108,7 @@
         <v>112</v>
       </c>
       <c r="BL4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BM4" s="39" t="s">
         <v>114</v>
@@ -2372,7 +3120,7 @@
         <v>115</v>
       </c>
       <c r="BP4" s="45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BQ4" s="46" t="s">
         <v>117</v>
@@ -2407,25 +3155,25 @@
     </row>
     <row r="5" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>82</v>
@@ -2438,7 +3186,7 @@
       </c>
       <c r="K5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L5" s="30" t="s">
         <v>79</v>
@@ -2478,22 +3226,22 @@
       </c>
       <c r="X5" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y5" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z5" s="34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA5" s="30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB5" s="40" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AC5" s="39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AD5" s="30">
         <v>765</v>
@@ -2517,14 +3265,14 @@
         <v>45293</v>
       </c>
       <c r="AK5" s="39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AL5" s="39" t="s">
         <v>98</v>
       </c>
       <c r="AM5" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="AN5" s="30">
         <v>110</v>
@@ -2540,20 +3288,20 @@
       </c>
       <c r="AR5" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS5" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT5" s="38" t="s">
         <v>99</v>
       </c>
       <c r="AU5" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AV5" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AW5" s="30" t="s">
         <v>105</v>
@@ -2583,7 +3331,7 @@
         <v>110</v>
       </c>
       <c r="BF5" s="44">
-        <v>9893790919</v>
+        <v>9893790949</v>
       </c>
       <c r="BG5" s="30" t="s">
         <v>79</v>
@@ -2592,7 +3340,7 @@
         <v>111</v>
       </c>
       <c r="BI5" s="30">
-        <v>47678965589</v>
+        <v>47678965619</v>
       </c>
       <c r="BJ5" s="30" t="s">
         <v>79</v>
@@ -2601,16 +3349,16 @@
         <v>112</v>
       </c>
       <c r="BL5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BM5" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BN5" s="45">
         <v>35591</v>
       </c>
       <c r="BO5" s="45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BP5" s="45" t="s">
         <v>99</v>
@@ -2648,25 +3396,25 @@
     </row>
     <row r="6" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>82</v>
@@ -2679,7 +3427,7 @@
       </c>
       <c r="K6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L6" s="30" t="s">
         <v>79</v>
@@ -2719,19 +3467,19 @@
       </c>
       <c r="X6" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y6" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z6" s="34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA6" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB6" s="40" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AC6" s="39" t="s">
         <v>95</v>
@@ -2758,7 +3506,7 @@
         <v>45293</v>
       </c>
       <c r="AK6" s="39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL6" s="39" t="s">
         <v>98</v>
@@ -2780,21 +3528,21 @@
       </c>
       <c r="AR6" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS6" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT6" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU6" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AV6" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AW6" s="30" t="s">
         <v>105</v>
@@ -2824,7 +3572,7 @@
         <v>110</v>
       </c>
       <c r="BF6" s="44">
-        <v>9893790920</v>
+        <v>9893790950</v>
       </c>
       <c r="BG6" s="30" t="s">
         <v>79</v>
@@ -2833,7 +3581,7 @@
         <v>111</v>
       </c>
       <c r="BI6" s="30">
-        <v>47678965590</v>
+        <v>47678965620</v>
       </c>
       <c r="BJ6" s="30" t="s">
         <v>79</v>
@@ -2842,7 +3590,7 @@
         <v>112</v>
       </c>
       <c r="BL6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BM6" s="39" t="s">
         <v>114</v>
@@ -2854,7 +3602,7 @@
         <v>115</v>
       </c>
       <c r="BP6" s="45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BQ6" s="46" t="s">
         <v>117</v>
@@ -2889,25 +3637,25 @@
     </row>
     <row r="7" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="48">
-        <v>10698400</v>
+        <v>165</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>166</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>82</v>
@@ -2920,7 +3668,7 @@
       </c>
       <c r="K7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L7" s="30" t="s">
         <v>79</v>
@@ -2960,22 +3708,22 @@
       </c>
       <c r="X7" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y7" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z7" s="34" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AA7" s="39" t="s">
         <v>90</v>
       </c>
       <c r="AB7" s="40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AC7" s="39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AD7" s="30">
         <v>765</v>
@@ -2999,7 +3747,7 @@
         <v>45293</v>
       </c>
       <c r="AK7" s="39" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AL7" s="39" t="s">
         <v>98</v>
@@ -3021,21 +3769,21 @@
       </c>
       <c r="AR7" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS7" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT7" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU7" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AV7" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AW7" s="30" t="s">
         <v>105</v>
@@ -3053,7 +3801,7 @@
         <v>109</v>
       </c>
       <c r="BB7" s="30" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BC7" s="35">
         <v>46022</v>
@@ -3065,7 +3813,7 @@
         <v>110</v>
       </c>
       <c r="BF7" s="44">
-        <v>9893790921</v>
+        <v>9893790951</v>
       </c>
       <c r="BG7" s="30" t="s">
         <v>79</v>
@@ -3074,7 +3822,7 @@
         <v>111</v>
       </c>
       <c r="BI7" s="30">
-        <v>47678965591</v>
+        <v>47678965621</v>
       </c>
       <c r="BJ7" s="30" t="s">
         <v>79</v>
@@ -3083,16 +3831,16 @@
         <v>112</v>
       </c>
       <c r="BL7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BM7" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BN7" s="45">
         <v>35591</v>
       </c>
       <c r="BO7" s="45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BP7" s="45" t="s">
         <v>99</v>
@@ -3130,25 +3878,25 @@
     </row>
     <row r="8" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="48">
-        <v>10698401</v>
+        <v>173</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>174</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>79</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>82</v>
@@ -3161,7 +3909,7 @@
       </c>
       <c r="K8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L8" s="30" t="s">
         <v>79</v>
@@ -3201,19 +3949,19 @@
       </c>
       <c r="X8" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y8" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z8" s="34" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB8" s="40" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AC8" s="39" t="s">
         <v>95</v>
@@ -3247,7 +3995,7 @@
       </c>
       <c r="AM8" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="AN8" s="30">
         <v>110</v>
@@ -3263,20 +4011,20 @@
       </c>
       <c r="AR8" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS8" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT8" s="38" t="s">
         <v>99</v>
       </c>
       <c r="AU8" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AV8" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AW8" s="30" t="s">
         <v>105</v>
@@ -3306,7 +4054,7 @@
         <v>110</v>
       </c>
       <c r="BF8" s="44">
-        <v>9893790922</v>
+        <v>9893790952</v>
       </c>
       <c r="BG8" s="30" t="s">
         <v>79</v>
@@ -3315,7 +4063,7 @@
         <v>111</v>
       </c>
       <c r="BI8" s="30">
-        <v>47678965592</v>
+        <v>47678965622</v>
       </c>
       <c r="BJ8" s="30" t="s">
         <v>79</v>
@@ -3324,7 +4072,7 @@
         <v>112</v>
       </c>
       <c r="BL8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="BM8" s="39" t="s">
         <v>114</v>
@@ -3336,7 +4084,7 @@
         <v>115</v>
       </c>
       <c r="BP8" s="45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BQ8" s="46" t="s">
         <v>117</v>
@@ -3371,13 +4119,13 @@
     </row>
     <row r="9" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="43" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>78</v>
@@ -3386,10 +4134,10 @@
         <v>79</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>82</v>
@@ -3402,7 +4150,7 @@
       </c>
       <c r="K9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>79</v>
@@ -3442,7 +4190,7 @@
       </c>
       <c r="X9" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y9" s="34" t="s">
         <v>92</v>
@@ -3454,7 +4202,7 @@
         <v>90</v>
       </c>
       <c r="AB9" s="40" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AC9" s="39" t="s">
         <v>95</v>
@@ -3481,7 +4229,7 @@
         <v>45293</v>
       </c>
       <c r="AK9" s="39" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AL9" s="39" t="s">
         <v>98</v>
@@ -3503,11 +4251,11 @@
       </c>
       <c r="AR9" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS9" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT9" s="38" t="str">
         <f t="shared" si="4"/>
@@ -3517,7 +4265,7 @@
         <v>103</v>
       </c>
       <c r="AV9" s="43" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AW9" s="30" t="s">
         <v>105</v>
@@ -3547,7 +4295,7 @@
         <v>110</v>
       </c>
       <c r="BF9" s="44">
-        <v>9893790923</v>
+        <v>9893790953</v>
       </c>
       <c r="BG9" s="30" t="s">
         <v>79</v>
@@ -3556,7 +4304,7 @@
         <v>111</v>
       </c>
       <c r="BI9" s="30">
-        <v>47678965593</v>
+        <v>47678965623</v>
       </c>
       <c r="BJ9" s="30" t="s">
         <v>79</v>
@@ -3565,16 +4313,16 @@
         <v>112</v>
       </c>
       <c r="BL9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="BM9" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BN9" s="45">
         <v>35591</v>
       </c>
       <c r="BO9" s="45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BP9" s="45" t="s">
         <v>99</v>
@@ -3610,12 +4358,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:78" s="25" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>184</v>
+        <v>186</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>187</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>77</v>
@@ -3627,10 +4375,10 @@
         <v>79</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>82</v>
@@ -3643,7 +4391,7 @@
       </c>
       <c r="K10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L10" s="30" t="s">
         <v>79</v>
@@ -3683,7 +4431,7 @@
       </c>
       <c r="X10" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y10" s="34" t="s">
         <v>92</v>
@@ -3695,10 +4443,10 @@
         <v>90</v>
       </c>
       <c r="AB10" s="40" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AC10" s="39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AD10" s="30">
         <v>765</v>
@@ -3744,11 +4492,11 @@
       </c>
       <c r="AR10" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS10" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT10" s="38" t="str">
         <f t="shared" si="4"/>
@@ -3758,7 +4506,7 @@
         <v>103</v>
       </c>
       <c r="AV10" s="43" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AW10" s="30" t="s">
         <v>105</v>
@@ -3788,7 +4536,7 @@
         <v>110</v>
       </c>
       <c r="BF10" s="44">
-        <v>9893790924</v>
+        <v>9893790954</v>
       </c>
       <c r="BG10" s="30" t="s">
         <v>79</v>
@@ -3797,7 +4545,7 @@
         <v>111</v>
       </c>
       <c r="BI10" s="30">
-        <v>47678965594</v>
+        <v>47678965624</v>
       </c>
       <c r="BJ10" s="30" t="s">
         <v>79</v>
@@ -3806,7 +4554,7 @@
         <v>112</v>
       </c>
       <c r="BL10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="BM10" s="39" t="s">
         <v>114</v>
@@ -3818,7 +4566,7 @@
         <v>115</v>
       </c>
       <c r="BP10" s="45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BQ10" s="46" t="s">
         <v>117</v>
@@ -3851,12 +4599,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:78" s="25" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>190</v>
+        <v>192</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>193</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>77</v>
@@ -3868,10 +4616,10 @@
         <v>79</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>82</v>
@@ -3884,7 +4632,7 @@
       </c>
       <c r="K11" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L11" s="30" t="s">
         <v>79</v>
@@ -3924,7 +4672,7 @@
       </c>
       <c r="X11" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y11" s="34" t="s">
         <v>92</v>
@@ -3933,10 +4681,10 @@
         <v>93</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB11" s="40" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AC11" s="39" t="s">
         <v>95</v>
@@ -3970,7 +4718,7 @@
       </c>
       <c r="AM11" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="AN11" s="30">
         <v>110</v>
@@ -3979,28 +4727,28 @@
         <v>100</v>
       </c>
       <c r="AP11" s="34" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AQ11" s="34" t="s">
         <v>102</v>
       </c>
       <c r="AR11" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS11" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT11" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="AU11" s="34" t="s">
         <v>103</v>
       </c>
       <c r="AV11" s="43" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AW11" s="30" t="s">
         <v>105</v>
@@ -4030,7 +4778,7 @@
         <v>110</v>
       </c>
       <c r="BF11" s="44">
-        <v>9893790925</v>
+        <v>9893790955</v>
       </c>
       <c r="BG11" s="30" t="s">
         <v>79</v>
@@ -4039,7 +4787,7 @@
         <v>111</v>
       </c>
       <c r="BI11" s="30">
-        <v>47678965595</v>
+        <v>47678965625</v>
       </c>
       <c r="BJ11" s="30" t="s">
         <v>79</v>
@@ -4048,16 +4796,16 @@
         <v>112</v>
       </c>
       <c r="BL11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="BM11" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BN11" s="45">
         <v>35591</v>
       </c>
       <c r="BO11" s="45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BP11" s="45" t="s">
         <v>99</v>
@@ -4095,13 +4843,13 @@
     </row>
     <row r="12" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="43" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D12" s="29" t="s">
         <v>78</v>
@@ -4110,10 +4858,10 @@
         <v>79</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H12" s="33" t="s">
         <v>82</v>
@@ -4126,7 +4874,7 @@
       </c>
       <c r="K12" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L12" s="30" t="s">
         <v>79</v>
@@ -4166,7 +4914,7 @@
       </c>
       <c r="X12" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y12" s="34" t="s">
         <v>92</v>
@@ -4178,10 +4926,10 @@
         <v>90</v>
       </c>
       <c r="AB12" s="40" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AC12" s="39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AD12" s="30">
         <v>765</v>
@@ -4205,7 +4953,7 @@
         <v>45293</v>
       </c>
       <c r="AK12" s="39" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AL12" s="39" t="s">
         <v>98</v>
@@ -4227,11 +4975,11 @@
       </c>
       <c r="AR12" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS12" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT12" s="38" t="str">
         <f t="shared" si="4"/>
@@ -4241,7 +4989,7 @@
         <v>103</v>
       </c>
       <c r="AV12" s="43" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AW12" s="30" t="s">
         <v>105</v>
@@ -4271,7 +5019,7 @@
         <v>110</v>
       </c>
       <c r="BF12" s="44">
-        <v>9893790926</v>
+        <v>9893790956</v>
       </c>
       <c r="BG12" s="30" t="s">
         <v>79</v>
@@ -4280,7 +5028,7 @@
         <v>111</v>
       </c>
       <c r="BI12" s="30">
-        <v>47678965596</v>
+        <v>47678965626</v>
       </c>
       <c r="BJ12" s="30" t="s">
         <v>79</v>
@@ -4289,7 +5037,7 @@
         <v>112</v>
       </c>
       <c r="BL12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="BM12" s="39" t="s">
         <v>114</v>
@@ -4301,7 +5049,7 @@
         <v>115</v>
       </c>
       <c r="BP12" s="45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BQ12" s="46" t="s">
         <v>117</v>
@@ -4336,13 +5084,13 @@
     </row>
     <row r="13" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="43" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D13" s="29" t="s">
         <v>78</v>
@@ -4351,10 +5099,10 @@
         <v>79</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G13" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>82</v>
@@ -4367,7 +5115,7 @@
       </c>
       <c r="K13" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L13" s="30" t="s">
         <v>79</v>
@@ -4407,7 +5155,7 @@
       </c>
       <c r="X13" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y13" s="34" t="s">
         <v>92</v>
@@ -4419,7 +5167,7 @@
         <v>90</v>
       </c>
       <c r="AB13" s="40" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AC13" s="39" t="s">
         <v>95</v>
@@ -4446,7 +5194,7 @@
         <v>45293</v>
       </c>
       <c r="AK13" s="39" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AL13" s="39" t="s">
         <v>98</v>
@@ -4468,11 +5216,11 @@
       </c>
       <c r="AR13" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS13" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT13" s="38" t="str">
         <f t="shared" si="4"/>
@@ -4482,7 +5230,7 @@
         <v>103</v>
       </c>
       <c r="AV13" s="43" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AW13" s="30" t="s">
         <v>105</v>
@@ -4512,7 +5260,7 @@
         <v>110</v>
       </c>
       <c r="BF13" s="44">
-        <v>9893790927</v>
+        <v>9893790957</v>
       </c>
       <c r="BG13" s="30" t="s">
         <v>79</v>
@@ -4521,7 +5269,7 @@
         <v>111</v>
       </c>
       <c r="BI13" s="30">
-        <v>47678965597</v>
+        <v>47678965627</v>
       </c>
       <c r="BJ13" s="30" t="s">
         <v>79</v>
@@ -4530,16 +5278,16 @@
         <v>112</v>
       </c>
       <c r="BL13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="BM13" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BN13" s="45">
         <v>35591</v>
       </c>
       <c r="BO13" s="45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BP13" s="45" t="s">
         <v>99</v>
@@ -4577,13 +5325,13 @@
     </row>
     <row r="14" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="43" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D14" s="29" t="s">
         <v>78</v>
@@ -4592,10 +5340,10 @@
         <v>79</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G14" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H14" s="33" t="s">
         <v>82</v>
@@ -4608,7 +5356,7 @@
       </c>
       <c r="K14" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L14" s="30" t="s">
         <v>79</v>
@@ -4648,7 +5396,7 @@
       </c>
       <c r="X14" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y14" s="34" t="s">
         <v>92</v>
@@ -4657,13 +5405,13 @@
         <v>93</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB14" s="40" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AC14" s="39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AD14" s="30">
         <v>765</v>
@@ -4687,14 +5435,14 @@
         <v>45293</v>
       </c>
       <c r="AK14" s="39" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AL14" s="39" t="s">
         <v>98</v>
       </c>
       <c r="AM14" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="AN14" s="30">
         <v>110</v>
@@ -4710,11 +5458,11 @@
       </c>
       <c r="AR14" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS14" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT14" s="38" t="s">
         <v>99</v>
@@ -4723,7 +5471,7 @@
         <v>103</v>
       </c>
       <c r="AV14" s="43" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AW14" s="30" t="s">
         <v>105</v>
@@ -4741,7 +5489,7 @@
         <v>109</v>
       </c>
       <c r="BB14" s="30" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BC14" s="35">
         <v>46022</v>
@@ -4753,7 +5501,7 @@
         <v>110</v>
       </c>
       <c r="BF14" s="44">
-        <v>9893790928</v>
+        <v>9893790958</v>
       </c>
       <c r="BG14" s="30" t="s">
         <v>79</v>
@@ -4762,7 +5510,7 @@
         <v>111</v>
       </c>
       <c r="BI14" s="30">
-        <v>47678965598</v>
+        <v>47678965628</v>
       </c>
       <c r="BJ14" s="30" t="s">
         <v>79</v>
@@ -4771,7 +5519,7 @@
         <v>112</v>
       </c>
       <c r="BL14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="BM14" s="39" t="s">
         <v>114</v>
@@ -4783,7 +5531,7 @@
         <v>115</v>
       </c>
       <c r="BP14" s="45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BQ14" s="46" t="s">
         <v>117</v>
@@ -4818,13 +5566,13 @@
     </row>
     <row r="15" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="43" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D15" s="29" t="s">
         <v>78</v>
@@ -4833,10 +5581,10 @@
         <v>79</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H15" s="33" t="s">
         <v>82</v>
@@ -4849,7 +5597,7 @@
       </c>
       <c r="K15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L15" s="30" t="s">
         <v>79</v>
@@ -4889,7 +5637,7 @@
       </c>
       <c r="X15" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y15" s="34" t="s">
         <v>92</v>
@@ -4898,13 +5646,13 @@
         <v>93</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB15" s="40" t="s">
         <v>94</v>
       </c>
       <c r="AC15" s="39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AD15" s="30">
         <v>765</v>
@@ -4935,7 +5683,7 @@
       </c>
       <c r="AM15" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="AN15" s="30">
         <v>110</v>
@@ -4944,22 +5692,22 @@
         <v>100</v>
       </c>
       <c r="AP15" s="39" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AQ15" s="34" t="s">
         <v>102</v>
       </c>
       <c r="AR15" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS15" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT15" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="AU15" s="34" t="s">
         <v>103</v>
@@ -4995,7 +5743,7 @@
         <v>110</v>
       </c>
       <c r="BF15" s="44">
-        <v>9893790929</v>
+        <v>9893790959</v>
       </c>
       <c r="BG15" s="30" t="s">
         <v>79</v>
@@ -5004,7 +5752,7 @@
         <v>111</v>
       </c>
       <c r="BI15" s="30">
-        <v>47678965599</v>
+        <v>47678965629</v>
       </c>
       <c r="BJ15" s="30" t="s">
         <v>79</v>
@@ -5013,16 +5761,16 @@
         <v>112</v>
       </c>
       <c r="BL15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="BM15" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BN15" s="45">
         <v>35591</v>
       </c>
       <c r="BO15" s="45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BP15" s="45" t="s">
         <v>99</v>
@@ -5060,13 +5808,13 @@
     </row>
     <row r="16" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="43" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D16" s="29" t="s">
         <v>78</v>
@@ -5075,10 +5823,10 @@
         <v>79</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H16" s="33" t="s">
         <v>82</v>
@@ -5091,7 +5839,7 @@
       </c>
       <c r="K16" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="L16" s="30" t="s">
         <v>79</v>
@@ -5131,7 +5879,7 @@
       </c>
       <c r="X16" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="Y16" s="34" t="s">
         <v>92</v>
@@ -5192,11 +5940,11 @@
       </c>
       <c r="AR16" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AS16" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45787</v>
       </c>
       <c r="AT16" s="38" t="str">
         <f t="shared" si="4"/>
@@ -5224,7 +5972,7 @@
         <v>109</v>
       </c>
       <c r="BB16" s="30" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BC16" s="35">
         <v>46022</v>
@@ -5236,7 +5984,7 @@
         <v>110</v>
       </c>
       <c r="BF16" s="44">
-        <v>9893790930</v>
+        <v>9893790960</v>
       </c>
       <c r="BG16" s="30" t="s">
         <v>79</v>
@@ -5245,7 +5993,7 @@
         <v>111</v>
       </c>
       <c r="BI16" s="30">
-        <v>47678965600</v>
+        <v>47678965630</v>
       </c>
       <c r="BJ16" s="30" t="s">
         <v>79</v>
@@ -5254,7 +6002,7 @@
         <v>112</v>
       </c>
       <c r="BL16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="BM16" s="39" t="s">
         <v>114</v>
@@ -5266,7 +6014,7 @@
         <v>115</v>
       </c>
       <c r="BP16" s="45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BQ16" s="46" t="s">
         <v>117</v>

--- a/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_Poland_Regression_PK14.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{73A4B905-1302-4225-9A8F-79A6B08D92A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9236E543-8E10-44F7-87DE-C69FFE811A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,6 @@
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="224">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -270,9 +269,6 @@
   [2m- expect.toBeVisible with timeout 5000ms[22m
 [2m  - waiting for locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[1]')[22m
 </t>
-  </si>
-  <si>
-    <t>Failed</t>
   </si>
   <si>
     <t>765 Retail Team 1 (Jizur Buzese (10226524) (Inherited))</t>
@@ -2112,89 +2108,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" customWidth="1"/>
-    <col min="4" max="4" width="41.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" customWidth="1"/>
+    <col min="4" max="4" width="41.453125" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="5.6328125" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" customWidth="1"/>
-    <col min="18" max="18" width="11.88671875" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="20.6328125" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" customWidth="1"/>
+    <col min="15" max="15" width="10.81640625" customWidth="1"/>
+    <col min="16" max="16" width="8.08984375" customWidth="1"/>
+    <col min="17" max="17" width="13.1796875" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" customWidth="1"/>
+    <col min="19" max="19" width="8.08984375" customWidth="1"/>
+    <col min="20" max="20" width="5.6328125" customWidth="1"/>
+    <col min="21" max="21" width="12.36328125" customWidth="1"/>
     <col min="22" max="22" width="17" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" customWidth="1"/>
-    <col min="24" max="24" width="10.5546875" customWidth="1"/>
-    <col min="25" max="25" width="8.109375" customWidth="1"/>
-    <col min="26" max="26" width="23.109375" customWidth="1"/>
-    <col min="27" max="27" width="19.6640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6328125" customWidth="1"/>
+    <col min="24" max="24" width="10.54296875" customWidth="1"/>
+    <col min="25" max="25" width="8.08984375" customWidth="1"/>
+    <col min="26" max="26" width="23.08984375" customWidth="1"/>
+    <col min="27" max="27" width="19.6328125" style="1" customWidth="1"/>
     <col min="28" max="28" width="37" customWidth="1"/>
-    <col min="29" max="29" width="9.21875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="8.44140625" customWidth="1"/>
-    <col min="31" max="31" width="12.109375" customWidth="1"/>
-    <col min="32" max="32" width="21.77734375" customWidth="1"/>
-    <col min="33" max="33" width="11.6640625" customWidth="1"/>
-    <col min="34" max="34" width="22.88671875" customWidth="1"/>
-    <col min="35" max="35" width="15.21875" customWidth="1"/>
-    <col min="36" max="36" width="14.109375" customWidth="1"/>
+    <col min="29" max="29" width="9.1796875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="8.453125" customWidth="1"/>
+    <col min="31" max="31" width="12.08984375" customWidth="1"/>
+    <col min="32" max="32" width="21.81640625" customWidth="1"/>
+    <col min="33" max="33" width="11.6328125" customWidth="1"/>
+    <col min="34" max="34" width="22.90625" customWidth="1"/>
+    <col min="35" max="35" width="15.1796875" customWidth="1"/>
+    <col min="36" max="36" width="14.08984375" customWidth="1"/>
     <col min="37" max="37" width="26" customWidth="1"/>
-    <col min="38" max="38" width="13.109375" style="1" customWidth="1"/>
-    <col min="39" max="39" width="19.21875" customWidth="1"/>
-    <col min="40" max="40" width="16.88671875" customWidth="1"/>
-    <col min="41" max="41" width="25.21875" customWidth="1"/>
-    <col min="42" max="42" width="12.6640625" customWidth="1"/>
-    <col min="43" max="43" width="6.5546875" customWidth="1"/>
-    <col min="44" max="44" width="19.33203125" customWidth="1"/>
-    <col min="45" max="45" width="19.109375" customWidth="1"/>
-    <col min="46" max="46" width="15.88671875" customWidth="1"/>
-    <col min="47" max="47" width="19.21875" customWidth="1"/>
-    <col min="48" max="48" width="23.44140625" customWidth="1"/>
-    <col min="49" max="49" width="14.6640625" customWidth="1"/>
-    <col min="50" max="50" width="23.109375" customWidth="1"/>
-    <col min="51" max="51" width="28.6640625" customWidth="1"/>
-    <col min="52" max="52" width="17.77734375" customWidth="1"/>
-    <col min="53" max="53" width="22.44140625" customWidth="1"/>
-    <col min="54" max="54" width="17.77734375" customWidth="1"/>
+    <col min="38" max="38" width="13.08984375" style="1" customWidth="1"/>
+    <col min="39" max="39" width="19.1796875" customWidth="1"/>
+    <col min="40" max="40" width="16.90625" customWidth="1"/>
+    <col min="41" max="41" width="25.1796875" customWidth="1"/>
+    <col min="42" max="42" width="12.6328125" customWidth="1"/>
+    <col min="43" max="43" width="6.54296875" customWidth="1"/>
+    <col min="44" max="44" width="19.36328125" customWidth="1"/>
+    <col min="45" max="45" width="19.08984375" customWidth="1"/>
+    <col min="46" max="46" width="15.90625" customWidth="1"/>
+    <col min="47" max="47" width="19.1796875" customWidth="1"/>
+    <col min="48" max="48" width="23.453125" customWidth="1"/>
+    <col min="49" max="49" width="14.6328125" customWidth="1"/>
+    <col min="50" max="50" width="23.08984375" customWidth="1"/>
+    <col min="51" max="51" width="28.6328125" customWidth="1"/>
+    <col min="52" max="52" width="17.81640625" customWidth="1"/>
+    <col min="53" max="53" width="22.453125" customWidth="1"/>
+    <col min="54" max="54" width="17.81640625" customWidth="1"/>
     <col min="55" max="55" width="18" customWidth="1"/>
-    <col min="56" max="56" width="9.109375" customWidth="1"/>
-    <col min="57" max="57" width="15.5546875" customWidth="1"/>
+    <col min="56" max="56" width="9.08984375" customWidth="1"/>
+    <col min="57" max="57" width="15.54296875" customWidth="1"/>
     <col min="58" max="58" width="12" customWidth="1"/>
-    <col min="59" max="59" width="9.109375" customWidth="1"/>
-    <col min="60" max="60" width="27.33203125" customWidth="1"/>
+    <col min="59" max="59" width="9.08984375" customWidth="1"/>
+    <col min="60" max="60" width="27.36328125" customWidth="1"/>
     <col min="61" max="61" width="12" customWidth="1"/>
-    <col min="62" max="62" width="9.109375" customWidth="1"/>
-    <col min="63" max="63" width="15.5546875" customWidth="1"/>
-    <col min="64" max="64" width="10.77734375" customWidth="1"/>
-    <col min="65" max="65" width="7.33203125" customWidth="1"/>
-    <col min="66" max="66" width="11.33203125" customWidth="1"/>
-    <col min="67" max="67" width="14.21875" customWidth="1"/>
+    <col min="62" max="62" width="9.08984375" customWidth="1"/>
+    <col min="63" max="63" width="15.54296875" customWidth="1"/>
+    <col min="64" max="64" width="10.81640625" customWidth="1"/>
+    <col min="65" max="65" width="7.36328125" customWidth="1"/>
+    <col min="66" max="66" width="11.36328125" customWidth="1"/>
+    <col min="67" max="67" width="14.1796875" customWidth="1"/>
     <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="16.33203125" customWidth="1"/>
-    <col min="70" max="70" width="12.5546875" customWidth="1"/>
-    <col min="71" max="71" width="21.6640625" customWidth="1"/>
-    <col min="72" max="72" width="12.21875" customWidth="1"/>
-    <col min="73" max="73" width="27.44140625" customWidth="1"/>
-    <col min="74" max="74" width="29.21875" customWidth="1"/>
-    <col min="75" max="75" width="8.44140625" customWidth="1"/>
-    <col min="76" max="76" width="26.88671875" customWidth="1"/>
-    <col min="77" max="77" width="22.33203125" customWidth="1"/>
-    <col min="78" max="78" width="23.21875" customWidth="1"/>
+    <col min="69" max="69" width="16.36328125" customWidth="1"/>
+    <col min="70" max="70" width="12.54296875" customWidth="1"/>
+    <col min="71" max="71" width="21.6328125" customWidth="1"/>
+    <col min="72" max="72" width="12.1796875" customWidth="1"/>
+    <col min="73" max="73" width="27.453125" customWidth="1"/>
+    <col min="74" max="74" width="29.1796875" customWidth="1"/>
+    <col min="75" max="75" width="8.453125" customWidth="1"/>
+    <col min="76" max="76" width="26.90625" customWidth="1"/>
+    <col min="77" max="77" width="22.36328125" customWidth="1"/>
+    <col min="78" max="78" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:78" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2430,7 +2426,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:78" s="25" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:78" s="25" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>75</v>
       </c>
@@ -2438,87 +2434,87 @@
         <v>76</v>
       </c>
       <c r="C2" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="E2" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="F2" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="G2" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="H2" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="I2" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="J2" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K2" s="35">
         <f t="shared" ref="K2:K16" ca="1" si="0">TODAY()-31</f>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L2" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M2" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N2" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N2" s="34" t="s">
+      <c r="O2" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="P2" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="Q2" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q2" s="34" t="s">
+      <c r="R2" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S2" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U2" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R2" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S2" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T2" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="35" t="s">
+      <c r="V2" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V2" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W2" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X2" s="38">
         <f t="shared" ref="X2:X16" ca="1" si="1">K2</f>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y2" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z2" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z2" s="34" t="s">
+      <c r="AA2" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB2" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AA2" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB2" s="40" t="s">
+      <c r="AC2" s="39" t="s">
         <v>94</v>
-      </c>
-      <c r="AC2" s="39" t="s">
-        <v>95</v>
       </c>
       <c r="AD2" s="30">
         <v>765</v>
@@ -2530,10 +2526,10 @@
         <v>40</v>
       </c>
       <c r="AG2" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH2" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI2" s="35">
         <v>43831</v>
@@ -2542,224 +2538,224 @@
         <v>45293</v>
       </c>
       <c r="AK2" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL2" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL2" s="39" t="s">
+      <c r="AM2" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM2" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN2" s="30">
         <v>110</v>
       </c>
       <c r="AO2" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP2" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP2" s="34" t="s">
+      <c r="AQ2" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ2" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR2" s="42">
         <f t="shared" ref="AR2:AR16" ca="1" si="2">X2</f>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS2" s="42">
         <f t="shared" ref="AS2:AS16" ca="1" si="3">X2</f>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT2" s="38" t="str">
         <f t="shared" ref="AT2:AT16" si="4">AM2</f>
         <v>N/A</v>
       </c>
       <c r="AU2" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AV2" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="AV2" s="43" t="s">
+      <c r="AW2" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AW2" s="30" t="s">
+      <c r="AX2" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX2" s="30" t="s">
+      <c r="AY2" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY2" s="30" t="s">
+      <c r="AZ2" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ2" s="30" t="s">
+      <c r="BA2" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA2" s="30" t="s">
+      <c r="BB2" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC2" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD2" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE2" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC2" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD2" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE2" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF2" s="44">
         <v>9893790961</v>
       </c>
       <c r="BG2" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH2" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI2" s="30">
         <v>47678965631</v>
       </c>
       <c r="BJ2" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK2" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="BL2" t="s">
         <v>112</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" s="39" t="s">
         <v>113</v>
-      </c>
-      <c r="BM2" s="39" t="s">
-        <v>114</v>
       </c>
       <c r="BN2" s="45">
         <v>35591</v>
       </c>
       <c r="BO2" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP2" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="BP2" s="45" t="s">
+      <c r="BQ2" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="BQ2" s="46" t="s">
+      <c r="BR2" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR2" s="30" t="s">
+      <c r="BS2" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS2" s="47" t="s">
+      <c r="BT2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="30" t="s">
+      <c r="BU2" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU2" s="46" t="s">
+      <c r="BV2" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV2" s="46" t="s">
+      <c r="BW2" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW2" s="30" t="s">
+      <c r="BX2" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX2" s="30" t="s">
+      <c r="BY2" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY2" s="30" t="s">
+      <c r="BZ2" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ2" s="25" t="s">
+    </row>
+    <row r="3" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="43" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="3" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="43" t="s">
+      <c r="B3" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="C3" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="D3" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="E3" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="E3" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="31" t="s">
+      <c r="G3" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>132</v>
-      </c>
       <c r="H3" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="J3" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J3" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M3" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N3" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="34" t="s">
+      <c r="O3" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O3" s="36" t="s">
+      <c r="P3" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P3" s="34" t="s">
+      <c r="Q3" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q3" s="34" t="s">
+      <c r="R3" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S3" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T3" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U3" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R3" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S3" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T3" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" s="35" t="s">
+      <c r="V3" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V3" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W3" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X3" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y3" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Z3" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA3" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB3" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="AA3" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB3" s="40" t="s">
-        <v>134</v>
-      </c>
       <c r="AC3" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD3" s="30">
         <v>765</v>
@@ -2771,10 +2767,10 @@
         <v>40</v>
       </c>
       <c r="AG3" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH3" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI3" s="35">
         <v>43831</v>
@@ -2783,224 +2779,224 @@
         <v>45293</v>
       </c>
       <c r="AK3" s="39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AL3" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM3" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM3" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN3" s="30">
         <v>110</v>
       </c>
       <c r="AO3" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP3" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP3" s="34" t="s">
+      <c r="AQ3" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ3" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR3" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS3" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT3" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU3" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="AV3" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="AV3" s="43" t="s">
-        <v>137</v>
-      </c>
       <c r="AW3" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX3" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX3" s="30" t="s">
+      <c r="AY3" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY3" s="30" t="s">
+      <c r="AZ3" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ3" s="30" t="s">
+      <c r="BA3" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA3" s="30" t="s">
+      <c r="BB3" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC3" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD3" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE3" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB3" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC3" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD3" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE3" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF3" s="44">
         <v>9893790962</v>
       </c>
       <c r="BG3" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH3" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI3" s="30">
         <v>47678965632</v>
       </c>
       <c r="BJ3" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK3" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BM3" s="39" t="s">
         <v>138</v>
-      </c>
-      <c r="BM3" s="39" t="s">
-        <v>139</v>
       </c>
       <c r="BN3" s="45">
         <v>35591</v>
       </c>
       <c r="BO3" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="BP3" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="BQ3" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR3" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS3" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT3" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU3" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV3" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW3" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX3" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BY3" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ3" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:78" s="25" customFormat="1" ht="377" x14ac:dyDescent="0.35">
+      <c r="A4" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="BP3" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="BQ3" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR3" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BS3" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT3" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU3" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV3" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW3" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="BY3" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="BZ3" s="25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:78" s="25" customFormat="1" ht="400.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="43" t="s">
+      <c r="B4" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="C4" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>143</v>
-      </c>
       <c r="G4" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H4" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="J4" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L4" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M4" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N4" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N4" s="34" t="s">
+      <c r="O4" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O4" s="36" t="s">
+      <c r="P4" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P4" s="34" t="s">
+      <c r="Q4" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q4" s="34" t="s">
+      <c r="R4" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S4" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T4" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U4" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R4" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S4" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T4" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U4" s="35" t="s">
+      <c r="V4" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V4" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W4" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X4" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y4" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Z4" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA4" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB4" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="AA4" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB4" s="40" t="s">
-        <v>145</v>
-      </c>
       <c r="AC4" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD4" s="30">
         <v>765</v>
@@ -3012,10 +3008,10 @@
         <v>40</v>
       </c>
       <c r="AG4" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH4" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI4" s="35">
         <v>43831</v>
@@ -3024,224 +3020,224 @@
         <v>45293</v>
       </c>
       <c r="AK4" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL4" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL4" s="39" t="s">
+      <c r="AM4" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM4" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN4" s="30">
         <v>110</v>
       </c>
       <c r="AO4" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP4" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP4" s="34" t="s">
+      <c r="AQ4" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ4" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR4" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS4" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT4" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU4" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="AV4" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="AV4" s="43" t="s">
-        <v>137</v>
-      </c>
       <c r="AW4" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX4" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AY4" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AZ4" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ4" s="30" t="s">
+      <c r="BA4" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA4" s="30" t="s">
+      <c r="BB4" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC4" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD4" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE4" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB4" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC4" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE4" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF4" s="44">
         <v>9893790963</v>
       </c>
       <c r="BG4" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH4" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI4" s="30">
         <v>47678965633</v>
       </c>
       <c r="BJ4" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK4" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BM4" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN4" s="45">
         <v>35591</v>
       </c>
       <c r="BO4" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP4" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="BQ4" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR4" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS4" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT4" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU4" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV4" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW4" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX4" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BY4" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ4" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="BQ4" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR4" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BS4" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT4" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU4" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV4" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW4" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX4" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="BY4" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="BZ4" s="25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="43" t="s">
+      <c r="B5" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="C5" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>150</v>
-      </c>
       <c r="G5" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H5" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="J5" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J5" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M5" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N5" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="O5" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="P5" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P5" s="34" t="s">
+      <c r="Q5" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q5" s="34" t="s">
+      <c r="R5" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S5" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T5" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U5" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R5" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S5" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T5" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U5" s="35" t="s">
+      <c r="V5" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V5" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W5" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X5" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y5" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Z5" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA5" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="AA5" s="30" t="s">
+      <c r="AB5" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="AB5" s="40" t="s">
+      <c r="AC5" s="39" t="s">
         <v>153</v>
-      </c>
-      <c r="AC5" s="39" t="s">
-        <v>154</v>
       </c>
       <c r="AD5" s="30">
         <v>765</v>
@@ -3253,10 +3249,10 @@
         <v>30</v>
       </c>
       <c r="AG5" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH5" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI5" s="35">
         <v>43831</v>
@@ -3265,224 +3261,224 @@
         <v>45293</v>
       </c>
       <c r="AK5" s="39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AL5" s="39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AM5" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="AN5" s="30">
         <v>110</v>
       </c>
       <c r="AO5" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP5" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP5" s="34" t="s">
+      <c r="AQ5" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ5" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR5" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS5" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT5" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AU5" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="AV5" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="AV5" s="43" t="s">
-        <v>137</v>
-      </c>
       <c r="AW5" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX5" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX5" s="30" t="s">
+      <c r="AY5" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY5" s="30" t="s">
+      <c r="AZ5" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ5" s="30" t="s">
+      <c r="BA5" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA5" s="30" t="s">
+      <c r="BB5" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC5" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD5" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE5" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB5" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC5" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD5" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE5" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF5" s="44">
         <v>9893790949</v>
       </c>
       <c r="BG5" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH5" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI5" s="30">
         <v>47678965619</v>
       </c>
       <c r="BJ5" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK5" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BM5" s="39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BN5" s="45">
         <v>35591</v>
       </c>
       <c r="BO5" s="45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BP5" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ5" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR5" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR5" s="30" t="s">
+      <c r="BS5" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS5" s="47" t="s">
+      <c r="BT5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT5" s="30" t="s">
+      <c r="BU5" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU5" s="46" t="s">
+      <c r="BV5" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV5" s="46" t="s">
+      <c r="BW5" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW5" s="30" t="s">
+      <c r="BX5" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX5" s="30" t="s">
+      <c r="BY5" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY5" s="30" t="s">
+      <c r="BZ5" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ5" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="6" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="C6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>159</v>
-      </c>
       <c r="G6" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H6" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="J6" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L6" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M6" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N6" s="34" t="s">
+      <c r="O6" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O6" s="36" t="s">
+      <c r="P6" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P6" s="34" t="s">
+      <c r="Q6" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q6" s="34" t="s">
+      <c r="R6" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S6" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T6" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U6" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R6" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S6" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T6" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U6" s="35" t="s">
+      <c r="V6" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V6" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W6" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X6" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y6" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Z6" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA6" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB6" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="AA6" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB6" s="40" t="s">
-        <v>161</v>
-      </c>
       <c r="AC6" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD6" s="30">
         <v>765</v>
@@ -3494,10 +3490,10 @@
         <v>40</v>
       </c>
       <c r="AG6" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH6" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI6" s="35">
         <v>43831</v>
@@ -3506,224 +3502,224 @@
         <v>45293</v>
       </c>
       <c r="AK6" s="39" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL6" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM6" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM6" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN6" s="30">
         <v>110</v>
       </c>
       <c r="AO6" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP6" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP6" s="34" t="s">
+      <c r="AQ6" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ6" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR6" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS6" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT6" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU6" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="AV6" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="AV6" s="43" t="s">
-        <v>137</v>
-      </c>
       <c r="AW6" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX6" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX6" s="30" t="s">
+      <c r="AY6" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY6" s="30" t="s">
+      <c r="AZ6" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ6" s="30" t="s">
+      <c r="BA6" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA6" s="30" t="s">
+      <c r="BB6" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC6" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD6" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE6" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB6" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC6" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD6" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE6" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF6" s="44">
         <v>9893790950</v>
       </c>
       <c r="BG6" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH6" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI6" s="30">
         <v>47678965620</v>
       </c>
       <c r="BJ6" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK6" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BM6" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN6" s="45">
         <v>35591</v>
       </c>
       <c r="BO6" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP6" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="BQ6" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR6" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS6" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT6" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU6" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV6" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW6" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX6" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BY6" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ6" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="43" t="s">
         <v>164</v>
       </c>
-      <c r="BQ6" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR6" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BS6" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT6" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU6" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV6" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW6" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX6" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="BY6" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="BZ6" s="25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="43" t="s">
+      <c r="B7" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="C7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>167</v>
-      </c>
       <c r="G7" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H7" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="J7" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J7" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L7" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M7" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N7" s="34" t="s">
+      <c r="O7" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O7" s="36" t="s">
+      <c r="P7" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P7" s="34" t="s">
+      <c r="Q7" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q7" s="34" t="s">
+      <c r="R7" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S7" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T7" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U7" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R7" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S7" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T7" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U7" s="35" t="s">
+      <c r="V7" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V7" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W7" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X7" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y7" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Z7" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA7" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB7" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="AA7" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB7" s="40" t="s">
-        <v>169</v>
-      </c>
       <c r="AC7" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD7" s="30">
         <v>765</v>
@@ -3735,10 +3731,10 @@
         <v>20</v>
       </c>
       <c r="AG7" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH7" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI7" s="35">
         <v>43831</v>
@@ -3747,224 +3743,224 @@
         <v>45293</v>
       </c>
       <c r="AK7" s="39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL7" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM7" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM7" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN7" s="30">
         <v>110</v>
       </c>
       <c r="AO7" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP7" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP7" s="34" t="s">
+      <c r="AQ7" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ7" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR7" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS7" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT7" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU7" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="AV7" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="AV7" s="43" t="s">
-        <v>137</v>
-      </c>
       <c r="AW7" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX7" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX7" s="30" t="s">
+      <c r="AY7" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY7" s="30" t="s">
+      <c r="AZ7" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ7" s="30" t="s">
+      <c r="BA7" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA7" s="30" t="s">
-        <v>109</v>
-      </c>
       <c r="BB7" s="30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BC7" s="35">
         <v>46022</v>
       </c>
       <c r="BD7" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BE7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BF7" s="44">
         <v>9893790951</v>
       </c>
       <c r="BG7" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH7" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI7" s="30">
         <v>47678965621</v>
       </c>
       <c r="BJ7" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK7" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BM7" s="39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BN7" s="45">
         <v>35591</v>
       </c>
       <c r="BO7" s="45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BP7" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ7" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR7" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR7" s="30" t="s">
+      <c r="BS7" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS7" s="47" t="s">
+      <c r="BT7" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT7" s="30" t="s">
+      <c r="BU7" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU7" s="46" t="s">
+      <c r="BV7" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV7" s="46" t="s">
+      <c r="BW7" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW7" s="30" t="s">
+      <c r="BX7" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX7" s="30" t="s">
+      <c r="BY7" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY7" s="30" t="s">
+      <c r="BZ7" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ7" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="8" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="C8" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>175</v>
-      </c>
       <c r="G8" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H8" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="J8" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J8" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M8" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N8" s="34" t="s">
+      <c r="O8" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O8" s="36" t="s">
+      <c r="P8" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P8" s="34" t="s">
+      <c r="Q8" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q8" s="34" t="s">
+      <c r="R8" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S8" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T8" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U8" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R8" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S8" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T8" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U8" s="35" t="s">
+      <c r="V8" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V8" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W8" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X8" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y8" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Z8" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA8" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB8" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="AA8" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB8" s="40" t="s">
-        <v>177</v>
-      </c>
       <c r="AC8" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD8" s="30">
         <v>765</v>
@@ -3976,10 +3972,10 @@
         <v>40</v>
       </c>
       <c r="AG8" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH8" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI8" s="35">
         <v>43831</v>
@@ -3988,224 +3984,224 @@
         <v>45293</v>
       </c>
       <c r="AK8" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL8" s="39" t="s">
         <v>97</v>
-      </c>
-      <c r="AL8" s="39" t="s">
-        <v>98</v>
       </c>
       <c r="AM8" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="AN8" s="30">
         <v>110</v>
       </c>
       <c r="AO8" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP8" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP8" s="34" t="s">
+      <c r="AQ8" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ8" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR8" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS8" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT8" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AU8" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="AV8" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="AV8" s="43" t="s">
-        <v>137</v>
-      </c>
       <c r="AW8" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX8" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX8" s="30" t="s">
+      <c r="AY8" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY8" s="30" t="s">
+      <c r="AZ8" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ8" s="30" t="s">
+      <c r="BA8" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA8" s="30" t="s">
+      <c r="BB8" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC8" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD8" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE8" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB8" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC8" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD8" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE8" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF8" s="44">
         <v>9893790952</v>
       </c>
       <c r="BG8" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH8" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI8" s="30">
         <v>47678965622</v>
       </c>
       <c r="BJ8" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK8" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BM8" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN8" s="45">
         <v>35591</v>
       </c>
       <c r="BO8" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP8" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BQ8" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR8" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR8" s="30" t="s">
+      <c r="BS8" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS8" s="47" t="s">
+      <c r="BT8" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT8" s="30" t="s">
+      <c r="BU8" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU8" s="46" t="s">
+      <c r="BV8" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV8" s="46" t="s">
+      <c r="BW8" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW8" s="30" t="s">
+      <c r="BX8" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX8" s="30" t="s">
+      <c r="BY8" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY8" s="30" t="s">
+      <c r="BZ8" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ8" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="9" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="C9" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>181</v>
-      </c>
       <c r="G9" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H9" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="J9" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J9" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N9" s="34" t="s">
+      <c r="O9" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O9" s="36" t="s">
+      <c r="P9" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="34" t="s">
+      <c r="Q9" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q9" s="34" t="s">
+      <c r="R9" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S9" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T9" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U9" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R9" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S9" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T9" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U9" s="35" t="s">
+      <c r="V9" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V9" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W9" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X9" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y9" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z9" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z9" s="34" t="s">
-        <v>93</v>
-      </c>
       <c r="AA9" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AB9" s="40" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC9" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD9" s="30">
         <v>765</v>
@@ -4217,10 +4213,10 @@
         <v>40</v>
       </c>
       <c r="AG9" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH9" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI9" s="35">
         <v>43831</v>
@@ -4229,224 +4225,224 @@
         <v>45293</v>
       </c>
       <c r="AK9" s="39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AL9" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM9" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM9" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN9" s="30">
         <v>110</v>
       </c>
       <c r="AO9" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP9" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP9" s="34" t="s">
+      <c r="AQ9" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ9" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR9" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS9" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT9" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU9" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AV9" s="43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AW9" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX9" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX9" s="30" t="s">
+      <c r="AY9" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY9" s="30" t="s">
+      <c r="AZ9" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ9" s="30" t="s">
+      <c r="BA9" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA9" s="30" t="s">
+      <c r="BB9" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC9" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD9" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE9" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB9" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC9" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD9" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE9" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF9" s="44">
         <v>9893790953</v>
       </c>
       <c r="BG9" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH9" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI9" s="30">
         <v>47678965623</v>
       </c>
       <c r="BJ9" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK9" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BM9" s="39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BN9" s="45">
         <v>35591</v>
       </c>
       <c r="BO9" s="45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BP9" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ9" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR9" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR9" s="30" t="s">
+      <c r="BS9" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS9" s="47" t="s">
+      <c r="BT9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT9" s="30" t="s">
+      <c r="BU9" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU9" s="46" t="s">
+      <c r="BV9" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV9" s="46" t="s">
+      <c r="BW9" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW9" s="30" t="s">
+      <c r="BX9" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX9" s="30" t="s">
+      <c r="BY9" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY9" s="30" t="s">
+      <c r="BZ9" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ9" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="10" spans="1:78" s="25" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:78" s="25" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A10" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="C10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>188</v>
-      </c>
       <c r="G10" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H10" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="J10" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L10" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M10" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N10" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N10" s="34" t="s">
+      <c r="O10" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O10" s="36" t="s">
+      <c r="P10" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="34" t="s">
+      <c r="Q10" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q10" s="34" t="s">
+      <c r="R10" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S10" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T10" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U10" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R10" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S10" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T10" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U10" s="35" t="s">
+      <c r="V10" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V10" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W10" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X10" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y10" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z10" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z10" s="34" t="s">
-        <v>93</v>
-      </c>
       <c r="AA10" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AB10" s="40" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AC10" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD10" s="30">
         <v>765</v>
@@ -4458,10 +4454,10 @@
         <v>10</v>
       </c>
       <c r="AG10" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH10" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI10" s="35">
         <v>43831</v>
@@ -4470,224 +4466,224 @@
         <v>45293</v>
       </c>
       <c r="AK10" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL10" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL10" s="39" t="s">
+      <c r="AM10" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM10" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN10" s="30">
         <v>110</v>
       </c>
       <c r="AO10" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP10" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP10" s="34" t="s">
+      <c r="AQ10" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ10" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR10" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS10" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT10" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU10" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AV10" s="43" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AW10" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX10" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX10" s="30" t="s">
+      <c r="AY10" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY10" s="30" t="s">
+      <c r="AZ10" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ10" s="30" t="s">
+      <c r="BA10" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA10" s="30" t="s">
+      <c r="BB10" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC10" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD10" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE10" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB10" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC10" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD10" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE10" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF10" s="44">
         <v>9893790954</v>
       </c>
       <c r="BG10" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH10" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI10" s="30">
         <v>47678965624</v>
       </c>
       <c r="BJ10" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK10" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="BM10" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN10" s="45">
         <v>35591</v>
       </c>
       <c r="BO10" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP10" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BQ10" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR10" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR10" s="30" t="s">
+      <c r="BS10" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS10" s="47" t="s">
+      <c r="BT10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT10" s="30" t="s">
+      <c r="BU10" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU10" s="46" t="s">
+      <c r="BV10" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV10" s="46" t="s">
+      <c r="BW10" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW10" s="30" t="s">
+      <c r="BX10" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX10" s="30" t="s">
+      <c r="BY10" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY10" s="30" t="s">
+      <c r="BZ10" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ10" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="11" spans="1:78" s="25" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:78" s="25" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A11" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="C11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="C11" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>194</v>
-      </c>
       <c r="G11" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H11" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I11" s="34" t="s">
+      <c r="J11" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J11" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K11" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L11" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M11" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N11" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N11" s="34" t="s">
+      <c r="O11" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O11" s="36" t="s">
+      <c r="P11" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P11" s="34" t="s">
+      <c r="Q11" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q11" s="34" t="s">
+      <c r="R11" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S11" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T11" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U11" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R11" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S11" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T11" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U11" s="35" t="s">
+      <c r="V11" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V11" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W11" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X11" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y11" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z11" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z11" s="34" t="s">
-        <v>93</v>
-      </c>
       <c r="AA11" s="30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AB11" s="40" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AC11" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD11" s="30">
         <v>765</v>
@@ -4699,10 +4695,10 @@
         <v>40</v>
       </c>
       <c r="AG11" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH11" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI11" s="35">
         <v>43831</v>
@@ -4711,225 +4707,225 @@
         <v>45293</v>
       </c>
       <c r="AK11" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL11" s="39" t="s">
         <v>97</v>
-      </c>
-      <c r="AL11" s="39" t="s">
-        <v>98</v>
       </c>
       <c r="AM11" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="AN11" s="30">
         <v>110</v>
       </c>
       <c r="AO11" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AP11" s="34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AQ11" s="34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AR11" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS11" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT11" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="AU11" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AV11" s="43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AW11" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX11" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX11" s="30" t="s">
+      <c r="AY11" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY11" s="30" t="s">
+      <c r="AZ11" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ11" s="30" t="s">
+      <c r="BA11" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA11" s="30" t="s">
+      <c r="BB11" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC11" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD11" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE11" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB11" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC11" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD11" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE11" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF11" s="44">
         <v>9893790955</v>
       </c>
       <c r="BG11" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH11" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI11" s="30">
         <v>47678965625</v>
       </c>
       <c r="BJ11" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK11" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BM11" s="39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BN11" s="45">
         <v>35591</v>
       </c>
       <c r="BO11" s="45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BP11" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ11" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR11" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR11" s="30" t="s">
+      <c r="BS11" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS11" s="47" t="s">
+      <c r="BT11" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT11" s="30" t="s">
+      <c r="BU11" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU11" s="46" t="s">
+      <c r="BV11" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV11" s="46" t="s">
+      <c r="BW11" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW11" s="30" t="s">
+      <c r="BX11" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX11" s="30" t="s">
+      <c r="BY11" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY11" s="30" t="s">
+      <c r="BZ11" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ11" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="12" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="C12" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>200</v>
-      </c>
       <c r="G12" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H12" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="J12" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J12" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K12" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L12" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M12" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N12" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N12" s="34" t="s">
+      <c r="O12" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O12" s="36" t="s">
+      <c r="P12" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P12" s="34" t="s">
+      <c r="Q12" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q12" s="34" t="s">
+      <c r="R12" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S12" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T12" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U12" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R12" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S12" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T12" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U12" s="35" t="s">
+      <c r="V12" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V12" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W12" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X12" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y12" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z12" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z12" s="34" t="s">
-        <v>93</v>
-      </c>
       <c r="AA12" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AB12" s="40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AC12" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD12" s="30">
         <v>765</v>
@@ -4941,10 +4937,10 @@
         <v>30</v>
       </c>
       <c r="AG12" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH12" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI12" s="35">
         <v>43831</v>
@@ -4953,224 +4949,224 @@
         <v>45293</v>
       </c>
       <c r="AK12" s="39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AL12" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM12" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM12" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN12" s="30">
         <v>110</v>
       </c>
       <c r="AO12" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP12" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP12" s="34" t="s">
+      <c r="AQ12" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ12" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR12" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS12" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT12" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU12" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AV12" s="43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AW12" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX12" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX12" s="30" t="s">
+      <c r="AY12" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY12" s="30" t="s">
+      <c r="AZ12" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ12" s="30" t="s">
+      <c r="BA12" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA12" s="30" t="s">
+      <c r="BB12" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC12" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD12" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE12" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB12" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC12" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD12" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE12" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF12" s="44">
         <v>9893790956</v>
       </c>
       <c r="BG12" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH12" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI12" s="30">
         <v>47678965626</v>
       </c>
       <c r="BJ12" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK12" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BM12" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN12" s="45">
         <v>35591</v>
       </c>
       <c r="BO12" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP12" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BQ12" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR12" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR12" s="30" t="s">
+      <c r="BS12" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS12" s="47" t="s">
+      <c r="BT12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT12" s="30" t="s">
+      <c r="BU12" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU12" s="46" t="s">
+      <c r="BV12" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV12" s="46" t="s">
+      <c r="BW12" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW12" s="30" t="s">
+      <c r="BX12" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX12" s="30" t="s">
+      <c r="BY12" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY12" s="30" t="s">
+      <c r="BZ12" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ12" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="13" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="C13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="C13" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>207</v>
-      </c>
       <c r="G13" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H13" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I13" s="34" t="s">
+      <c r="J13" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J13" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K13" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L13" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M13" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N13" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N13" s="34" t="s">
+      <c r="O13" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O13" s="36" t="s">
+      <c r="P13" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P13" s="34" t="s">
+      <c r="Q13" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q13" s="34" t="s">
+      <c r="R13" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S13" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U13" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R13" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S13" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T13" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U13" s="35" t="s">
+      <c r="V13" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V13" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W13" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X13" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y13" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z13" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z13" s="34" t="s">
-        <v>93</v>
-      </c>
       <c r="AA13" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AB13" s="40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AC13" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AD13" s="30">
         <v>765</v>
@@ -5182,10 +5178,10 @@
         <v>40</v>
       </c>
       <c r="AG13" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH13" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI13" s="35">
         <v>43831</v>
@@ -5194,224 +5190,224 @@
         <v>45293</v>
       </c>
       <c r="AK13" s="39" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AL13" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM13" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM13" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN13" s="30">
         <v>110</v>
       </c>
       <c r="AO13" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP13" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP13" s="34" t="s">
+      <c r="AQ13" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ13" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR13" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS13" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT13" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU13" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AV13" s="43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AW13" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX13" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX13" s="30" t="s">
+      <c r="AY13" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY13" s="30" t="s">
+      <c r="AZ13" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ13" s="30" t="s">
+      <c r="BA13" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA13" s="30" t="s">
+      <c r="BB13" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC13" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD13" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE13" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB13" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC13" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD13" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE13" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF13" s="44">
         <v>9893790957</v>
       </c>
       <c r="BG13" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH13" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI13" s="30">
         <v>47678965627</v>
       </c>
       <c r="BJ13" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK13" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="BM13" s="39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BN13" s="45">
         <v>35591</v>
       </c>
       <c r="BO13" s="45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BP13" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ13" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR13" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR13" s="30" t="s">
+      <c r="BS13" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS13" s="47" t="s">
+      <c r="BT13" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT13" s="30" t="s">
+      <c r="BU13" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU13" s="46" t="s">
+      <c r="BV13" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV13" s="46" t="s">
+      <c r="BW13" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW13" s="30" t="s">
+      <c r="BX13" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX13" s="30" t="s">
+      <c r="BY13" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY13" s="30" t="s">
+      <c r="BZ13" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ13" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="14" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="B14" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="C14" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="C14" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>214</v>
-      </c>
       <c r="G14" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H14" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I14" s="34" t="s">
+      <c r="J14" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J14" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K14" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L14" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M14" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N14" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N14" s="34" t="s">
+      <c r="O14" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O14" s="36" t="s">
+      <c r="P14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P14" s="34" t="s">
+      <c r="Q14" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q14" s="34" t="s">
+      <c r="R14" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S14" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T14" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U14" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R14" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S14" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T14" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U14" s="35" t="s">
+      <c r="V14" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V14" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W14" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X14" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y14" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z14" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z14" s="34" t="s">
-        <v>93</v>
-      </c>
       <c r="AA14" s="30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AB14" s="40" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AC14" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD14" s="30">
         <v>765</v>
@@ -5423,10 +5419,10 @@
         <v>20</v>
       </c>
       <c r="AG14" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH14" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI14" s="35">
         <v>43831</v>
@@ -5435,224 +5431,224 @@
         <v>45293</v>
       </c>
       <c r="AK14" s="39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL14" s="39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AM14" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="AN14" s="30">
         <v>110</v>
       </c>
       <c r="AO14" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP14" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP14" s="34" t="s">
+      <c r="AQ14" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ14" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR14" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS14" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT14" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AU14" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AV14" s="43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AW14" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX14" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX14" s="30" t="s">
+      <c r="AY14" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY14" s="30" t="s">
+      <c r="AZ14" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ14" s="30" t="s">
+      <c r="BA14" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA14" s="30" t="s">
-        <v>109</v>
-      </c>
       <c r="BB14" s="30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BC14" s="35">
         <v>46022</v>
       </c>
       <c r="BD14" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BE14" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BF14" s="44">
         <v>9893790958</v>
       </c>
       <c r="BG14" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH14" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI14" s="30">
         <v>47678965628</v>
       </c>
       <c r="BJ14" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK14" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="BM14" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN14" s="45">
         <v>35591</v>
       </c>
       <c r="BO14" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP14" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BQ14" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR14" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR14" s="30" t="s">
+      <c r="BS14" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS14" s="47" t="s">
+      <c r="BT14" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT14" s="30" t="s">
+      <c r="BU14" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU14" s="46" t="s">
+      <c r="BV14" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV14" s="46" t="s">
+      <c r="BW14" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW14" s="30" t="s">
+      <c r="BX14" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX14" s="30" t="s">
+      <c r="BY14" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY14" s="30" t="s">
+      <c r="BZ14" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ14" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="15" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="C15" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="C15" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>219</v>
-      </c>
       <c r="G15" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H15" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I15" s="34" t="s">
+      <c r="J15" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J15" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L15" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M15" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N15" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N15" s="34" t="s">
+      <c r="O15" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O15" s="36" t="s">
+      <c r="P15" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P15" s="34" t="s">
+      <c r="Q15" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q15" s="34" t="s">
+      <c r="R15" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S15" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T15" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U15" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R15" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S15" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U15" s="35" t="s">
+      <c r="V15" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V15" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W15" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X15" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y15" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z15" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z15" s="34" t="s">
+      <c r="AA15" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB15" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AA15" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB15" s="40" t="s">
-        <v>94</v>
-      </c>
       <c r="AC15" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD15" s="30">
         <v>765</v>
@@ -5664,10 +5660,10 @@
         <v>10</v>
       </c>
       <c r="AG15" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH15" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI15" s="35">
         <v>43831</v>
@@ -5676,225 +5672,225 @@
         <v>45293</v>
       </c>
       <c r="AK15" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL15" s="39" t="s">
         <v>97</v>
-      </c>
-      <c r="AL15" s="39" t="s">
-        <v>98</v>
       </c>
       <c r="AM15" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="AN15" s="30">
         <v>110</v>
       </c>
       <c r="AO15" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AP15" s="39" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AQ15" s="34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AR15" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS15" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT15" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="AU15" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AV15" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="AV15" s="43" t="s">
+      <c r="AW15" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AW15" s="30" t="s">
+      <c r="AX15" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX15" s="30" t="s">
+      <c r="AY15" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY15" s="30" t="s">
+      <c r="AZ15" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ15" s="30" t="s">
+      <c r="BA15" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA15" s="30" t="s">
+      <c r="BB15" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC15" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD15" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE15" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="BB15" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC15" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD15" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE15" s="30" t="s">
-        <v>110</v>
       </c>
       <c r="BF15" s="44">
         <v>9893790959</v>
       </c>
       <c r="BG15" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH15" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI15" s="30">
         <v>47678965629</v>
       </c>
       <c r="BJ15" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK15" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="BM15" s="39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BN15" s="45">
         <v>35591</v>
       </c>
       <c r="BO15" s="45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BP15" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BQ15" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR15" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR15" s="30" t="s">
+      <c r="BS15" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS15" s="47" t="s">
+      <c r="BT15" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT15" s="30" t="s">
+      <c r="BU15" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU15" s="46" t="s">
+      <c r="BV15" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV15" s="46" t="s">
+      <c r="BW15" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW15" s="30" t="s">
+      <c r="BX15" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX15" s="30" t="s">
+      <c r="BY15" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY15" s="30" t="s">
+      <c r="BZ15" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ15" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="16" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="43" t="s">
         <v>221</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="C16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="C16" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>223</v>
-      </c>
       <c r="G16" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H16" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="J16" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="J16" s="34" t="s">
-        <v>84</v>
       </c>
       <c r="K16" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="L16" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M16" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N16" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="N16" s="34" t="s">
+      <c r="O16" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="O16" s="36" t="s">
+      <c r="P16" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P16" s="34" t="s">
+      <c r="Q16" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q16" s="34" t="s">
+      <c r="R16" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="S16" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="T16" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U16" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="R16" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="S16" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="T16" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="U16" s="35" t="s">
+      <c r="V16" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="V16" s="37" t="s">
-        <v>91</v>
-      </c>
       <c r="W16" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X16" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="Y16" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z16" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="Z16" s="34" t="s">
+      <c r="AA16" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB16" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AA16" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB16" s="40" t="s">
+      <c r="AC16" s="39" t="s">
         <v>94</v>
-      </c>
-      <c r="AC16" s="39" t="s">
-        <v>95</v>
       </c>
       <c r="AD16" s="30">
         <v>765</v>
@@ -5906,10 +5902,10 @@
         <v>40</v>
       </c>
       <c r="AG16" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH16" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI16" s="35">
         <v>43831</v>
@@ -5918,136 +5914,136 @@
         <v>45293</v>
       </c>
       <c r="AK16" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL16" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AL16" s="39" t="s">
+      <c r="AM16" s="41" t="s">
         <v>98</v>
-      </c>
-      <c r="AM16" s="41" t="s">
-        <v>99</v>
       </c>
       <c r="AN16" s="30">
         <v>110</v>
       </c>
       <c r="AO16" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP16" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="AP16" s="34" t="s">
+      <c r="AQ16" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AQ16" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AR16" s="42">
         <f t="shared" ca="1" si="2"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AS16" s="42">
         <f t="shared" ca="1" si="3"/>
-        <v>45787</v>
+        <v>45795</v>
       </c>
       <c r="AT16" s="38" t="str">
         <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AU16" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AV16" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="AV16" s="43" t="s">
+      <c r="AW16" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AW16" s="30" t="s">
+      <c r="AX16" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AX16" s="30" t="s">
+      <c r="AY16" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AY16" s="30" t="s">
+      <c r="AZ16" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AZ16" s="30" t="s">
+      <c r="BA16" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="BA16" s="30" t="s">
-        <v>109</v>
-      </c>
       <c r="BB16" s="30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BC16" s="35">
         <v>46022</v>
       </c>
       <c r="BD16" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BE16" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BF16" s="44">
         <v>9893790960</v>
       </c>
       <c r="BG16" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BH16" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI16" s="30">
         <v>47678965630</v>
       </c>
       <c r="BJ16" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BK16" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BM16" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN16" s="45">
         <v>35591</v>
       </c>
       <c r="BO16" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BP16" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BQ16" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR16" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR16" s="30" t="s">
+      <c r="BS16" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="BS16" s="47" t="s">
+      <c r="BT16" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT16" s="30" t="s">
+      <c r="BU16" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="BU16" s="46" t="s">
+      <c r="BV16" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="BV16" s="46" t="s">
+      <c r="BW16" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="BW16" s="30" t="s">
+      <c r="BX16" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="BX16" s="30" t="s">
+      <c r="BY16" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="BY16" s="30" t="s">
+      <c r="BZ16" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BZ16" s="25" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="17" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="49"/>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
@@ -6127,7 +6123,7 @@
       <c r="BY17" s="49"/>
       <c r="BZ17" s="49"/>
     </row>
-    <row r="18" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="49"/>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
@@ -6207,7 +6203,7 @@
       <c r="BY18" s="49"/>
       <c r="BZ18" s="49"/>
     </row>
-    <row r="19" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="49"/>
       <c r="B19" s="49"/>
       <c r="C19" s="49"/>
@@ -6287,7 +6283,7 @@
       <c r="BY19" s="49"/>
       <c r="BZ19" s="49"/>
     </row>
-    <row r="20" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="49"/>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
@@ -6367,7 +6363,7 @@
       <c r="BY20" s="49"/>
       <c r="BZ20" s="49"/>
     </row>
-    <row r="21" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="49"/>
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>
@@ -6447,7 +6443,7 @@
       <c r="BY21" s="49"/>
       <c r="BZ21" s="49"/>
     </row>
-    <row r="22" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="49"/>
       <c r="B22" s="49"/>
       <c r="C22" s="49"/>
@@ -6527,7 +6523,7 @@
       <c r="BY22" s="49"/>
       <c r="BZ22" s="49"/>
     </row>
-    <row r="23" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="49"/>
       <c r="B23" s="49"/>
       <c r="C23" s="49"/>
@@ -6607,7 +6603,7 @@
       <c r="BY23" s="49"/>
       <c r="BZ23" s="49"/>
     </row>
-    <row r="24" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
       <c r="C24" s="49"/>
@@ -6687,7 +6683,7 @@
       <c r="BY24" s="49"/>
       <c r="BZ24" s="49"/>
     </row>
-    <row r="25" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
       <c r="C25" s="49"/>
@@ -6767,7 +6763,7 @@
       <c r="BY25" s="49"/>
       <c r="BZ25" s="49"/>
     </row>
-    <row r="26" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="49"/>
       <c r="B26" s="49"/>
       <c r="C26" s="49"/>
@@ -6847,7 +6843,7 @@
       <c r="BY26" s="49"/>
       <c r="BZ26" s="49"/>
     </row>
-    <row r="27" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="49"/>
       <c r="B27" s="49"/>
       <c r="C27" s="49"/>
@@ -6927,7 +6923,7 @@
       <c r="BY27" s="49"/>
       <c r="BZ27" s="49"/>
     </row>
-    <row r="28" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -7007,7 +7003,7 @@
       <c r="BY28" s="49"/>
       <c r="BZ28" s="49"/>
     </row>
-    <row r="29" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
       <c r="C29" s="49"/>
@@ -7087,7 +7083,7 @@
       <c r="BY29" s="49"/>
       <c r="BZ29" s="49"/>
     </row>
-    <row r="30" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="49"/>
       <c r="B30" s="49"/>
       <c r="C30" s="49"/>
@@ -7167,7 +7163,7 @@
       <c r="BY30" s="49"/>
       <c r="BZ30" s="49"/>
     </row>
-    <row r="31" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="49"/>
       <c r="B31" s="49"/>
       <c r="C31" s="49"/>
@@ -7247,7 +7243,7 @@
       <c r="BY31" s="49"/>
       <c r="BZ31" s="49"/>
     </row>
-    <row r="32" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="49"/>
       <c r="B32" s="49"/>
       <c r="C32" s="49"/>
@@ -7327,7 +7323,7 @@
       <c r="BY32" s="49"/>
       <c r="BZ32" s="49"/>
     </row>
-    <row r="33" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
       <c r="C33" s="49"/>
@@ -7407,7 +7403,7 @@
       <c r="BY33" s="49"/>
       <c r="BZ33" s="49"/>
     </row>
-    <row r="34" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
       <c r="C34" s="49"/>
@@ -7487,7 +7483,7 @@
       <c r="BY34" s="49"/>
       <c r="BZ34" s="49"/>
     </row>
-    <row r="35" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -7567,7 +7563,7 @@
       <c r="BY35" s="49"/>
       <c r="BZ35" s="49"/>
     </row>
-    <row r="36" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
       <c r="C36" s="49"/>
@@ -7647,7 +7643,7 @@
       <c r="BY36" s="49"/>
       <c r="BZ36" s="49"/>
     </row>
-    <row r="37" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
       <c r="C37" s="49"/>
@@ -7727,7 +7723,7 @@
       <c r="BY37" s="49"/>
       <c r="BZ37" s="49"/>
     </row>
-    <row r="38" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="49"/>
       <c r="B38" s="49"/>
       <c r="C38" s="49"/>
@@ -7807,7 +7803,7 @@
       <c r="BY38" s="49"/>
       <c r="BZ38" s="49"/>
     </row>
-    <row r="39" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="49"/>
       <c r="B39" s="49"/>
       <c r="C39" s="49"/>
@@ -7887,7 +7883,7 @@
       <c r="BY39" s="49"/>
       <c r="BZ39" s="49"/>
     </row>
-    <row r="40" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="49"/>
       <c r="B40" s="49"/>
       <c r="C40" s="49"/>
@@ -7967,7 +7963,7 @@
       <c r="BY40" s="49"/>
       <c r="BZ40" s="49"/>
     </row>
-    <row r="41" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
       <c r="C41" s="49"/>
@@ -8047,7 +8043,7 @@
       <c r="BY41" s="49"/>
       <c r="BZ41" s="49"/>
     </row>
-    <row r="42" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="49"/>
       <c r="B42" s="49"/>
       <c r="C42" s="49"/>
@@ -8127,7 +8123,7 @@
       <c r="BY42" s="49"/>
       <c r="BZ42" s="49"/>
     </row>
-    <row r="43" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="49"/>
       <c r="B43" s="49"/>
       <c r="C43" s="49"/>
@@ -8207,7 +8203,7 @@
       <c r="BY43" s="49"/>
       <c r="BZ43" s="49"/>
     </row>
-    <row r="44" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="49"/>
       <c r="B44" s="49"/>
       <c r="C44" s="49"/>
@@ -8287,7 +8283,7 @@
       <c r="BY44" s="49"/>
       <c r="BZ44" s="49"/>
     </row>
-    <row r="45" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
       <c r="C45" s="49"/>
@@ -8367,7 +8363,7 @@
       <c r="BY45" s="49"/>
       <c r="BZ45" s="49"/>
     </row>
-    <row r="46" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
       <c r="C46" s="49"/>
@@ -8447,7 +8443,7 @@
       <c r="BY46" s="49"/>
       <c r="BZ46" s="49"/>
     </row>
-    <row r="47" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
       <c r="C47" s="49"/>
@@ -8527,7 +8523,7 @@
       <c r="BY47" s="49"/>
       <c r="BZ47" s="49"/>
     </row>
-    <row r="48" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
       <c r="C48" s="49"/>
@@ -8607,7 +8603,7 @@
       <c r="BY48" s="49"/>
       <c r="BZ48" s="49"/>
     </row>
-    <row r="49" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
       <c r="C49" s="49"/>
@@ -8687,7 +8683,7 @@
       <c r="BY49" s="49"/>
       <c r="BZ49" s="49"/>
     </row>
-    <row r="50" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
       <c r="C50" s="49"/>
@@ -8767,7 +8763,7 @@
       <c r="BY50" s="49"/>
       <c r="BZ50" s="49"/>
     </row>
-    <row r="51" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="49"/>
       <c r="B51" s="49"/>
       <c r="C51" s="49"/>
@@ -8847,7 +8843,7 @@
       <c r="BY51" s="49"/>
       <c r="BZ51" s="49"/>
     </row>
-    <row r="52" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="49"/>
       <c r="B52" s="49"/>
       <c r="C52" s="49"/>
@@ -8927,7 +8923,7 @@
       <c r="BY52" s="49"/>
       <c r="BZ52" s="49"/>
     </row>
-    <row r="53" spans="1:78" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:78" s="25" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="49"/>
       <c r="B53" s="49"/>
       <c r="C53" s="49"/>
@@ -9007,7 +9003,7 @@
       <c r="BY53" s="49"/>
       <c r="BZ53" s="49"/>
     </row>
-    <row r="54" spans="1:78" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:78" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="49"/>
       <c r="B54" s="49"/>
       <c r="C54" s="49"/>
